--- a/product-definitions/spreadsheet/voc-concentration.xlsx
+++ b/product-definitions/spreadsheet/voc-concentration.xlsx
@@ -2556,7 +2556,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>19</v>
@@ -2574,7 +2574,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
         <v>20</v>
@@ -2592,7 +2592,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
         <v>22</v>
@@ -2610,7 +2610,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
         <v>23</v>
@@ -2628,7 +2628,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
         <v>25</v>
@@ -2646,7 +2646,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="10" t="s">
         <v>26</v>
@@ -2664,7 +2664,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
         <v>28</v>
@@ -2682,7 +2682,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="18" t="s">
         <v>30</v>
@@ -2700,7 +2700,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="11"/>
@@ -2714,7 +2714,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>35</v>
       </c>
@@ -2730,7 +2730,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
         <v>12</v>
@@ -2766,7 +2766,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
         <v>2</v>
@@ -2784,7 +2784,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="9" t="s">
         <v>19</v>
@@ -2802,7 +2802,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="9" t="s">
         <v>20</v>
@@ -2820,7 +2820,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="9"/>
       <c r="B36" s="9" t="s">
         <v>22</v>
@@ -2838,7 +2838,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="9"/>
       <c r="B37" s="9" t="s">
         <v>23</v>
@@ -2856,7 +2856,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="9"/>
       <c r="B38" s="9" t="s">
         <v>25</v>
@@ -2874,7 +2874,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="9"/>
       <c r="B39" s="10" t="s">
         <v>26</v>
@@ -2892,7 +2892,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="9"/>
       <c r="B40" s="9" t="s">
         <v>28</v>
@@ -2910,7 +2910,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="9"/>
       <c r="B41" s="18" t="s">
         <v>30</v>
@@ -2928,7 +2928,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -2942,7 +2942,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>38</v>
       </c>
@@ -2958,7 +2958,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="9"/>
       <c r="B44" s="9" t="s">
         <v>10</v>
@@ -2976,7 +2976,7 @@
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="9"/>
       <c r="B45" s="9" t="s">
         <v>12</v>
@@ -2994,7 +2994,7 @@
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
         <v>2</v>
@@ -3012,7 +3012,7 @@
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="9"/>
       <c r="B47" s="9" t="s">
         <v>19</v>
@@ -3030,7 +3030,7 @@
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="9"/>
       <c r="B48" s="9" t="s">
         <v>20</v>
@@ -3048,7 +3048,7 @@
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="9"/>
       <c r="B49" s="9" t="s">
         <v>22</v>
@@ -3066,7 +3066,7 @@
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="9"/>
       <c r="B50" s="9" t="s">
         <v>23</v>
@@ -3084,7 +3084,7 @@
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="9"/>
       <c r="B51" s="9" t="s">
         <v>25</v>
@@ -3102,7 +3102,7 @@
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="9"/>
       <c r="B52" s="10" t="s">
         <v>26</v>
@@ -3120,7 +3120,7 @@
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="9"/>
       <c r="B53" s="9" t="s">
         <v>28</v>
@@ -3138,7 +3138,7 @@
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="9"/>
       <c r="B54" s="18" t="s">
         <v>30</v>
@@ -3156,7 +3156,7 @@
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -3170,7 +3170,7 @@
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>41</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="9"/>
       <c r="B57" s="9" t="s">
         <v>10</v>
@@ -3204,7 +3204,7 @@
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="9"/>
       <c r="B58" s="9" t="s">
         <v>12</v>
@@ -3222,7 +3222,7 @@
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="11"/>
       <c r="B59" s="10" t="s">
         <v>2</v>
@@ -3242,7 +3242,7 @@
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9"/>
       <c r="B60" s="10" t="s">
         <v>16</v>
@@ -3262,7 +3262,7 @@
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="9"/>
       <c r="B61" s="9" t="s">
         <v>19</v>
@@ -3280,7 +3280,7 @@
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="9"/>
       <c r="B62" s="9" t="s">
         <v>20</v>
@@ -3298,7 +3298,7 @@
       <c r="K62" s="9"/>
       <c r="L62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="9"/>
       <c r="B63" s="9" t="s">
         <v>22</v>
@@ -3316,7 +3316,7 @@
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="9"/>
       <c r="B64" s="9" t="s">
         <v>23</v>
@@ -3334,7 +3334,7 @@
       <c r="K64" s="9"/>
       <c r="L64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="9"/>
       <c r="B65" s="9" t="s">
         <v>25</v>
@@ -3352,7 +3352,7 @@
       <c r="K65" s="9"/>
       <c r="L65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
         <v>26</v>
@@ -3370,7 +3370,7 @@
       <c r="K66" s="9"/>
       <c r="L66" s="9"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="9"/>
       <c r="B67" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="9"/>
       <c r="B68" s="18" t="s">
         <v>30</v>
@@ -3406,7 +3406,7 @@
       <c r="K68" s="9"/>
       <c r="L68" s="9"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -3420,7 +3420,7 @@
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>44</v>
       </c>
@@ -3436,7 +3436,7 @@
       <c r="K70" s="9"/>
       <c r="L70" s="9"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="9"/>
       <c r="B71" s="9" t="s">
         <v>10</v>
@@ -3454,7 +3454,7 @@
       <c r="K71" s="9"/>
       <c r="L71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="9"/>
       <c r="B72" s="9" t="s">
         <v>12</v>
@@ -3472,7 +3472,7 @@
       <c r="K72" s="9"/>
       <c r="L72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="11"/>
       <c r="B73" s="10" t="s">
         <v>2</v>
@@ -3492,7 +3492,7 @@
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="9"/>
       <c r="B74" s="10" t="s">
         <v>16</v>
@@ -3512,7 +3512,7 @@
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="9" t="s">
         <v>19</v>
@@ -3530,7 +3530,7 @@
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="9"/>
       <c r="B76" s="9" t="s">
         <v>20</v>
@@ -3548,7 +3548,7 @@
       <c r="K76" s="9"/>
       <c r="L76" s="9"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="9"/>
       <c r="B77" s="9" t="s">
         <v>22</v>
@@ -3566,7 +3566,7 @@
       <c r="K77" s="9"/>
       <c r="L77" s="9"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="9"/>
       <c r="B78" s="9" t="s">
         <v>23</v>
@@ -3584,7 +3584,7 @@
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="9"/>
       <c r="B79" s="9" t="s">
         <v>25</v>
@@ -3602,7 +3602,7 @@
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="9"/>
       <c r="B80" s="10" t="s">
         <v>26</v>
@@ -3620,7 +3620,7 @@
       <c r="K80" s="9"/>
       <c r="L80" s="9"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="9"/>
       <c r="B81" s="9" t="s">
         <v>28</v>
@@ -3638,7 +3638,7 @@
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="9"/>
       <c r="B82" s="18" t="s">
         <v>30</v>
@@ -3656,7 +3656,7 @@
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="11"/>
@@ -3670,7 +3670,7 @@
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>46</v>
       </c>
@@ -3681,7 +3681,7 @@
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="9"/>
       <c r="B85" s="9" t="s">
         <v>10</v>
@@ -3694,7 +3694,7 @@
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="9"/>
       <c r="B86" s="9" t="s">
         <v>12</v>
@@ -3707,7 +3707,7 @@
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="10" t="s">
         <v>2</v>
@@ -3720,7 +3720,7 @@
       <c r="F87" s="11"/>
       <c r="G87" s="9"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="9"/>
       <c r="B88" s="9" t="s">
         <v>19</v>
@@ -3733,7 +3733,7 @@
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="9"/>
       <c r="B89" s="9" t="s">
         <v>20</v>
@@ -3746,7 +3746,7 @@
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="9"/>
       <c r="B90" s="9" t="s">
         <v>22</v>
@@ -3759,7 +3759,7 @@
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="9"/>
       <c r="B91" s="9" t="s">
         <v>23</v>
@@ -3772,7 +3772,7 @@
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="9"/>
       <c r="B92" s="9" t="s">
         <v>25</v>
@@ -3785,7 +3785,7 @@
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="9"/>
       <c r="B93" s="10" t="s">
         <v>26</v>
@@ -3798,7 +3798,7 @@
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="9"/>
       <c r="B94" s="9" t="s">
         <v>28</v>
@@ -3811,7 +3811,7 @@
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="9"/>
       <c r="B95" s="18" t="s">
         <v>30</v>
@@ -3824,7 +3824,7 @@
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -3833,7 +3833,7 @@
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>48</v>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="9"/>
       <c r="B98" s="9" t="s">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="9"/>
       <c r="B99" s="9" t="s">
         <v>12</v>
@@ -3870,7 +3870,7 @@
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="10" t="s">
         <v>2</v>
@@ -3883,7 +3883,7 @@
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="9"/>
       <c r="B101" s="9" t="s">
         <v>19</v>
@@ -3896,7 +3896,7 @@
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="9"/>
       <c r="B102" s="9" t="s">
         <v>20</v>
@@ -3909,7 +3909,7 @@
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="9"/>
       <c r="B103" s="9" t="s">
         <v>22</v>
@@ -3922,7 +3922,7 @@
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="9"/>
       <c r="B104" s="9" t="s">
         <v>23</v>
@@ -3935,7 +3935,7 @@
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="9"/>
       <c r="B105" s="9" t="s">
         <v>25</v>
@@ -3948,7 +3948,7 @@
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="9"/>
       <c r="B106" s="10" t="s">
         <v>26</v>
@@ -3961,7 +3961,7 @@
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="9"/>
       <c r="B107" s="9" t="s">
         <v>28</v>
@@ -3974,7 +3974,7 @@
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="9"/>
       <c r="B108" s="18" t="s">
         <v>30</v>
@@ -3987,12 +3987,12 @@
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>50</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="9"/>
       <c r="B111" s="9" t="s">
         <v>10</v>
@@ -4014,7 +4014,7 @@
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="9"/>
       <c r="B112" s="9" t="s">
         <v>12</v>
@@ -4026,7 +4026,7 @@
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="11"/>
       <c r="B113" s="10" t="s">
         <v>2</v>
@@ -4040,7 +4040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="9"/>
       <c r="B114" s="10" t="s">
         <v>16</v>
@@ -4054,7 +4054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="9"/>
       <c r="B115" s="9" t="s">
         <v>19</v>
@@ -4066,7 +4066,7 @@
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="9"/>
       <c r="B116" s="9" t="s">
         <v>20</v>
@@ -4078,7 +4078,7 @@
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="9"/>
       <c r="B117" s="9" t="s">
         <v>22</v>
@@ -4090,7 +4090,7 @@
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="9"/>
       <c r="B118" s="9" t="s">
         <v>23</v>
@@ -4102,7 +4102,7 @@
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="9"/>
       <c r="B119" s="9" t="s">
         <v>25</v>
@@ -4114,7 +4114,7 @@
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="9"/>
       <c r="B120" s="10" t="s">
         <v>26</v>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="F120" s="9"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="9"/>
       <c r="B121" s="9" t="s">
         <v>28</v>
@@ -4138,7 +4138,7 @@
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="9"/>
       <c r="B122" s="18" t="s">
         <v>30</v>
@@ -4150,7 +4150,7 @@
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -4158,7 +4158,7 @@
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="8" t="s">
         <v>53</v>
       </c>
@@ -4168,7 +4168,7 @@
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="9"/>
       <c r="B125" s="9" t="s">
         <v>10</v>
@@ -4180,7 +4180,7 @@
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="9"/>
       <c r="B126" s="9" t="s">
         <v>12</v>
@@ -4192,7 +4192,7 @@
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="11"/>
       <c r="B127" s="10" t="s">
         <v>2</v>
@@ -4206,7 +4206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="9"/>
       <c r="B128" s="10" t="s">
         <v>16</v>
@@ -4220,7 +4220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="9"/>
       <c r="B129" s="9" t="s">
         <v>19</v>
@@ -4232,7 +4232,7 @@
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="9"/>
       <c r="B130" s="9" t="s">
         <v>20</v>
@@ -4244,7 +4244,7 @@
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="9"/>
       <c r="B131" s="9" t="s">
         <v>22</v>
@@ -4256,7 +4256,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="9"/>
       <c r="B132" s="9" t="s">
         <v>23</v>
@@ -4268,7 +4268,7 @@
       <c r="E132" s="9"/>
       <c r="F132" s="9"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="9"/>
       <c r="B133" s="9" t="s">
         <v>25</v>
@@ -4280,7 +4280,7 @@
       <c r="E133" s="9"/>
       <c r="F133" s="9"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="9"/>
       <c r="B134" s="10" t="s">
         <v>26</v>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="F134" s="9"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="9"/>
       <c r="B135" s="9" t="s">
         <v>28</v>
@@ -4304,7 +4304,7 @@
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="9"/>
       <c r="B136" s="18" t="s">
         <v>30</v>
@@ -4316,7 +4316,7 @@
       <c r="E136" s="9"/>
       <c r="F136" s="9"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="11"/>
@@ -4324,7 +4324,7 @@
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="8" t="s">
         <v>55</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="E138" s="9"/>
       <c r="F138" s="9"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="9"/>
       <c r="B139" s="9" t="s">
         <v>10</v>
@@ -4346,7 +4346,7 @@
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="9"/>
       <c r="B140" s="9" t="s">
         <v>12</v>
@@ -4358,7 +4358,7 @@
       <c r="E140" s="9"/>
       <c r="F140" s="9"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="10"/>
       <c r="B141" s="10" t="s">
         <v>2</v>
@@ -4370,7 +4370,7 @@
       <c r="E141" s="11"/>
       <c r="F141" s="11"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="9"/>
       <c r="B142" s="9" t="s">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       <c r="E142" s="9"/>
       <c r="F142" s="9"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="9"/>
       <c r="B143" s="9" t="s">
         <v>20</v>
@@ -4394,7 +4394,7 @@
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="9"/>
       <c r="B144" s="9" t="s">
         <v>22</v>
@@ -4406,7 +4406,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="9"/>
       <c r="B145" s="9" t="s">
         <v>23</v>
@@ -4418,7 +4418,7 @@
       <c r="E145" s="9"/>
       <c r="F145" s="9"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="9"/>
       <c r="B146" s="9" t="s">
         <v>25</v>
@@ -4430,7 +4430,7 @@
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="9"/>
       <c r="B147" s="10" t="s">
         <v>26</v>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="F147" s="9"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="9"/>
       <c r="B148" s="9" t="s">
         <v>28</v>
@@ -4454,7 +4454,7 @@
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="9"/>
       <c r="B149" s="18" t="s">
         <v>30</v>
@@ -4466,7 +4466,7 @@
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -4474,7 +4474,7 @@
       <c r="E150" s="9"/>
       <c r="F150" s="9"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="8" t="s">
         <v>57</v>
       </c>
@@ -4484,7 +4484,7 @@
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="9"/>
       <c r="B152" s="9" t="s">
         <v>10</v>
@@ -4496,7 +4496,7 @@
       <c r="E152" s="9"/>
       <c r="F152" s="9"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="9"/>
       <c r="B153" s="9" t="s">
         <v>12</v>
@@ -4508,7 +4508,7 @@
       <c r="E153" s="9"/>
       <c r="F153" s="9"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="10"/>
       <c r="B154" s="10" t="s">
         <v>2</v>
@@ -4520,7 +4520,7 @@
       <c r="E154" s="11"/>
       <c r="F154" s="9"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="9"/>
       <c r="B155" s="9" t="s">
         <v>19</v>
@@ -4532,7 +4532,7 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="9"/>
       <c r="B156" s="9" t="s">
         <v>20</v>
@@ -4544,7 +4544,7 @@
       <c r="E156" s="9"/>
       <c r="F156" s="9"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="9"/>
       <c r="B157" s="9" t="s">
         <v>22</v>
@@ -4556,7 +4556,7 @@
       <c r="E157" s="9"/>
       <c r="F157" s="9"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="9"/>
       <c r="B158" s="9" t="s">
         <v>23</v>
@@ -4568,7 +4568,7 @@
       <c r="E158" s="9"/>
       <c r="F158" s="9"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="9"/>
       <c r="B159" s="9" t="s">
         <v>25</v>
@@ -4580,7 +4580,7 @@
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="9"/>
       <c r="B160" s="10" t="s">
         <v>26</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="F160" s="9"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="9"/>
       <c r="B161" s="9" t="s">
         <v>28</v>
@@ -4604,7 +4604,7 @@
       <c r="E161" s="9"/>
       <c r="F161" s="9"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="9"/>
       <c r="B162" s="18" t="s">
         <v>30</v>
@@ -4616,7 +4616,8 @@
       <c r="E162" s="9"/>
       <c r="F162" s="9"/>
     </row>
-    <row r="164">
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="8" t="s">
         <v>59</v>
       </c>
@@ -4626,7 +4627,7 @@
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="9"/>
       <c r="B165" s="9" t="s">
         <v>10</v>
@@ -4638,7 +4639,7 @@
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="9"/>
       <c r="B166" s="9" t="s">
         <v>12</v>
@@ -4650,7 +4651,7 @@
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="11"/>
       <c r="B167" s="10" t="s">
         <v>2</v>
@@ -4664,7 +4665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="9"/>
       <c r="B168" s="10" t="s">
         <v>16</v>
@@ -4678,7 +4679,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="9"/>
       <c r="B169" s="9" t="s">
         <v>19</v>
@@ -4690,7 +4691,7 @@
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="9"/>
       <c r="B170" s="9" t="s">
         <v>20</v>
@@ -4702,7 +4703,7 @@
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="9"/>
       <c r="B171" s="9" t="s">
         <v>22</v>
@@ -4714,7 +4715,7 @@
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="9"/>
       <c r="B172" s="9" t="s">
         <v>23</v>
@@ -4726,7 +4727,7 @@
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="9"/>
       <c r="B173" s="9" t="s">
         <v>25</v>
@@ -4738,7 +4739,7 @@
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="9"/>
       <c r="B174" s="10" t="s">
         <v>26</v>
@@ -4750,7 +4751,7 @@
       </c>
       <c r="F174" s="9"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="9"/>
       <c r="B175" s="9" t="s">
         <v>28</v>
@@ -4762,7 +4763,7 @@
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="9"/>
       <c r="B176" s="18" t="s">
         <v>30</v>
@@ -4774,7 +4775,7 @@
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="9"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -4782,7 +4783,7 @@
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8" t="s">
         <v>62</v>
       </c>
@@ -4792,7 +4793,7 @@
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="9"/>
       <c r="B179" s="9" t="s">
         <v>10</v>
@@ -4804,7 +4805,7 @@
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="9"/>
       <c r="B180" s="9" t="s">
         <v>12</v>
@@ -4816,7 +4817,7 @@
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="11"/>
       <c r="B181" s="10" t="s">
         <v>2</v>
@@ -4830,7 +4831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="9"/>
       <c r="B182" s="10" t="s">
         <v>16</v>
@@ -4844,7 +4845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="9"/>
       <c r="B183" s="9" t="s">
         <v>19</v>
@@ -4856,7 +4857,7 @@
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="9"/>
       <c r="B184" s="9" t="s">
         <v>20</v>
@@ -4868,7 +4869,7 @@
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="9"/>
       <c r="B185" s="9" t="s">
         <v>22</v>
@@ -4880,7 +4881,7 @@
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="9"/>
       <c r="B186" s="9" t="s">
         <v>23</v>
@@ -4892,7 +4893,7 @@
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="9"/>
       <c r="B187" s="9" t="s">
         <v>25</v>
@@ -4904,7 +4905,7 @@
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="9"/>
       <c r="B188" s="10" t="s">
         <v>26</v>
@@ -4916,7 +4917,7 @@
       </c>
       <c r="F188" s="9"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="9"/>
       <c r="B189" s="9" t="s">
         <v>28</v>
@@ -4928,7 +4929,7 @@
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="9"/>
       <c r="B190" s="18" t="s">
         <v>30</v>
@@ -4940,7 +4941,7 @@
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="11"/>
@@ -4948,7 +4949,7 @@
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8" t="s">
         <v>64</v>
       </c>
@@ -4958,7 +4959,7 @@
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="9"/>
       <c r="B193" s="9" t="s">
         <v>10</v>
@@ -4970,7 +4971,7 @@
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="9"/>
       <c r="B194" s="9" t="s">
         <v>12</v>
@@ -4982,7 +4983,7 @@
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="10"/>
       <c r="B195" s="10" t="s">
         <v>2</v>
@@ -4994,7 +4995,7 @@
       <c r="E195" s="11"/>
       <c r="F195" s="11"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="9"/>
       <c r="B196" s="9" t="s">
         <v>19</v>
@@ -5006,7 +5007,7 @@
       <c r="E196" s="9"/>
       <c r="F196" s="9"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="9"/>
       <c r="B197" s="9" t="s">
         <v>20</v>
@@ -5018,7 +5019,7 @@
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="9"/>
       <c r="B198" s="9" t="s">
         <v>22</v>
@@ -5030,7 +5031,7 @@
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="9"/>
       <c r="B199" s="9" t="s">
         <v>23</v>
@@ -5042,7 +5043,7 @@
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="9"/>
       <c r="B200" s="9" t="s">
         <v>25</v>
@@ -5054,7 +5055,7 @@
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="9"/>
       <c r="B201" s="10" t="s">
         <v>26</v>
@@ -5066,7 +5067,7 @@
       </c>
       <c r="F201" s="9"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="9"/>
       <c r="B202" s="9" t="s">
         <v>28</v>
@@ -5078,7 +5079,7 @@
       <c r="E202" s="9"/>
       <c r="F202" s="9"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="9"/>
       <c r="B203" s="18" t="s">
         <v>30</v>
@@ -5090,7 +5091,7 @@
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="9"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -5098,7 +5099,7 @@
       <c r="E204" s="9"/>
       <c r="F204" s="9"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="8" t="s">
         <v>66</v>
       </c>
@@ -5108,7 +5109,7 @@
       <c r="E205" s="9"/>
       <c r="F205" s="9"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="9"/>
       <c r="B206" s="9" t="s">
         <v>10</v>
@@ -5120,7 +5121,7 @@
       <c r="E206" s="9"/>
       <c r="F206" s="9"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="9"/>
       <c r="B207" s="9" t="s">
         <v>12</v>
@@ -5132,7 +5133,7 @@
       <c r="E207" s="9"/>
       <c r="F207" s="9"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="10"/>
       <c r="B208" s="10" t="s">
         <v>2</v>
@@ -5144,7 +5145,7 @@
       <c r="E208" s="11"/>
       <c r="F208" s="9"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="9"/>
       <c r="B209" s="9" t="s">
         <v>19</v>
@@ -5156,7 +5157,7 @@
       <c r="E209" s="9"/>
       <c r="F209" s="9"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="9"/>
       <c r="B210" s="9" t="s">
         <v>20</v>
@@ -5168,7 +5169,7 @@
       <c r="E210" s="9"/>
       <c r="F210" s="9"/>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="9"/>
       <c r="B211" s="9" t="s">
         <v>22</v>
@@ -5180,7 +5181,7 @@
       <c r="E211" s="9"/>
       <c r="F211" s="9"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="9"/>
       <c r="B212" s="9" t="s">
         <v>23</v>
@@ -5192,7 +5193,7 @@
       <c r="E212" s="9"/>
       <c r="F212" s="9"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="9"/>
       <c r="B213" s="9" t="s">
         <v>25</v>
@@ -5204,7 +5205,7 @@
       <c r="E213" s="9"/>
       <c r="F213" s="9"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="9"/>
       <c r="B214" s="10" t="s">
         <v>26</v>
@@ -5216,7 +5217,7 @@
       </c>
       <c r="F214" s="9"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="9"/>
       <c r="B215" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5229,7 @@
       <c r="E215" s="9"/>
       <c r="F215" s="9"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="9"/>
       <c r="B216" s="18" t="s">
         <v>30</v>
@@ -5240,7 +5241,8 @@
       <c r="E216" s="9"/>
       <c r="F216" s="9"/>
     </row>
-    <row r="218">
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="8" t="s">
         <v>68</v>
       </c>
@@ -5251,7 +5253,7 @@
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="9"/>
       <c r="B219" s="9" t="s">
         <v>10</v>
@@ -5264,7 +5266,7 @@
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="9"/>
       <c r="B220" s="9" t="s">
         <v>12</v>
@@ -5277,7 +5279,7 @@
       <c r="F220" s="9"/>
       <c r="G220" s="9"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="11"/>
       <c r="B221" s="10" t="s">
         <v>2</v>
@@ -5292,7 +5294,7 @@
       </c>
       <c r="G221" s="9"/>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>16</v>
@@ -5307,7 +5309,7 @@
       </c>
       <c r="G222" s="9"/>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="9"/>
       <c r="B223" s="9" t="s">
         <v>19</v>
@@ -5320,7 +5322,7 @@
       <c r="F223" s="9"/>
       <c r="G223" s="9"/>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="9"/>
       <c r="B224" s="9" t="s">
         <v>20</v>
@@ -5333,7 +5335,7 @@
       <c r="F224" s="9"/>
       <c r="G224" s="9"/>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="9"/>
       <c r="B225" s="9" t="s">
         <v>22</v>
@@ -5346,7 +5348,7 @@
       <c r="F225" s="9"/>
       <c r="G225" s="9"/>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="9"/>
       <c r="B226" s="9" t="s">
         <v>23</v>
@@ -5359,7 +5361,7 @@
       <c r="F226" s="9"/>
       <c r="G226" s="9"/>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="9"/>
       <c r="B227" s="9" t="s">
         <v>25</v>
@@ -5372,7 +5374,7 @@
       <c r="F227" s="9"/>
       <c r="G227" s="9"/>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="9"/>
       <c r="B228" s="10" t="s">
         <v>26</v>
@@ -5385,7 +5387,7 @@
       <c r="F228" s="9"/>
       <c r="G228" s="9"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="9"/>
       <c r="B229" s="9" t="s">
         <v>28</v>
@@ -5398,7 +5400,7 @@
       <c r="F229" s="9"/>
       <c r="G229" s="9"/>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="9"/>
       <c r="B230" s="18" t="s">
         <v>30</v>
@@ -5411,7 +5413,7 @@
       <c r="F230" s="9"/>
       <c r="G230" s="9"/>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="9"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -5420,7 +5422,7 @@
       <c r="F231" s="9"/>
       <c r="G231" s="9"/>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="8" t="s">
         <v>71</v>
       </c>
@@ -5431,7 +5433,7 @@
       <c r="F232" s="9"/>
       <c r="G232" s="9"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="9"/>
       <c r="B233" s="9" t="s">
         <v>10</v>
@@ -5444,7 +5446,7 @@
       <c r="F233" s="9"/>
       <c r="G233" s="9"/>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="9"/>
       <c r="B234" s="9" t="s">
         <v>12</v>
@@ -5457,7 +5459,7 @@
       <c r="F234" s="9"/>
       <c r="G234" s="9"/>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="11"/>
       <c r="B235" s="10" t="s">
         <v>2</v>
@@ -5472,7 +5474,7 @@
       </c>
       <c r="G235" s="9"/>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="9"/>
       <c r="B236" s="10" t="s">
         <v>16</v>
@@ -5487,7 +5489,7 @@
       </c>
       <c r="G236" s="9"/>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="9"/>
       <c r="B237" s="9" t="s">
         <v>19</v>
@@ -5500,7 +5502,7 @@
       <c r="F237" s="9"/>
       <c r="G237" s="9"/>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="9"/>
       <c r="B238" s="9" t="s">
         <v>20</v>
@@ -5513,7 +5515,7 @@
       <c r="F238" s="9"/>
       <c r="G238" s="9"/>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="9"/>
       <c r="B239" s="9" t="s">
         <v>22</v>
@@ -5526,7 +5528,7 @@
       <c r="F239" s="9"/>
       <c r="G239" s="9"/>
     </row>
-    <row r="240">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="9"/>
       <c r="B240" s="9" t="s">
         <v>23</v>
@@ -5539,7 +5541,7 @@
       <c r="F240" s="9"/>
       <c r="G240" s="9"/>
     </row>
-    <row r="241">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="9"/>
       <c r="B241" s="9" t="s">
         <v>25</v>
@@ -5552,7 +5554,7 @@
       <c r="F241" s="9"/>
       <c r="G241" s="9"/>
     </row>
-    <row r="242">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="9"/>
       <c r="B242" s="10" t="s">
         <v>26</v>
@@ -5565,7 +5567,7 @@
       <c r="F242" s="9"/>
       <c r="G242" s="9"/>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="9"/>
       <c r="B243" s="9" t="s">
         <v>28</v>
@@ -5578,7 +5580,7 @@
       <c r="F243" s="9"/>
       <c r="G243" s="9"/>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="9"/>
       <c r="B244" s="18" t="s">
         <v>30</v>
@@ -5591,7 +5593,7 @@
       <c r="F244" s="9"/>
       <c r="G244" s="9"/>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="9"/>
       <c r="B245" s="9"/>
       <c r="C245" s="11"/>
@@ -5600,7 +5602,7 @@
       <c r="F245" s="9"/>
       <c r="G245" s="9"/>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="8" t="s">
         <v>73</v>
       </c>
@@ -5611,7 +5613,7 @@
       <c r="F246" s="9"/>
       <c r="G246" s="9"/>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="9"/>
       <c r="B247" s="9" t="s">
         <v>10</v>
@@ -5624,7 +5626,7 @@
       <c r="F247" s="9"/>
       <c r="G247" s="9"/>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="9"/>
       <c r="B248" s="9" t="s">
         <v>12</v>
@@ -5637,7 +5639,7 @@
       <c r="F248" s="9"/>
       <c r="G248" s="9"/>
     </row>
-    <row r="249">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="10"/>
       <c r="B249" s="10" t="s">
         <v>2</v>
@@ -5650,7 +5652,7 @@
       <c r="F249" s="11"/>
       <c r="G249" s="9"/>
     </row>
-    <row r="250">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="9"/>
       <c r="B250" s="9" t="s">
         <v>19</v>
@@ -5663,7 +5665,7 @@
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
     </row>
-    <row r="251">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="9"/>
       <c r="B251" s="9" t="s">
         <v>20</v>
@@ -5676,7 +5678,7 @@
       <c r="F251" s="9"/>
       <c r="G251" s="9"/>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="9"/>
       <c r="B252" s="9" t="s">
         <v>22</v>
@@ -5689,7 +5691,7 @@
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="9"/>
       <c r="B253" s="9" t="s">
         <v>23</v>
@@ -5702,7 +5704,7 @@
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
     </row>
-    <row r="254">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="9"/>
       <c r="B254" s="9" t="s">
         <v>25</v>
@@ -5715,7 +5717,7 @@
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
     </row>
-    <row r="255">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="9"/>
       <c r="B255" s="10" t="s">
         <v>26</v>
@@ -5728,7 +5730,7 @@
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
     </row>
-    <row r="256">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="9"/>
       <c r="B256" s="9" t="s">
         <v>28</v>
@@ -5741,7 +5743,7 @@
       <c r="F256" s="9"/>
       <c r="G256" s="9"/>
     </row>
-    <row r="257">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="9"/>
       <c r="B257" s="18" t="s">
         <v>30</v>
@@ -5754,7 +5756,7 @@
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
     </row>
-    <row r="258">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="9"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
@@ -5763,7 +5765,7 @@
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
     </row>
-    <row r="259">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="8" t="s">
         <v>75</v>
       </c>
@@ -5774,7 +5776,7 @@
       <c r="F259" s="9"/>
       <c r="G259" s="9"/>
     </row>
-    <row r="260">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="9"/>
       <c r="B260" s="9" t="s">
         <v>10</v>
@@ -5787,7 +5789,7 @@
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
     </row>
-    <row r="261">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="9"/>
       <c r="B261" s="9" t="s">
         <v>12</v>
@@ -5800,7 +5802,7 @@
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
     </row>
-    <row r="262">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="10"/>
       <c r="B262" s="10" t="s">
         <v>2</v>
@@ -5813,7 +5815,7 @@
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
     </row>
-    <row r="263">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="9"/>
       <c r="B263" s="9" t="s">
         <v>19</v>
@@ -5826,7 +5828,7 @@
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
     </row>
-    <row r="264">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="9"/>
       <c r="B264" s="9" t="s">
         <v>20</v>
@@ -5839,7 +5841,7 @@
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
     </row>
-    <row r="265">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="9"/>
       <c r="B265" s="9" t="s">
         <v>22</v>
@@ -5852,7 +5854,7 @@
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
     </row>
-    <row r="266">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="9"/>
       <c r="B266" s="9" t="s">
         <v>23</v>
@@ -5865,7 +5867,7 @@
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
     </row>
-    <row r="267">
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="9"/>
       <c r="B267" s="9" t="s">
         <v>25</v>
@@ -5878,7 +5880,7 @@
       <c r="F267" s="9"/>
       <c r="G267" s="9"/>
     </row>
-    <row r="268">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="9"/>
       <c r="B268" s="10" t="s">
         <v>26</v>
@@ -5891,7 +5893,7 @@
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
     </row>
-    <row r="269">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="9"/>
       <c r="B269" s="9" t="s">
         <v>28</v>
@@ -5904,7 +5906,7 @@
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
     </row>
-    <row r="270">
+    <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="9"/>
       <c r="B270" s="18" t="s">
         <v>30</v>
@@ -5917,7 +5919,8 @@
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
     </row>
-    <row r="272">
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="8" t="s">
         <v>77</v>
       </c>
@@ -5927,7 +5930,7 @@
       <c r="E272" s="9"/>
       <c r="F272" s="9"/>
     </row>
-    <row r="273">
+    <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="9"/>
       <c r="B273" s="9" t="s">
         <v>10</v>
@@ -5939,7 +5942,7 @@
       <c r="E273" s="9"/>
       <c r="F273" s="9"/>
     </row>
-    <row r="274">
+    <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="9"/>
       <c r="B274" s="9" t="s">
         <v>12</v>
@@ -5951,7 +5954,7 @@
       <c r="E274" s="9"/>
       <c r="F274" s="9"/>
     </row>
-    <row r="275">
+    <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="11"/>
       <c r="B275" s="10" t="s">
         <v>2</v>
@@ -5965,7 +5968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="9"/>
       <c r="B276" s="10" t="s">
         <v>16</v>
@@ -5979,7 +5982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="9"/>
       <c r="B277" s="9" t="s">
         <v>19</v>
@@ -5991,7 +5994,7 @@
       <c r="E277" s="9"/>
       <c r="F277" s="9"/>
     </row>
-    <row r="278">
+    <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="9"/>
       <c r="B278" s="9" t="s">
         <v>20</v>
@@ -6003,7 +6006,7 @@
       <c r="E278" s="9"/>
       <c r="F278" s="9"/>
     </row>
-    <row r="279">
+    <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="9"/>
       <c r="B279" s="9" t="s">
         <v>22</v>
@@ -6015,7 +6018,7 @@
       <c r="E279" s="9"/>
       <c r="F279" s="9"/>
     </row>
-    <row r="280">
+    <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="9"/>
       <c r="B280" s="9" t="s">
         <v>23</v>
@@ -6027,7 +6030,7 @@
       <c r="E280" s="9"/>
       <c r="F280" s="9"/>
     </row>
-    <row r="281">
+    <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="9"/>
       <c r="B281" s="9" t="s">
         <v>25</v>
@@ -6039,7 +6042,7 @@
       <c r="E281" s="9"/>
       <c r="F281" s="9"/>
     </row>
-    <row r="282">
+    <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="9"/>
       <c r="B282" s="10" t="s">
         <v>26</v>
@@ -6051,7 +6054,7 @@
       </c>
       <c r="F282" s="9"/>
     </row>
-    <row r="283">
+    <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="9"/>
       <c r="B283" s="9" t="s">
         <v>28</v>
@@ -6063,7 +6066,7 @@
       <c r="E283" s="9"/>
       <c r="F283" s="9"/>
     </row>
-    <row r="284">
+    <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="9"/>
       <c r="B284" s="18" t="s">
         <v>30</v>
@@ -6075,7 +6078,7 @@
       <c r="E284" s="9"/>
       <c r="F284" s="9"/>
     </row>
-    <row r="285">
+    <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="9"/>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
@@ -6083,7 +6086,7 @@
       <c r="E285" s="9"/>
       <c r="F285" s="9"/>
     </row>
-    <row r="286">
+    <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="8" t="s">
         <v>79</v>
       </c>
@@ -6093,7 +6096,7 @@
       <c r="E286" s="9"/>
       <c r="F286" s="9"/>
     </row>
-    <row r="287">
+    <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="9"/>
       <c r="B287" s="9" t="s">
         <v>10</v>
@@ -6105,7 +6108,7 @@
       <c r="E287" s="9"/>
       <c r="F287" s="9"/>
     </row>
-    <row r="288">
+    <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="9"/>
       <c r="B288" s="9" t="s">
         <v>12</v>
@@ -6117,7 +6120,7 @@
       <c r="E288" s="9"/>
       <c r="F288" s="9"/>
     </row>
-    <row r="289">
+    <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="11"/>
       <c r="B289" s="10" t="s">
         <v>2</v>
@@ -6131,7 +6134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="9"/>
       <c r="B290" s="10" t="s">
         <v>16</v>
@@ -6145,7 +6148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="9"/>
       <c r="B291" s="9" t="s">
         <v>19</v>
@@ -6157,7 +6160,7 @@
       <c r="E291" s="9"/>
       <c r="F291" s="9"/>
     </row>
-    <row r="292">
+    <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="9"/>
       <c r="B292" s="9" t="s">
         <v>20</v>
@@ -6169,7 +6172,7 @@
       <c r="E292" s="9"/>
       <c r="F292" s="9"/>
     </row>
-    <row r="293">
+    <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="9"/>
       <c r="B293" s="9" t="s">
         <v>22</v>
@@ -6181,7 +6184,7 @@
       <c r="E293" s="9"/>
       <c r="F293" s="9"/>
     </row>
-    <row r="294">
+    <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="9"/>
       <c r="B294" s="9" t="s">
         <v>23</v>
@@ -6193,7 +6196,7 @@
       <c r="E294" s="9"/>
       <c r="F294" s="9"/>
     </row>
-    <row r="295">
+    <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="9"/>
       <c r="B295" s="9" t="s">
         <v>25</v>
@@ -6205,7 +6208,7 @@
       <c r="E295" s="9"/>
       <c r="F295" s="9"/>
     </row>
-    <row r="296">
+    <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="9"/>
       <c r="B296" s="10" t="s">
         <v>26</v>
@@ -6217,7 +6220,7 @@
       </c>
       <c r="F296" s="9"/>
     </row>
-    <row r="297">
+    <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="9"/>
       <c r="B297" s="9" t="s">
         <v>28</v>
@@ -6229,7 +6232,7 @@
       <c r="E297" s="9"/>
       <c r="F297" s="9"/>
     </row>
-    <row r="298">
+    <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="9"/>
       <c r="B298" s="18" t="s">
         <v>30</v>
@@ -6241,7 +6244,7 @@
       <c r="E298" s="9"/>
       <c r="F298" s="9"/>
     </row>
-    <row r="299">
+    <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="9"/>
       <c r="B299" s="9"/>
       <c r="C299" s="11"/>
@@ -6249,7 +6252,7 @@
       <c r="E299" s="9"/>
       <c r="F299" s="9"/>
     </row>
-    <row r="300">
+    <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="8" t="s">
         <v>81</v>
       </c>
@@ -6259,7 +6262,7 @@
       <c r="E300" s="9"/>
       <c r="F300" s="9"/>
     </row>
-    <row r="301">
+    <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="9"/>
       <c r="B301" s="9" t="s">
         <v>10</v>
@@ -6271,7 +6274,7 @@
       <c r="E301" s="9"/>
       <c r="F301" s="9"/>
     </row>
-    <row r="302">
+    <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="9"/>
       <c r="B302" s="9" t="s">
         <v>12</v>
@@ -6283,7 +6286,7 @@
       <c r="E302" s="9"/>
       <c r="F302" s="9"/>
     </row>
-    <row r="303">
+    <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="10"/>
       <c r="B303" s="10" t="s">
         <v>2</v>
@@ -6295,7 +6298,7 @@
       <c r="E303" s="11"/>
       <c r="F303" s="11"/>
     </row>
-    <row r="304">
+    <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="9"/>
       <c r="B304" s="9" t="s">
         <v>19</v>
@@ -6307,7 +6310,7 @@
       <c r="E304" s="9"/>
       <c r="F304" s="9"/>
     </row>
-    <row r="305">
+    <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="9"/>
       <c r="B305" s="9" t="s">
         <v>20</v>
@@ -6319,7 +6322,7 @@
       <c r="E305" s="9"/>
       <c r="F305" s="9"/>
     </row>
-    <row r="306">
+    <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="9"/>
       <c r="B306" s="9" t="s">
         <v>22</v>
@@ -6331,7 +6334,7 @@
       <c r="E306" s="9"/>
       <c r="F306" s="9"/>
     </row>
-    <row r="307">
+    <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="9"/>
       <c r="B307" s="9" t="s">
         <v>23</v>
@@ -6343,7 +6346,7 @@
       <c r="E307" s="9"/>
       <c r="F307" s="9"/>
     </row>
-    <row r="308">
+    <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="9"/>
       <c r="B308" s="9" t="s">
         <v>25</v>
@@ -6355,7 +6358,7 @@
       <c r="E308" s="9"/>
       <c r="F308" s="9"/>
     </row>
-    <row r="309">
+    <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="9"/>
       <c r="B309" s="10" t="s">
         <v>26</v>
@@ -6367,7 +6370,7 @@
       </c>
       <c r="F309" s="9"/>
     </row>
-    <row r="310">
+    <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="9"/>
       <c r="B310" s="9" t="s">
         <v>28</v>
@@ -6379,7 +6382,7 @@
       <c r="E310" s="9"/>
       <c r="F310" s="9"/>
     </row>
-    <row r="311">
+    <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="9"/>
       <c r="B311" s="18" t="s">
         <v>30</v>
@@ -6391,7 +6394,7 @@
       <c r="E311" s="9"/>
       <c r="F311" s="9"/>
     </row>
-    <row r="312">
+    <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="9"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
@@ -6399,7 +6402,7 @@
       <c r="E312" s="9"/>
       <c r="F312" s="9"/>
     </row>
-    <row r="313">
+    <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="8" t="s">
         <v>83</v>
       </c>
@@ -6409,7 +6412,7 @@
       <c r="E313" s="9"/>
       <c r="F313" s="9"/>
     </row>
-    <row r="314">
+    <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="9"/>
       <c r="B314" s="9" t="s">
         <v>10</v>
@@ -6421,7 +6424,7 @@
       <c r="E314" s="9"/>
       <c r="F314" s="9"/>
     </row>
-    <row r="315">
+    <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="9"/>
       <c r="B315" s="9" t="s">
         <v>12</v>
@@ -6433,7 +6436,7 @@
       <c r="E315" s="9"/>
       <c r="F315" s="9"/>
     </row>
-    <row r="316">
+    <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="10"/>
       <c r="B316" s="10" t="s">
         <v>2</v>
@@ -6445,7 +6448,7 @@
       <c r="E316" s="11"/>
       <c r="F316" s="9"/>
     </row>
-    <row r="317">
+    <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="9"/>
       <c r="B317" s="9" t="s">
         <v>19</v>
@@ -6457,7 +6460,7 @@
       <c r="E317" s="9"/>
       <c r="F317" s="9"/>
     </row>
-    <row r="318">
+    <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="9"/>
       <c r="B318" s="9" t="s">
         <v>20</v>
@@ -6469,7 +6472,7 @@
       <c r="E318" s="9"/>
       <c r="F318" s="9"/>
     </row>
-    <row r="319">
+    <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="9"/>
       <c r="B319" s="9" t="s">
         <v>22</v>
@@ -6481,7 +6484,7 @@
       <c r="E319" s="9"/>
       <c r="F319" s="9"/>
     </row>
-    <row r="320">
+    <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="9"/>
       <c r="B320" s="9" t="s">
         <v>23</v>
@@ -6493,7 +6496,7 @@
       <c r="E320" s="9"/>
       <c r="F320" s="9"/>
     </row>
-    <row r="321">
+    <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="9"/>
       <c r="B321" s="9" t="s">
         <v>25</v>
@@ -6505,7 +6508,7 @@
       <c r="E321" s="9"/>
       <c r="F321" s="9"/>
     </row>
-    <row r="322">
+    <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="9"/>
       <c r="B322" s="10" t="s">
         <v>26</v>
@@ -6517,7 +6520,7 @@
       </c>
       <c r="F322" s="9"/>
     </row>
-    <row r="323">
+    <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="9"/>
       <c r="B323" s="9" t="s">
         <v>28</v>
@@ -6529,7 +6532,7 @@
       <c r="E323" s="9"/>
       <c r="F323" s="9"/>
     </row>
-    <row r="324">
+    <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="9"/>
       <c r="B324" s="18" t="s">
         <v>30</v>
@@ -6541,7 +6544,8 @@
       <c r="E324" s="9"/>
       <c r="F324" s="9"/>
     </row>
-    <row r="326">
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="8" t="s">
         <v>85</v>
       </c>
@@ -6552,7 +6556,7 @@
       <c r="F326" s="9"/>
       <c r="G326" s="9"/>
     </row>
-    <row r="327">
+    <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="9"/>
       <c r="B327" s="9" t="s">
         <v>10</v>
@@ -6565,7 +6569,7 @@
       <c r="F327" s="9"/>
       <c r="G327" s="9"/>
     </row>
-    <row r="328">
+    <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="9"/>
       <c r="B328" s="9" t="s">
         <v>12</v>
@@ -6578,7 +6582,7 @@
       <c r="F328" s="9"/>
       <c r="G328" s="9"/>
     </row>
-    <row r="329">
+    <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="11"/>
       <c r="B329" s="10" t="s">
         <v>2</v>
@@ -6593,7 +6597,7 @@
       </c>
       <c r="G329" s="9"/>
     </row>
-    <row r="330">
+    <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="9"/>
       <c r="B330" s="10" t="s">
         <v>16</v>
@@ -6608,7 +6612,7 @@
       </c>
       <c r="G330" s="9"/>
     </row>
-    <row r="331">
+    <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="9"/>
       <c r="B331" s="9" t="s">
         <v>19</v>
@@ -6621,7 +6625,7 @@
       <c r="F331" s="9"/>
       <c r="G331" s="9"/>
     </row>
-    <row r="332">
+    <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="9"/>
       <c r="B332" s="9" t="s">
         <v>20</v>
@@ -6634,7 +6638,7 @@
       <c r="F332" s="9"/>
       <c r="G332" s="9"/>
     </row>
-    <row r="333">
+    <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="9"/>
       <c r="B333" s="9" t="s">
         <v>22</v>
@@ -6647,7 +6651,7 @@
       <c r="F333" s="9"/>
       <c r="G333" s="9"/>
     </row>
-    <row r="334">
+    <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="9"/>
       <c r="B334" s="9" t="s">
         <v>23</v>
@@ -6660,7 +6664,7 @@
       <c r="F334" s="9"/>
       <c r="G334" s="9"/>
     </row>
-    <row r="335">
+    <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="9"/>
       <c r="B335" s="9" t="s">
         <v>25</v>
@@ -6673,7 +6677,7 @@
       <c r="F335" s="9"/>
       <c r="G335" s="9"/>
     </row>
-    <row r="336">
+    <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="9"/>
       <c r="B336" s="10" t="s">
         <v>26</v>
@@ -6686,7 +6690,7 @@
       <c r="F336" s="9"/>
       <c r="G336" s="9"/>
     </row>
-    <row r="337">
+    <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="9"/>
       <c r="B337" s="9" t="s">
         <v>28</v>
@@ -6699,7 +6703,7 @@
       <c r="F337" s="9"/>
       <c r="G337" s="9"/>
     </row>
-    <row r="338">
+    <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="9"/>
       <c r="B338" s="18" t="s">
         <v>30</v>
@@ -6712,7 +6716,7 @@
       <c r="F338" s="9"/>
       <c r="G338" s="9"/>
     </row>
-    <row r="339">
+    <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="9"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
@@ -6721,7 +6725,7 @@
       <c r="F339" s="9"/>
       <c r="G339" s="9"/>
     </row>
-    <row r="340">
+    <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="8" t="s">
         <v>88</v>
       </c>
@@ -6732,7 +6736,7 @@
       <c r="F340" s="9"/>
       <c r="G340" s="9"/>
     </row>
-    <row r="341">
+    <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="9"/>
       <c r="B341" s="9" t="s">
         <v>10</v>
@@ -6745,7 +6749,7 @@
       <c r="F341" s="9"/>
       <c r="G341" s="9"/>
     </row>
-    <row r="342">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="9"/>
       <c r="B342" s="9" t="s">
         <v>12</v>
@@ -6758,7 +6762,7 @@
       <c r="F342" s="9"/>
       <c r="G342" s="9"/>
     </row>
-    <row r="343">
+    <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="11"/>
       <c r="B343" s="10" t="s">
         <v>2</v>
@@ -6773,7 +6777,7 @@
       </c>
       <c r="G343" s="9"/>
     </row>
-    <row r="344">
+    <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="9"/>
       <c r="B344" s="10" t="s">
         <v>16</v>
@@ -6788,7 +6792,7 @@
       </c>
       <c r="G344" s="9"/>
     </row>
-    <row r="345">
+    <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="9"/>
       <c r="B345" s="9" t="s">
         <v>19</v>
@@ -6801,7 +6805,7 @@
       <c r="F345" s="9"/>
       <c r="G345" s="9"/>
     </row>
-    <row r="346">
+    <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="9"/>
       <c r="B346" s="9" t="s">
         <v>20</v>
@@ -6814,7 +6818,7 @@
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
     </row>
-    <row r="347">
+    <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="9"/>
       <c r="B347" s="9" t="s">
         <v>22</v>
@@ -6827,7 +6831,7 @@
       <c r="F347" s="9"/>
       <c r="G347" s="9"/>
     </row>
-    <row r="348">
+    <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="9"/>
       <c r="B348" s="9" t="s">
         <v>23</v>
@@ -6840,7 +6844,7 @@
       <c r="F348" s="9"/>
       <c r="G348" s="9"/>
     </row>
-    <row r="349">
+    <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="9"/>
       <c r="B349" s="9" t="s">
         <v>25</v>
@@ -6853,7 +6857,7 @@
       <c r="F349" s="9"/>
       <c r="G349" s="9"/>
     </row>
-    <row r="350">
+    <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="9"/>
       <c r="B350" s="10" t="s">
         <v>26</v>
@@ -6866,7 +6870,7 @@
       <c r="F350" s="9"/>
       <c r="G350" s="9"/>
     </row>
-    <row r="351">
+    <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="9"/>
       <c r="B351" s="9" t="s">
         <v>28</v>
@@ -6879,7 +6883,7 @@
       <c r="F351" s="9"/>
       <c r="G351" s="9"/>
     </row>
-    <row r="352">
+    <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="9"/>
       <c r="B352" s="18" t="s">
         <v>30</v>
@@ -6892,7 +6896,7 @@
       <c r="F352" s="9"/>
       <c r="G352" s="9"/>
     </row>
-    <row r="353">
+    <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="9"/>
       <c r="B353" s="9"/>
       <c r="C353" s="11"/>
@@ -6901,7 +6905,7 @@
       <c r="F353" s="9"/>
       <c r="G353" s="9"/>
     </row>
-    <row r="354">
+    <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="8" t="s">
         <v>90</v>
       </c>
@@ -6912,7 +6916,7 @@
       <c r="F354" s="9"/>
       <c r="G354" s="9"/>
     </row>
-    <row r="355">
+    <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="9"/>
       <c r="B355" s="9" t="s">
         <v>10</v>
@@ -6925,7 +6929,7 @@
       <c r="F355" s="9"/>
       <c r="G355" s="9"/>
     </row>
-    <row r="356">
+    <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="9"/>
       <c r="B356" s="9" t="s">
         <v>12</v>
@@ -6938,7 +6942,7 @@
       <c r="F356" s="9"/>
       <c r="G356" s="9"/>
     </row>
-    <row r="357">
+    <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="10"/>
       <c r="B357" s="10" t="s">
         <v>2</v>
@@ -6951,7 +6955,7 @@
       <c r="F357" s="11"/>
       <c r="G357" s="9"/>
     </row>
-    <row r="358">
+    <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="9"/>
       <c r="B358" s="9" t="s">
         <v>19</v>
@@ -6964,7 +6968,7 @@
       <c r="F358" s="9"/>
       <c r="G358" s="9"/>
     </row>
-    <row r="359">
+    <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="9"/>
       <c r="B359" s="9" t="s">
         <v>20</v>
@@ -6977,7 +6981,7 @@
       <c r="F359" s="9"/>
       <c r="G359" s="9"/>
     </row>
-    <row r="360">
+    <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="9"/>
       <c r="B360" s="9" t="s">
         <v>22</v>
@@ -6990,7 +6994,7 @@
       <c r="F360" s="9"/>
       <c r="G360" s="9"/>
     </row>
-    <row r="361">
+    <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="9"/>
       <c r="B361" s="9" t="s">
         <v>23</v>
@@ -7003,7 +7007,7 @@
       <c r="F361" s="9"/>
       <c r="G361" s="9"/>
     </row>
-    <row r="362">
+    <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="9"/>
       <c r="B362" s="9" t="s">
         <v>25</v>
@@ -7016,7 +7020,7 @@
       <c r="F362" s="9"/>
       <c r="G362" s="9"/>
     </row>
-    <row r="363">
+    <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="9"/>
       <c r="B363" s="10" t="s">
         <v>26</v>
@@ -7029,7 +7033,7 @@
       <c r="F363" s="9"/>
       <c r="G363" s="9"/>
     </row>
-    <row r="364">
+    <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="9"/>
       <c r="B364" s="9" t="s">
         <v>28</v>
@@ -7042,7 +7046,7 @@
       <c r="F364" s="9"/>
       <c r="G364" s="9"/>
     </row>
-    <row r="365">
+    <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="9"/>
       <c r="B365" s="18" t="s">
         <v>30</v>
@@ -7055,7 +7059,7 @@
       <c r="F365" s="9"/>
       <c r="G365" s="9"/>
     </row>
-    <row r="366">
+    <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="9"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
@@ -7064,7 +7068,7 @@
       <c r="F366" s="9"/>
       <c r="G366" s="9"/>
     </row>
-    <row r="367">
+    <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="8" t="s">
         <v>92</v>
       </c>
@@ -7075,7 +7079,7 @@
       <c r="F367" s="9"/>
       <c r="G367" s="9"/>
     </row>
-    <row r="368">
+    <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="9"/>
       <c r="B368" s="9" t="s">
         <v>10</v>
@@ -7088,7 +7092,7 @@
       <c r="F368" s="9"/>
       <c r="G368" s="9"/>
     </row>
-    <row r="369">
+    <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="9"/>
       <c r="B369" s="9" t="s">
         <v>12</v>
@@ -7101,7 +7105,7 @@
       <c r="F369" s="9"/>
       <c r="G369" s="9"/>
     </row>
-    <row r="370">
+    <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="10"/>
       <c r="B370" s="10" t="s">
         <v>2</v>
@@ -7114,7 +7118,7 @@
       <c r="F370" s="9"/>
       <c r="G370" s="9"/>
     </row>
-    <row r="371">
+    <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="9"/>
       <c r="B371" s="9" t="s">
         <v>19</v>
@@ -7127,7 +7131,7 @@
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
     </row>
-    <row r="372">
+    <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="9"/>
       <c r="B372" s="9" t="s">
         <v>20</v>
@@ -7140,7 +7144,7 @@
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
     </row>
-    <row r="373">
+    <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="9"/>
       <c r="B373" s="9" t="s">
         <v>22</v>
@@ -7153,7 +7157,7 @@
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
     </row>
-    <row r="374">
+    <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="9"/>
       <c r="B374" s="9" t="s">
         <v>23</v>
@@ -7166,7 +7170,7 @@
       <c r="F374" s="9"/>
       <c r="G374" s="9"/>
     </row>
-    <row r="375">
+    <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="9"/>
       <c r="B375" s="9" t="s">
         <v>25</v>
@@ -7179,7 +7183,7 @@
       <c r="F375" s="9"/>
       <c r="G375" s="9"/>
     </row>
-    <row r="376">
+    <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="9"/>
       <c r="B376" s="10" t="s">
         <v>26</v>
@@ -7192,7 +7196,7 @@
       <c r="F376" s="9"/>
       <c r="G376" s="9"/>
     </row>
-    <row r="377">
+    <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="9"/>
       <c r="B377" s="9" t="s">
         <v>28</v>
@@ -7205,7 +7209,7 @@
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
     </row>
-    <row r="378">
+    <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="9"/>
       <c r="B378" s="18" t="s">
         <v>30</v>
@@ -7218,7 +7222,8 @@
       <c r="F378" s="9"/>
       <c r="G378" s="9"/>
     </row>
-    <row r="380">
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="8" t="s">
         <v>94</v>
       </c>
@@ -7228,7 +7233,7 @@
       <c r="E380" s="9"/>
       <c r="F380" s="9"/>
     </row>
-    <row r="381">
+    <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="9"/>
       <c r="B381" s="9" t="s">
         <v>10</v>
@@ -7240,7 +7245,7 @@
       <c r="E381" s="9"/>
       <c r="F381" s="9"/>
     </row>
-    <row r="382">
+    <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="9"/>
       <c r="B382" s="9" t="s">
         <v>12</v>
@@ -7252,7 +7257,7 @@
       <c r="E382" s="9"/>
       <c r="F382" s="9"/>
     </row>
-    <row r="383">
+    <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="11"/>
       <c r="B383" s="10" t="s">
         <v>2</v>
@@ -7266,7 +7271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="9"/>
       <c r="B384" s="10" t="s">
         <v>16</v>
@@ -7280,7 +7285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="9"/>
       <c r="B385" s="9" t="s">
         <v>19</v>
@@ -7292,7 +7297,7 @@
       <c r="E385" s="9"/>
       <c r="F385" s="9"/>
     </row>
-    <row r="386">
+    <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="9"/>
       <c r="B386" s="9" t="s">
         <v>20</v>
@@ -7304,7 +7309,7 @@
       <c r="E386" s="9"/>
       <c r="F386" s="9"/>
     </row>
-    <row r="387">
+    <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="9"/>
       <c r="B387" s="9" t="s">
         <v>22</v>
@@ -7316,7 +7321,7 @@
       <c r="E387" s="9"/>
       <c r="F387" s="9"/>
     </row>
-    <row r="388">
+    <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="9"/>
       <c r="B388" s="9" t="s">
         <v>23</v>
@@ -7328,7 +7333,7 @@
       <c r="E388" s="9"/>
       <c r="F388" s="9"/>
     </row>
-    <row r="389">
+    <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="9"/>
       <c r="B389" s="9" t="s">
         <v>25</v>
@@ -7340,7 +7345,7 @@
       <c r="E389" s="9"/>
       <c r="F389" s="9"/>
     </row>
-    <row r="390">
+    <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="9"/>
       <c r="B390" s="10" t="s">
         <v>26</v>
@@ -7352,7 +7357,7 @@
       </c>
       <c r="F390" s="9"/>
     </row>
-    <row r="391">
+    <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="9"/>
       <c r="B391" s="9" t="s">
         <v>28</v>
@@ -7364,7 +7369,7 @@
       <c r="E391" s="9"/>
       <c r="F391" s="9"/>
     </row>
-    <row r="392">
+    <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="9"/>
       <c r="B392" s="18" t="s">
         <v>30</v>
@@ -7376,7 +7381,7 @@
       <c r="E392" s="9"/>
       <c r="F392" s="9"/>
     </row>
-    <row r="393">
+    <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="9"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
@@ -7384,7 +7389,7 @@
       <c r="E393" s="9"/>
       <c r="F393" s="9"/>
     </row>
-    <row r="394">
+    <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="8" t="s">
         <v>97</v>
       </c>
@@ -7394,7 +7399,7 @@
       <c r="E394" s="9"/>
       <c r="F394" s="9"/>
     </row>
-    <row r="395">
+    <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="9"/>
       <c r="B395" s="9" t="s">
         <v>10</v>
@@ -7406,7 +7411,7 @@
       <c r="E395" s="9"/>
       <c r="F395" s="9"/>
     </row>
-    <row r="396">
+    <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="9"/>
       <c r="B396" s="9" t="s">
         <v>12</v>
@@ -7418,7 +7423,7 @@
       <c r="E396" s="9"/>
       <c r="F396" s="9"/>
     </row>
-    <row r="397">
+    <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="11"/>
       <c r="B397" s="10" t="s">
         <v>2</v>
@@ -7432,7 +7437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="9"/>
       <c r="B398" s="10" t="s">
         <v>16</v>
@@ -7446,7 +7451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="9"/>
       <c r="B399" s="9" t="s">
         <v>19</v>
@@ -7458,7 +7463,7 @@
       <c r="E399" s="9"/>
       <c r="F399" s="9"/>
     </row>
-    <row r="400">
+    <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="9"/>
       <c r="B400" s="9" t="s">
         <v>20</v>
@@ -7470,7 +7475,7 @@
       <c r="E400" s="9"/>
       <c r="F400" s="9"/>
     </row>
-    <row r="401">
+    <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="9"/>
       <c r="B401" s="9" t="s">
         <v>22</v>
@@ -7482,7 +7487,7 @@
       <c r="E401" s="9"/>
       <c r="F401" s="9"/>
     </row>
-    <row r="402">
+    <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="9"/>
       <c r="B402" s="9" t="s">
         <v>23</v>
@@ -7494,7 +7499,7 @@
       <c r="E402" s="9"/>
       <c r="F402" s="9"/>
     </row>
-    <row r="403">
+    <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="9"/>
       <c r="B403" s="9" t="s">
         <v>25</v>
@@ -7506,7 +7511,7 @@
       <c r="E403" s="9"/>
       <c r="F403" s="9"/>
     </row>
-    <row r="404">
+    <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="9"/>
       <c r="B404" s="10" t="s">
         <v>26</v>
@@ -7518,7 +7523,7 @@
       </c>
       <c r="F404" s="9"/>
     </row>
-    <row r="405">
+    <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="9"/>
       <c r="B405" s="9" t="s">
         <v>28</v>
@@ -7530,7 +7535,7 @@
       <c r="E405" s="9"/>
       <c r="F405" s="9"/>
     </row>
-    <row r="406">
+    <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="9"/>
       <c r="B406" s="18" t="s">
         <v>30</v>
@@ -7542,7 +7547,7 @@
       <c r="E406" s="9"/>
       <c r="F406" s="9"/>
     </row>
-    <row r="407">
+    <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="9"/>
       <c r="B407" s="9"/>
       <c r="C407" s="11"/>
@@ -7550,7 +7555,7 @@
       <c r="E407" s="9"/>
       <c r="F407" s="9"/>
     </row>
-    <row r="408">
+    <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="8" t="s">
         <v>99</v>
       </c>
@@ -7560,7 +7565,7 @@
       <c r="E408" s="9"/>
       <c r="F408" s="9"/>
     </row>
-    <row r="409">
+    <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="9"/>
       <c r="B409" s="9" t="s">
         <v>10</v>
@@ -7572,7 +7577,7 @@
       <c r="E409" s="9"/>
       <c r="F409" s="9"/>
     </row>
-    <row r="410">
+    <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="9"/>
       <c r="B410" s="9" t="s">
         <v>12</v>
@@ -7584,7 +7589,7 @@
       <c r="E410" s="9"/>
       <c r="F410" s="9"/>
     </row>
-    <row r="411">
+    <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>2</v>
@@ -7596,7 +7601,7 @@
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
     </row>
-    <row r="412">
+    <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="9"/>
       <c r="B412" s="9" t="s">
         <v>19</v>
@@ -7608,7 +7613,7 @@
       <c r="E412" s="9"/>
       <c r="F412" s="9"/>
     </row>
-    <row r="413">
+    <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="9"/>
       <c r="B413" s="9" t="s">
         <v>20</v>
@@ -7620,7 +7625,7 @@
       <c r="E413" s="9"/>
       <c r="F413" s="9"/>
     </row>
-    <row r="414">
+    <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="9"/>
       <c r="B414" s="9" t="s">
         <v>22</v>
@@ -7632,7 +7637,7 @@
       <c r="E414" s="9"/>
       <c r="F414" s="9"/>
     </row>
-    <row r="415">
+    <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="9"/>
       <c r="B415" s="9" t="s">
         <v>23</v>
@@ -7644,7 +7649,7 @@
       <c r="E415" s="9"/>
       <c r="F415" s="9"/>
     </row>
-    <row r="416">
+    <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="9"/>
       <c r="B416" s="9" t="s">
         <v>25</v>
@@ -7656,7 +7661,7 @@
       <c r="E416" s="9"/>
       <c r="F416" s="9"/>
     </row>
-    <row r="417">
+    <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="9"/>
       <c r="B417" s="10" t="s">
         <v>26</v>
@@ -7668,7 +7673,7 @@
       </c>
       <c r="F417" s="9"/>
     </row>
-    <row r="418">
+    <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="9"/>
       <c r="B418" s="9" t="s">
         <v>28</v>
@@ -7680,7 +7685,7 @@
       <c r="E418" s="9"/>
       <c r="F418" s="9"/>
     </row>
-    <row r="419">
+    <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="9"/>
       <c r="B419" s="18" t="s">
         <v>30</v>
@@ -7692,7 +7697,7 @@
       <c r="E419" s="9"/>
       <c r="F419" s="9"/>
     </row>
-    <row r="420">
+    <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="9"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
@@ -7700,7 +7705,7 @@
       <c r="E420" s="9"/>
       <c r="F420" s="9"/>
     </row>
-    <row r="421">
+    <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="8" t="s">
         <v>101</v>
       </c>
@@ -7710,7 +7715,7 @@
       <c r="E421" s="9"/>
       <c r="F421" s="9"/>
     </row>
-    <row r="422">
+    <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="9"/>
       <c r="B422" s="9" t="s">
         <v>10</v>
@@ -7722,7 +7727,7 @@
       <c r="E422" s="9"/>
       <c r="F422" s="9"/>
     </row>
-    <row r="423">
+    <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="9"/>
       <c r="B423" s="9" t="s">
         <v>12</v>
@@ -7734,7 +7739,7 @@
       <c r="E423" s="9"/>
       <c r="F423" s="9"/>
     </row>
-    <row r="424">
+    <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="10"/>
       <c r="B424" s="10" t="s">
         <v>2</v>
@@ -7746,7 +7751,7 @@
       <c r="E424" s="11"/>
       <c r="F424" s="9"/>
     </row>
-    <row r="425">
+    <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="9"/>
       <c r="B425" s="9" t="s">
         <v>19</v>
@@ -7758,7 +7763,7 @@
       <c r="E425" s="9"/>
       <c r="F425" s="9"/>
     </row>
-    <row r="426">
+    <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="9"/>
       <c r="B426" s="9" t="s">
         <v>20</v>
@@ -7770,7 +7775,7 @@
       <c r="E426" s="9"/>
       <c r="F426" s="9"/>
     </row>
-    <row r="427">
+    <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="9"/>
       <c r="B427" s="9" t="s">
         <v>22</v>
@@ -7782,7 +7787,7 @@
       <c r="E427" s="9"/>
       <c r="F427" s="9"/>
     </row>
-    <row r="428">
+    <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="9"/>
       <c r="B428" s="9" t="s">
         <v>23</v>
@@ -7794,7 +7799,7 @@
       <c r="E428" s="9"/>
       <c r="F428" s="9"/>
     </row>
-    <row r="429">
+    <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="9"/>
       <c r="B429" s="9" t="s">
         <v>25</v>
@@ -7806,7 +7811,7 @@
       <c r="E429" s="9"/>
       <c r="F429" s="9"/>
     </row>
-    <row r="430">
+    <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="9"/>
       <c r="B430" s="10" t="s">
         <v>26</v>
@@ -7818,7 +7823,7 @@
       </c>
       <c r="F430" s="9"/>
     </row>
-    <row r="431">
+    <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="9"/>
       <c r="B431" s="9" t="s">
         <v>28</v>
@@ -7830,7 +7835,7 @@
       <c r="E431" s="9"/>
       <c r="F431" s="9"/>
     </row>
-    <row r="432">
+    <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="9"/>
       <c r="B432" s="18" t="s">
         <v>30</v>
@@ -7842,7 +7847,8 @@
       <c r="E432" s="9"/>
       <c r="F432" s="9"/>
     </row>
-    <row r="434">
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="8" t="s">
         <v>103</v>
       </c>
@@ -7852,7 +7858,7 @@
       <c r="E434" s="9"/>
       <c r="F434" s="9"/>
     </row>
-    <row r="435">
+    <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="9"/>
       <c r="B435" s="9" t="s">
         <v>10</v>
@@ -7864,7 +7870,7 @@
       <c r="E435" s="9"/>
       <c r="F435" s="9"/>
     </row>
-    <row r="436">
+    <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="9"/>
       <c r="B436" s="9" t="s">
         <v>12</v>
@@ -7876,7 +7882,7 @@
       <c r="E436" s="9"/>
       <c r="F436" s="9"/>
     </row>
-    <row r="437">
+    <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="11"/>
       <c r="B437" s="10" t="s">
         <v>2</v>
@@ -7890,7 +7896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="9"/>
       <c r="B438" s="10" t="s">
         <v>16</v>
@@ -7904,7 +7910,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="9"/>
       <c r="B439" s="9" t="s">
         <v>19</v>
@@ -7916,7 +7922,7 @@
       <c r="E439" s="9"/>
       <c r="F439" s="9"/>
     </row>
-    <row r="440">
+    <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="9"/>
       <c r="B440" s="9" t="s">
         <v>20</v>
@@ -7928,7 +7934,7 @@
       <c r="E440" s="9"/>
       <c r="F440" s="9"/>
     </row>
-    <row r="441">
+    <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="9"/>
       <c r="B441" s="9" t="s">
         <v>22</v>
@@ -7940,7 +7946,7 @@
       <c r="E441" s="9"/>
       <c r="F441" s="9"/>
     </row>
-    <row r="442">
+    <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="9"/>
       <c r="B442" s="9" t="s">
         <v>23</v>
@@ -7952,7 +7958,7 @@
       <c r="E442" s="9"/>
       <c r="F442" s="9"/>
     </row>
-    <row r="443">
+    <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="9"/>
       <c r="B443" s="9" t="s">
         <v>25</v>
@@ -7964,7 +7970,7 @@
       <c r="E443" s="9"/>
       <c r="F443" s="9"/>
     </row>
-    <row r="444">
+    <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="9"/>
       <c r="B444" s="10" t="s">
         <v>26</v>
@@ -7976,7 +7982,7 @@
       </c>
       <c r="F444" s="9"/>
     </row>
-    <row r="445">
+    <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="9"/>
       <c r="B445" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7994,7 @@
       <c r="E445" s="9"/>
       <c r="F445" s="9"/>
     </row>
-    <row r="446">
+    <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="9"/>
       <c r="B446" s="18" t="s">
         <v>30</v>
@@ -8000,7 +8006,7 @@
       <c r="E446" s="9"/>
       <c r="F446" s="9"/>
     </row>
-    <row r="447">
+    <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="9"/>
       <c r="B447" s="9"/>
       <c r="C447" s="9"/>
@@ -8008,7 +8014,7 @@
       <c r="E447" s="9"/>
       <c r="F447" s="9"/>
     </row>
-    <row r="448">
+    <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="8" t="s">
         <v>105</v>
       </c>
@@ -8018,7 +8024,7 @@
       <c r="E448" s="9"/>
       <c r="F448" s="9"/>
     </row>
-    <row r="449">
+    <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="9"/>
       <c r="B449" s="9" t="s">
         <v>10</v>
@@ -8030,7 +8036,7 @@
       <c r="E449" s="9"/>
       <c r="F449" s="9"/>
     </row>
-    <row r="450">
+    <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="9"/>
       <c r="B450" s="9" t="s">
         <v>12</v>
@@ -8042,7 +8048,7 @@
       <c r="E450" s="9"/>
       <c r="F450" s="9"/>
     </row>
-    <row r="451">
+    <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="11"/>
       <c r="B451" s="10" t="s">
         <v>2</v>
@@ -8056,7 +8062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="9"/>
       <c r="B452" s="10" t="s">
         <v>16</v>
@@ -8070,7 +8076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="9"/>
       <c r="B453" s="9" t="s">
         <v>19</v>
@@ -8082,7 +8088,7 @@
       <c r="E453" s="9"/>
       <c r="F453" s="9"/>
     </row>
-    <row r="454">
+    <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="9"/>
       <c r="B454" s="9" t="s">
         <v>20</v>
@@ -8094,7 +8100,7 @@
       <c r="E454" s="9"/>
       <c r="F454" s="9"/>
     </row>
-    <row r="455">
+    <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="9"/>
       <c r="B455" s="9" t="s">
         <v>22</v>
@@ -8106,7 +8112,7 @@
       <c r="E455" s="9"/>
       <c r="F455" s="9"/>
     </row>
-    <row r="456">
+    <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="9"/>
       <c r="B456" s="9" t="s">
         <v>23</v>
@@ -8118,7 +8124,7 @@
       <c r="E456" s="9"/>
       <c r="F456" s="9"/>
     </row>
-    <row r="457">
+    <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="9"/>
       <c r="B457" s="9" t="s">
         <v>25</v>
@@ -8130,7 +8136,7 @@
       <c r="E457" s="9"/>
       <c r="F457" s="9"/>
     </row>
-    <row r="458">
+    <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="9"/>
       <c r="B458" s="10" t="s">
         <v>26</v>
@@ -8142,7 +8148,7 @@
       </c>
       <c r="F458" s="9"/>
     </row>
-    <row r="459">
+    <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="9"/>
       <c r="B459" s="9" t="s">
         <v>28</v>
@@ -8154,7 +8160,7 @@
       <c r="E459" s="9"/>
       <c r="F459" s="9"/>
     </row>
-    <row r="460">
+    <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="9"/>
       <c r="B460" s="18" t="s">
         <v>30</v>
@@ -8166,7 +8172,7 @@
       <c r="E460" s="9"/>
       <c r="F460" s="9"/>
     </row>
-    <row r="461">
+    <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="9"/>
       <c r="B461" s="9"/>
       <c r="C461" s="11"/>
@@ -8174,7 +8180,7 @@
       <c r="E461" s="9"/>
       <c r="F461" s="9"/>
     </row>
-    <row r="462">
+    <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="8" t="s">
         <v>107</v>
       </c>
@@ -8184,7 +8190,7 @@
       <c r="E462" s="9"/>
       <c r="F462" s="9"/>
     </row>
-    <row r="463">
+    <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="9"/>
       <c r="B463" s="9" t="s">
         <v>10</v>
@@ -8196,7 +8202,7 @@
       <c r="E463" s="9"/>
       <c r="F463" s="9"/>
     </row>
-    <row r="464">
+    <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="9"/>
       <c r="B464" s="9" t="s">
         <v>12</v>
@@ -8208,7 +8214,7 @@
       <c r="E464" s="9"/>
       <c r="F464" s="9"/>
     </row>
-    <row r="465">
+    <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="10"/>
       <c r="B465" s="10" t="s">
         <v>2</v>
@@ -8220,7 +8226,7 @@
       <c r="E465" s="11"/>
       <c r="F465" s="11"/>
     </row>
-    <row r="466">
+    <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="9"/>
       <c r="B466" s="9" t="s">
         <v>19</v>
@@ -8232,7 +8238,7 @@
       <c r="E466" s="9"/>
       <c r="F466" s="9"/>
     </row>
-    <row r="467">
+    <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="9"/>
       <c r="B467" s="9" t="s">
         <v>20</v>
@@ -8244,7 +8250,7 @@
       <c r="E467" s="9"/>
       <c r="F467" s="9"/>
     </row>
-    <row r="468">
+    <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="9"/>
       <c r="B468" s="9" t="s">
         <v>22</v>
@@ -8256,7 +8262,7 @@
       <c r="E468" s="9"/>
       <c r="F468" s="9"/>
     </row>
-    <row r="469">
+    <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="9"/>
       <c r="B469" s="9" t="s">
         <v>23</v>
@@ -8268,7 +8274,7 @@
       <c r="E469" s="9"/>
       <c r="F469" s="9"/>
     </row>
-    <row r="470">
+    <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="9"/>
       <c r="B470" s="9" t="s">
         <v>25</v>
@@ -8280,7 +8286,7 @@
       <c r="E470" s="9"/>
       <c r="F470" s="9"/>
     </row>
-    <row r="471">
+    <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="9"/>
       <c r="B471" s="10" t="s">
         <v>26</v>
@@ -8292,7 +8298,7 @@
       </c>
       <c r="F471" s="9"/>
     </row>
-    <row r="472">
+    <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="9"/>
       <c r="B472" s="9" t="s">
         <v>28</v>
@@ -8304,7 +8310,7 @@
       <c r="E472" s="9"/>
       <c r="F472" s="9"/>
     </row>
-    <row r="473">
+    <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="9"/>
       <c r="B473" s="18" t="s">
         <v>30</v>
@@ -8316,7 +8322,7 @@
       <c r="E473" s="9"/>
       <c r="F473" s="9"/>
     </row>
-    <row r="474">
+    <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="9"/>
       <c r="B474" s="9"/>
       <c r="C474" s="9"/>
@@ -8324,7 +8330,7 @@
       <c r="E474" s="9"/>
       <c r="F474" s="9"/>
     </row>
-    <row r="475">
+    <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="8" t="s">
         <v>109</v>
       </c>
@@ -8334,7 +8340,7 @@
       <c r="E475" s="9"/>
       <c r="F475" s="9"/>
     </row>
-    <row r="476">
+    <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="9"/>
       <c r="B476" s="9" t="s">
         <v>10</v>
@@ -8346,7 +8352,7 @@
       <c r="E476" s="9"/>
       <c r="F476" s="9"/>
     </row>
-    <row r="477">
+    <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="9"/>
       <c r="B477" s="9" t="s">
         <v>12</v>
@@ -8358,7 +8364,7 @@
       <c r="E477" s="9"/>
       <c r="F477" s="9"/>
     </row>
-    <row r="478">
+    <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="10"/>
       <c r="B478" s="10" t="s">
         <v>2</v>
@@ -8370,7 +8376,7 @@
       <c r="E478" s="11"/>
       <c r="F478" s="9"/>
     </row>
-    <row r="479">
+    <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="9"/>
       <c r="B479" s="9" t="s">
         <v>19</v>
@@ -8382,7 +8388,7 @@
       <c r="E479" s="9"/>
       <c r="F479" s="9"/>
     </row>
-    <row r="480">
+    <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="9"/>
       <c r="B480" s="9" t="s">
         <v>20</v>
@@ -8394,7 +8400,7 @@
       <c r="E480" s="9"/>
       <c r="F480" s="9"/>
     </row>
-    <row r="481">
+    <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="9"/>
       <c r="B481" s="9" t="s">
         <v>22</v>
@@ -8406,7 +8412,7 @@
       <c r="E481" s="9"/>
       <c r="F481" s="9"/>
     </row>
-    <row r="482">
+    <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="9"/>
       <c r="B482" s="9" t="s">
         <v>23</v>
@@ -8418,7 +8424,7 @@
       <c r="E482" s="9"/>
       <c r="F482" s="9"/>
     </row>
-    <row r="483">
+    <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="9"/>
       <c r="B483" s="9" t="s">
         <v>25</v>
@@ -8430,7 +8436,7 @@
       <c r="E483" s="9"/>
       <c r="F483" s="9"/>
     </row>
-    <row r="484">
+    <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="9"/>
       <c r="B484" s="10" t="s">
         <v>26</v>
@@ -8442,7 +8448,7 @@
       </c>
       <c r="F484" s="9"/>
     </row>
-    <row r="485">
+    <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="9"/>
       <c r="B485" s="9" t="s">
         <v>28</v>
@@ -8454,7 +8460,7 @@
       <c r="E485" s="9"/>
       <c r="F485" s="9"/>
     </row>
-    <row r="486">
+    <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="9"/>
       <c r="B486" s="18" t="s">
         <v>30</v>
@@ -8466,7 +8472,8 @@
       <c r="E486" s="9"/>
       <c r="F486" s="9"/>
     </row>
-    <row r="488">
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="8" t="s">
         <v>111</v>
       </c>
@@ -8477,7 +8484,7 @@
       <c r="F488" s="9"/>
       <c r="G488" s="9"/>
     </row>
-    <row r="489">
+    <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="9"/>
       <c r="B489" s="9" t="s">
         <v>10</v>
@@ -8490,7 +8497,7 @@
       <c r="F489" s="9"/>
       <c r="G489" s="9"/>
     </row>
-    <row r="490">
+    <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="9"/>
       <c r="B490" s="9" t="s">
         <v>12</v>
@@ -8503,7 +8510,7 @@
       <c r="F490" s="9"/>
       <c r="G490" s="9"/>
     </row>
-    <row r="491">
+    <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="11"/>
       <c r="B491" s="10" t="s">
         <v>2</v>
@@ -8518,7 +8525,7 @@
       </c>
       <c r="G491" s="9"/>
     </row>
-    <row r="492">
+    <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="9"/>
       <c r="B492" s="10" t="s">
         <v>16</v>
@@ -8533,7 +8540,7 @@
       </c>
       <c r="G492" s="9"/>
     </row>
-    <row r="493">
+    <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="9"/>
       <c r="B493" s="9" t="s">
         <v>19</v>
@@ -8546,7 +8553,7 @@
       <c r="F493" s="9"/>
       <c r="G493" s="9"/>
     </row>
-    <row r="494">
+    <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="9"/>
       <c r="B494" s="9" t="s">
         <v>20</v>
@@ -8559,7 +8566,7 @@
       <c r="F494" s="9"/>
       <c r="G494" s="9"/>
     </row>
-    <row r="495">
+    <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="9"/>
       <c r="B495" s="9" t="s">
         <v>22</v>
@@ -8572,7 +8579,7 @@
       <c r="F495" s="9"/>
       <c r="G495" s="9"/>
     </row>
-    <row r="496">
+    <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="9"/>
       <c r="B496" s="9" t="s">
         <v>23</v>
@@ -8585,7 +8592,7 @@
       <c r="F496" s="9"/>
       <c r="G496" s="9"/>
     </row>
-    <row r="497">
+    <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="9"/>
       <c r="B497" s="9" t="s">
         <v>25</v>
@@ -8598,7 +8605,7 @@
       <c r="F497" s="9"/>
       <c r="G497" s="9"/>
     </row>
-    <row r="498">
+    <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="9"/>
       <c r="B498" s="10" t="s">
         <v>26</v>
@@ -8611,7 +8618,7 @@
       <c r="F498" s="9"/>
       <c r="G498" s="9"/>
     </row>
-    <row r="499">
+    <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="9"/>
       <c r="B499" s="9" t="s">
         <v>28</v>
@@ -8624,7 +8631,7 @@
       <c r="F499" s="9"/>
       <c r="G499" s="9"/>
     </row>
-    <row r="500">
+    <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="9"/>
       <c r="B500" s="18" t="s">
         <v>30</v>
@@ -8637,7 +8644,7 @@
       <c r="F500" s="9"/>
       <c r="G500" s="9"/>
     </row>
-    <row r="501">
+    <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="9"/>
       <c r="B501" s="9"/>
       <c r="C501" s="9"/>
@@ -8646,7 +8653,7 @@
       <c r="F501" s="9"/>
       <c r="G501" s="9"/>
     </row>
-    <row r="502">
+    <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="8" t="s">
         <v>114</v>
       </c>
@@ -8657,7 +8664,7 @@
       <c r="F502" s="9"/>
       <c r="G502" s="9"/>
     </row>
-    <row r="503">
+    <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="9"/>
       <c r="B503" s="9" t="s">
         <v>10</v>
@@ -8670,7 +8677,7 @@
       <c r="F503" s="9"/>
       <c r="G503" s="9"/>
     </row>
-    <row r="504">
+    <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="9"/>
       <c r="B504" s="9" t="s">
         <v>12</v>
@@ -8683,7 +8690,7 @@
       <c r="F504" s="9"/>
       <c r="G504" s="9"/>
     </row>
-    <row r="505">
+    <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="11"/>
       <c r="B505" s="10" t="s">
         <v>2</v>
@@ -8698,7 +8705,7 @@
       </c>
       <c r="G505" s="9"/>
     </row>
-    <row r="506">
+    <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="9"/>
       <c r="B506" s="10" t="s">
         <v>16</v>
@@ -8713,7 +8720,7 @@
       </c>
       <c r="G506" s="9"/>
     </row>
-    <row r="507">
+    <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="9"/>
       <c r="B507" s="9" t="s">
         <v>19</v>
@@ -8726,7 +8733,7 @@
       <c r="F507" s="9"/>
       <c r="G507" s="9"/>
     </row>
-    <row r="508">
+    <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="9"/>
       <c r="B508" s="9" t="s">
         <v>20</v>
@@ -8739,7 +8746,7 @@
       <c r="F508" s="9"/>
       <c r="G508" s="9"/>
     </row>
-    <row r="509">
+    <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="9"/>
       <c r="B509" s="9" t="s">
         <v>22</v>
@@ -8752,7 +8759,7 @@
       <c r="F509" s="9"/>
       <c r="G509" s="9"/>
     </row>
-    <row r="510">
+    <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="9"/>
       <c r="B510" s="9" t="s">
         <v>23</v>
@@ -8765,7 +8772,7 @@
       <c r="F510" s="9"/>
       <c r="G510" s="9"/>
     </row>
-    <row r="511">
+    <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="9"/>
       <c r="B511" s="9" t="s">
         <v>25</v>
@@ -8778,7 +8785,7 @@
       <c r="F511" s="9"/>
       <c r="G511" s="9"/>
     </row>
-    <row r="512">
+    <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="9"/>
       <c r="B512" s="10" t="s">
         <v>26</v>
@@ -8791,7 +8798,7 @@
       <c r="F512" s="9"/>
       <c r="G512" s="9"/>
     </row>
-    <row r="513">
+    <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="9"/>
       <c r="B513" s="9" t="s">
         <v>28</v>
@@ -8804,7 +8811,7 @@
       <c r="F513" s="9"/>
       <c r="G513" s="9"/>
     </row>
-    <row r="514">
+    <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="9"/>
       <c r="B514" s="18" t="s">
         <v>30</v>
@@ -8817,7 +8824,7 @@
       <c r="F514" s="9"/>
       <c r="G514" s="9"/>
     </row>
-    <row r="515">
+    <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="9"/>
       <c r="B515" s="9"/>
       <c r="C515" s="11"/>
@@ -8826,7 +8833,7 @@
       <c r="F515" s="9"/>
       <c r="G515" s="9"/>
     </row>
-    <row r="516">
+    <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="8" t="s">
         <v>116</v>
       </c>
@@ -8837,7 +8844,7 @@
       <c r="F516" s="9"/>
       <c r="G516" s="9"/>
     </row>
-    <row r="517">
+    <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="9"/>
       <c r="B517" s="9" t="s">
         <v>10</v>
@@ -8850,7 +8857,7 @@
       <c r="F517" s="9"/>
       <c r="G517" s="9"/>
     </row>
-    <row r="518">
+    <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="9"/>
       <c r="B518" s="9" t="s">
         <v>12</v>
@@ -8863,7 +8870,7 @@
       <c r="F518" s="9"/>
       <c r="G518" s="9"/>
     </row>
-    <row r="519">
+    <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="10"/>
       <c r="B519" s="10" t="s">
         <v>2</v>
@@ -8876,7 +8883,7 @@
       <c r="F519" s="11"/>
       <c r="G519" s="9"/>
     </row>
-    <row r="520">
+    <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="9"/>
       <c r="B520" s="9" t="s">
         <v>19</v>
@@ -8889,7 +8896,7 @@
       <c r="F520" s="9"/>
       <c r="G520" s="9"/>
     </row>
-    <row r="521">
+    <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="9"/>
       <c r="B521" s="9" t="s">
         <v>20</v>
@@ -8902,7 +8909,7 @@
       <c r="F521" s="9"/>
       <c r="G521" s="9"/>
     </row>
-    <row r="522">
+    <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="9"/>
       <c r="B522" s="9" t="s">
         <v>22</v>
@@ -8915,7 +8922,7 @@
       <c r="F522" s="9"/>
       <c r="G522" s="9"/>
     </row>
-    <row r="523">
+    <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="9"/>
       <c r="B523" s="9" t="s">
         <v>23</v>
@@ -8928,7 +8935,7 @@
       <c r="F523" s="9"/>
       <c r="G523" s="9"/>
     </row>
-    <row r="524">
+    <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="9"/>
       <c r="B524" s="9" t="s">
         <v>25</v>
@@ -8941,7 +8948,7 @@
       <c r="F524" s="9"/>
       <c r="G524" s="9"/>
     </row>
-    <row r="525">
+    <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="9"/>
       <c r="B525" s="10" t="s">
         <v>26</v>
@@ -8954,7 +8961,7 @@
       <c r="F525" s="9"/>
       <c r="G525" s="9"/>
     </row>
-    <row r="526">
+    <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="9"/>
       <c r="B526" s="9" t="s">
         <v>28</v>
@@ -8967,7 +8974,7 @@
       <c r="F526" s="9"/>
       <c r="G526" s="9"/>
     </row>
-    <row r="527">
+    <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="9"/>
       <c r="B527" s="18" t="s">
         <v>30</v>
@@ -8980,7 +8987,7 @@
       <c r="F527" s="9"/>
       <c r="G527" s="9"/>
     </row>
-    <row r="528">
+    <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="9"/>
       <c r="B528" s="9"/>
       <c r="C528" s="9"/>
@@ -8989,7 +8996,7 @@
       <c r="F528" s="9"/>
       <c r="G528" s="9"/>
     </row>
-    <row r="529">
+    <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="8" t="s">
         <v>118</v>
       </c>
@@ -9000,7 +9007,7 @@
       <c r="F529" s="9"/>
       <c r="G529" s="9"/>
     </row>
-    <row r="530">
+    <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="9"/>
       <c r="B530" s="9" t="s">
         <v>10</v>
@@ -9013,7 +9020,7 @@
       <c r="F530" s="9"/>
       <c r="G530" s="9"/>
     </row>
-    <row r="531">
+    <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="9"/>
       <c r="B531" s="9" t="s">
         <v>12</v>
@@ -9026,7 +9033,7 @@
       <c r="F531" s="9"/>
       <c r="G531" s="9"/>
     </row>
-    <row r="532">
+    <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="10"/>
       <c r="B532" s="10" t="s">
         <v>2</v>
@@ -9039,7 +9046,7 @@
       <c r="F532" s="9"/>
       <c r="G532" s="9"/>
     </row>
-    <row r="533">
+    <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="9"/>
       <c r="B533" s="9" t="s">
         <v>19</v>
@@ -9052,7 +9059,7 @@
       <c r="F533" s="9"/>
       <c r="G533" s="9"/>
     </row>
-    <row r="534">
+    <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="9"/>
       <c r="B534" s="9" t="s">
         <v>20</v>
@@ -9065,7 +9072,7 @@
       <c r="F534" s="9"/>
       <c r="G534" s="9"/>
     </row>
-    <row r="535">
+    <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="9"/>
       <c r="B535" s="9" t="s">
         <v>22</v>
@@ -9078,7 +9085,7 @@
       <c r="F535" s="9"/>
       <c r="G535" s="9"/>
     </row>
-    <row r="536">
+    <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="9"/>
       <c r="B536" s="9" t="s">
         <v>23</v>
@@ -9091,7 +9098,7 @@
       <c r="F536" s="9"/>
       <c r="G536" s="9"/>
     </row>
-    <row r="537">
+    <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="9"/>
       <c r="B537" s="9" t="s">
         <v>25</v>
@@ -9104,7 +9111,7 @@
       <c r="F537" s="9"/>
       <c r="G537" s="9"/>
     </row>
-    <row r="538">
+    <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="9"/>
       <c r="B538" s="10" t="s">
         <v>26</v>
@@ -9117,7 +9124,7 @@
       <c r="F538" s="9"/>
       <c r="G538" s="9"/>
     </row>
-    <row r="539">
+    <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="9"/>
       <c r="B539" s="9" t="s">
         <v>28</v>
@@ -9130,7 +9137,7 @@
       <c r="F539" s="9"/>
       <c r="G539" s="9"/>
     </row>
-    <row r="540">
+    <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="9"/>
       <c r="B540" s="18" t="s">
         <v>30</v>
@@ -9143,7 +9150,8 @@
       <c r="F540" s="9"/>
       <c r="G540" s="9"/>
     </row>
-    <row r="542">
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="8" t="s">
         <v>120</v>
       </c>
@@ -9155,7 +9163,7 @@
       <c r="G542" s="9"/>
       <c r="H542" s="9"/>
     </row>
-    <row r="543">
+    <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="9"/>
       <c r="B543" s="9" t="s">
         <v>10</v>
@@ -9169,7 +9177,7 @@
       <c r="G543" s="9"/>
       <c r="H543" s="9"/>
     </row>
-    <row r="544">
+    <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="9"/>
       <c r="B544" s="9" t="s">
         <v>12</v>
@@ -9183,7 +9191,7 @@
       <c r="G544" s="9"/>
       <c r="H544" s="9"/>
     </row>
-    <row r="545">
+    <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="11"/>
       <c r="B545" s="10" t="s">
         <v>2</v>
@@ -9199,7 +9207,7 @@
       <c r="G545" s="9"/>
       <c r="H545" s="9"/>
     </row>
-    <row r="546">
+    <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="9"/>
       <c r="B546" s="10" t="s">
         <v>16</v>
@@ -9215,7 +9223,7 @@
       <c r="G546" s="9"/>
       <c r="H546" s="9"/>
     </row>
-    <row r="547">
+    <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="9"/>
       <c r="B547" s="9" t="s">
         <v>19</v>
@@ -9229,7 +9237,7 @@
       <c r="G547" s="9"/>
       <c r="H547" s="9"/>
     </row>
-    <row r="548">
+    <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="9"/>
       <c r="B548" s="9" t="s">
         <v>20</v>
@@ -9243,7 +9251,7 @@
       <c r="G548" s="9"/>
       <c r="H548" s="9"/>
     </row>
-    <row r="549">
+    <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="9"/>
       <c r="B549" s="9" t="s">
         <v>22</v>
@@ -9257,7 +9265,7 @@
       <c r="G549" s="9"/>
       <c r="H549" s="9"/>
     </row>
-    <row r="550">
+    <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="9"/>
       <c r="B550" s="9" t="s">
         <v>23</v>
@@ -9271,7 +9279,7 @@
       <c r="G550" s="9"/>
       <c r="H550" s="9"/>
     </row>
-    <row r="551">
+    <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="9"/>
       <c r="B551" s="9" t="s">
         <v>25</v>
@@ -9285,7 +9293,7 @@
       <c r="G551" s="9"/>
       <c r="H551" s="9"/>
     </row>
-    <row r="552">
+    <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="9"/>
       <c r="B552" s="10" t="s">
         <v>26</v>
@@ -9299,7 +9307,7 @@
       <c r="G552" s="9"/>
       <c r="H552" s="9"/>
     </row>
-    <row r="553">
+    <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="9"/>
       <c r="B553" s="9" t="s">
         <v>28</v>
@@ -9313,7 +9321,7 @@
       <c r="G553" s="9"/>
       <c r="H553" s="9"/>
     </row>
-    <row r="554">
+    <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="9"/>
       <c r="B554" s="18" t="s">
         <v>30</v>
@@ -9327,7 +9335,7 @@
       <c r="G554" s="9"/>
       <c r="H554" s="9"/>
     </row>
-    <row r="555">
+    <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="9"/>
       <c r="B555" s="9"/>
       <c r="C555" s="9"/>
@@ -9337,7 +9345,7 @@
       <c r="G555" s="9"/>
       <c r="H555" s="9"/>
     </row>
-    <row r="556">
+    <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="8" t="s">
         <v>123</v>
       </c>
@@ -9349,7 +9357,7 @@
       <c r="G556" s="9"/>
       <c r="H556" s="9"/>
     </row>
-    <row r="557">
+    <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="9"/>
       <c r="B557" s="9" t="s">
         <v>10</v>
@@ -9363,7 +9371,7 @@
       <c r="G557" s="9"/>
       <c r="H557" s="9"/>
     </row>
-    <row r="558">
+    <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="9"/>
       <c r="B558" s="9" t="s">
         <v>12</v>
@@ -9377,7 +9385,7 @@
       <c r="G558" s="9"/>
       <c r="H558" s="9"/>
     </row>
-    <row r="559">
+    <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="11"/>
       <c r="B559" s="10" t="s">
         <v>2</v>
@@ -9393,7 +9401,7 @@
       <c r="G559" s="9"/>
       <c r="H559" s="9"/>
     </row>
-    <row r="560">
+    <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="9"/>
       <c r="B560" s="10" t="s">
         <v>16</v>
@@ -9409,7 +9417,7 @@
       <c r="G560" s="9"/>
       <c r="H560" s="9"/>
     </row>
-    <row r="561">
+    <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="9"/>
       <c r="B561" s="9" t="s">
         <v>19</v>
@@ -9423,7 +9431,7 @@
       <c r="G561" s="9"/>
       <c r="H561" s="9"/>
     </row>
-    <row r="562">
+    <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="9"/>
       <c r="B562" s="9" t="s">
         <v>20</v>
@@ -9437,7 +9445,7 @@
       <c r="G562" s="9"/>
       <c r="H562" s="9"/>
     </row>
-    <row r="563">
+    <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="9"/>
       <c r="B563" s="9" t="s">
         <v>22</v>
@@ -9451,7 +9459,7 @@
       <c r="G563" s="9"/>
       <c r="H563" s="9"/>
     </row>
-    <row r="564">
+    <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="9"/>
       <c r="B564" s="9" t="s">
         <v>23</v>
@@ -9465,7 +9473,7 @@
       <c r="G564" s="9"/>
       <c r="H564" s="9"/>
     </row>
-    <row r="565">
+    <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="9"/>
       <c r="B565" s="9" t="s">
         <v>25</v>
@@ -9479,7 +9487,7 @@
       <c r="G565" s="9"/>
       <c r="H565" s="9"/>
     </row>
-    <row r="566">
+    <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="9"/>
       <c r="B566" s="10" t="s">
         <v>26</v>
@@ -9493,7 +9501,7 @@
       <c r="G566" s="9"/>
       <c r="H566" s="9"/>
     </row>
-    <row r="567">
+    <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="9"/>
       <c r="B567" s="9" t="s">
         <v>28</v>
@@ -9507,7 +9515,7 @@
       <c r="G567" s="9"/>
       <c r="H567" s="9"/>
     </row>
-    <row r="568">
+    <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="9"/>
       <c r="B568" s="18" t="s">
         <v>30</v>
@@ -9521,7 +9529,7 @@
       <c r="G568" s="9"/>
       <c r="H568" s="9"/>
     </row>
-    <row r="569">
+    <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="9"/>
       <c r="B569" s="9"/>
       <c r="C569" s="11"/>
@@ -9531,7 +9539,7 @@
       <c r="G569" s="9"/>
       <c r="H569" s="9"/>
     </row>
-    <row r="570">
+    <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="8" t="s">
         <v>125</v>
       </c>
@@ -9543,7 +9551,7 @@
       <c r="G570" s="9"/>
       <c r="H570" s="9"/>
     </row>
-    <row r="571">
+    <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="9"/>
       <c r="B571" s="9" t="s">
         <v>10</v>
@@ -9557,7 +9565,7 @@
       <c r="G571" s="9"/>
       <c r="H571" s="9"/>
     </row>
-    <row r="572">
+    <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="9"/>
       <c r="B572" s="9" t="s">
         <v>12</v>
@@ -9571,7 +9579,7 @@
       <c r="G572" s="9"/>
       <c r="H572" s="9"/>
     </row>
-    <row r="573">
+    <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="10"/>
       <c r="B573" s="10" t="s">
         <v>2</v>
@@ -9585,7 +9593,7 @@
       <c r="G573" s="9"/>
       <c r="H573" s="9"/>
     </row>
-    <row r="574">
+    <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="9"/>
       <c r="B574" s="9" t="s">
         <v>19</v>
@@ -9599,7 +9607,7 @@
       <c r="G574" s="9"/>
       <c r="H574" s="9"/>
     </row>
-    <row r="575">
+    <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="9"/>
       <c r="B575" s="9" t="s">
         <v>20</v>
@@ -9613,7 +9621,7 @@
       <c r="G575" s="9"/>
       <c r="H575" s="9"/>
     </row>
-    <row r="576">
+    <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="9"/>
       <c r="B576" s="9" t="s">
         <v>22</v>
@@ -9627,7 +9635,7 @@
       <c r="G576" s="9"/>
       <c r="H576" s="9"/>
     </row>
-    <row r="577">
+    <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="9"/>
       <c r="B577" s="9" t="s">
         <v>23</v>
@@ -9641,7 +9649,7 @@
       <c r="G577" s="9"/>
       <c r="H577" s="9"/>
     </row>
-    <row r="578">
+    <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="9"/>
       <c r="B578" s="9" t="s">
         <v>25</v>
@@ -9655,7 +9663,7 @@
       <c r="G578" s="9"/>
       <c r="H578" s="9"/>
     </row>
-    <row r="579">
+    <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="9"/>
       <c r="B579" s="10" t="s">
         <v>26</v>
@@ -9669,7 +9677,7 @@
       <c r="G579" s="9"/>
       <c r="H579" s="9"/>
     </row>
-    <row r="580">
+    <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="9"/>
       <c r="B580" s="9" t="s">
         <v>28</v>
@@ -9683,7 +9691,7 @@
       <c r="G580" s="9"/>
       <c r="H580" s="9"/>
     </row>
-    <row r="581">
+    <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="9"/>
       <c r="B581" s="18" t="s">
         <v>30</v>
@@ -9697,7 +9705,7 @@
       <c r="G581" s="9"/>
       <c r="H581" s="9"/>
     </row>
-    <row r="582">
+    <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="9"/>
       <c r="B582" s="9"/>
       <c r="C582" s="9"/>
@@ -9707,7 +9715,7 @@
       <c r="G582" s="9"/>
       <c r="H582" s="9"/>
     </row>
-    <row r="583">
+    <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="8" t="s">
         <v>127</v>
       </c>
@@ -9719,7 +9727,7 @@
       <c r="G583" s="9"/>
       <c r="H583" s="9"/>
     </row>
-    <row r="584">
+    <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="9"/>
       <c r="B584" s="9" t="s">
         <v>10</v>
@@ -9733,7 +9741,7 @@
       <c r="G584" s="9"/>
       <c r="H584" s="9"/>
     </row>
-    <row r="585">
+    <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="9"/>
       <c r="B585" s="9" t="s">
         <v>12</v>
@@ -9747,7 +9755,7 @@
       <c r="G585" s="9"/>
       <c r="H585" s="9"/>
     </row>
-    <row r="586">
+    <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="10"/>
       <c r="B586" s="10" t="s">
         <v>2</v>
@@ -9761,7 +9769,7 @@
       <c r="G586" s="9"/>
       <c r="H586" s="9"/>
     </row>
-    <row r="587">
+    <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="9"/>
       <c r="B587" s="9" t="s">
         <v>19</v>
@@ -9775,7 +9783,7 @@
       <c r="G587" s="9"/>
       <c r="H587" s="9"/>
     </row>
-    <row r="588">
+    <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="9"/>
       <c r="B588" s="9" t="s">
         <v>20</v>
@@ -9789,7 +9797,7 @@
       <c r="G588" s="9"/>
       <c r="H588" s="9"/>
     </row>
-    <row r="589">
+    <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="9"/>
       <c r="B589" s="9" t="s">
         <v>22</v>
@@ -9803,7 +9811,7 @@
       <c r="G589" s="9"/>
       <c r="H589" s="9"/>
     </row>
-    <row r="590">
+    <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="9"/>
       <c r="B590" s="9" t="s">
         <v>23</v>
@@ -9817,7 +9825,7 @@
       <c r="G590" s="9"/>
       <c r="H590" s="9"/>
     </row>
-    <row r="591">
+    <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="9"/>
       <c r="B591" s="9" t="s">
         <v>25</v>
@@ -9831,7 +9839,7 @@
       <c r="G591" s="9"/>
       <c r="H591" s="9"/>
     </row>
-    <row r="592">
+    <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="9"/>
       <c r="B592" s="10" t="s">
         <v>26</v>
@@ -9845,7 +9853,7 @@
       <c r="G592" s="9"/>
       <c r="H592" s="9"/>
     </row>
-    <row r="593">
+    <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="9"/>
       <c r="B593" s="9" t="s">
         <v>28</v>
@@ -9859,7 +9867,7 @@
       <c r="G593" s="9"/>
       <c r="H593" s="9"/>
     </row>
-    <row r="594">
+    <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="9"/>
       <c r="B594" s="18" t="s">
         <v>30</v>
@@ -9873,7 +9881,8 @@
       <c r="G594" s="9"/>
       <c r="H594" s="9"/>
     </row>
-    <row r="596">
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="8" t="s">
         <v>129</v>
       </c>
@@ -9884,7 +9893,7 @@
       <c r="F596" s="9"/>
       <c r="G596" s="9"/>
     </row>
-    <row r="597">
+    <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="9"/>
       <c r="B597" s="9" t="s">
         <v>10</v>
@@ -9897,7 +9906,7 @@
       <c r="F597" s="9"/>
       <c r="G597" s="9"/>
     </row>
-    <row r="598">
+    <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="9"/>
       <c r="B598" s="9" t="s">
         <v>12</v>
@@ -9910,7 +9919,7 @@
       <c r="F598" s="9"/>
       <c r="G598" s="9"/>
     </row>
-    <row r="599">
+    <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="11"/>
       <c r="B599" s="10" t="s">
         <v>2</v>
@@ -9925,7 +9934,7 @@
       </c>
       <c r="G599" s="9"/>
     </row>
-    <row r="600">
+    <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="9"/>
       <c r="B600" s="10" t="s">
         <v>16</v>
@@ -9940,7 +9949,7 @@
       </c>
       <c r="G600" s="9"/>
     </row>
-    <row r="601">
+    <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="9"/>
       <c r="B601" s="9" t="s">
         <v>19</v>
@@ -9953,7 +9962,7 @@
       <c r="F601" s="9"/>
       <c r="G601" s="9"/>
     </row>
-    <row r="602">
+    <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="9"/>
       <c r="B602" s="9" t="s">
         <v>20</v>
@@ -9966,7 +9975,7 @@
       <c r="F602" s="9"/>
       <c r="G602" s="9"/>
     </row>
-    <row r="603">
+    <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="9"/>
       <c r="B603" s="9" t="s">
         <v>22</v>
@@ -9979,7 +9988,7 @@
       <c r="F603" s="9"/>
       <c r="G603" s="9"/>
     </row>
-    <row r="604">
+    <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="9"/>
       <c r="B604" s="9" t="s">
         <v>23</v>
@@ -9992,7 +10001,7 @@
       <c r="F604" s="9"/>
       <c r="G604" s="9"/>
     </row>
-    <row r="605">
+    <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="9"/>
       <c r="B605" s="9" t="s">
         <v>25</v>
@@ -10005,7 +10014,7 @@
       <c r="F605" s="9"/>
       <c r="G605" s="9"/>
     </row>
-    <row r="606">
+    <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="9"/>
       <c r="B606" s="10" t="s">
         <v>26</v>
@@ -10018,7 +10027,7 @@
       <c r="F606" s="9"/>
       <c r="G606" s="9"/>
     </row>
-    <row r="607">
+    <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="9"/>
       <c r="B607" s="9" t="s">
         <v>28</v>
@@ -10031,7 +10040,7 @@
       <c r="F607" s="9"/>
       <c r="G607" s="9"/>
     </row>
-    <row r="608">
+    <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="9"/>
       <c r="B608" s="18" t="s">
         <v>30</v>
@@ -10044,7 +10053,7 @@
       <c r="F608" s="9"/>
       <c r="G608" s="9"/>
     </row>
-    <row r="609">
+    <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="9"/>
       <c r="B609" s="9"/>
       <c r="C609" s="9"/>
@@ -10053,7 +10062,7 @@
       <c r="F609" s="9"/>
       <c r="G609" s="9"/>
     </row>
-    <row r="610">
+    <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="8" t="s">
         <v>132</v>
       </c>
@@ -10064,7 +10073,7 @@
       <c r="F610" s="9"/>
       <c r="G610" s="9"/>
     </row>
-    <row r="611">
+    <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="9"/>
       <c r="B611" s="9" t="s">
         <v>10</v>
@@ -10077,7 +10086,7 @@
       <c r="F611" s="9"/>
       <c r="G611" s="9"/>
     </row>
-    <row r="612">
+    <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="9"/>
       <c r="B612" s="9" t="s">
         <v>12</v>
@@ -10090,7 +10099,7 @@
       <c r="F612" s="9"/>
       <c r="G612" s="9"/>
     </row>
-    <row r="613">
+    <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="11"/>
       <c r="B613" s="10" t="s">
         <v>2</v>
@@ -10105,7 +10114,7 @@
       </c>
       <c r="G613" s="9"/>
     </row>
-    <row r="614">
+    <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="9"/>
       <c r="B614" s="10" t="s">
         <v>16</v>
@@ -10120,7 +10129,7 @@
       </c>
       <c r="G614" s="9"/>
     </row>
-    <row r="615">
+    <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="9"/>
       <c r="B615" s="9" t="s">
         <v>19</v>
@@ -10133,7 +10142,7 @@
       <c r="F615" s="9"/>
       <c r="G615" s="9"/>
     </row>
-    <row r="616">
+    <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="9"/>
       <c r="B616" s="9" t="s">
         <v>20</v>
@@ -10146,7 +10155,7 @@
       <c r="F616" s="9"/>
       <c r="G616" s="9"/>
     </row>
-    <row r="617">
+    <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="9"/>
       <c r="B617" s="9" t="s">
         <v>22</v>
@@ -10159,7 +10168,7 @@
       <c r="F617" s="9"/>
       <c r="G617" s="9"/>
     </row>
-    <row r="618">
+    <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="9"/>
       <c r="B618" s="9" t="s">
         <v>23</v>
@@ -10172,7 +10181,7 @@
       <c r="F618" s="9"/>
       <c r="G618" s="9"/>
     </row>
-    <row r="619">
+    <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="9"/>
       <c r="B619" s="9" t="s">
         <v>25</v>
@@ -10185,7 +10194,7 @@
       <c r="F619" s="9"/>
       <c r="G619" s="9"/>
     </row>
-    <row r="620">
+    <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="9"/>
       <c r="B620" s="10" t="s">
         <v>26</v>
@@ -10198,7 +10207,7 @@
       <c r="F620" s="9"/>
       <c r="G620" s="9"/>
     </row>
-    <row r="621">
+    <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="9"/>
       <c r="B621" s="9" t="s">
         <v>28</v>
@@ -10211,7 +10220,7 @@
       <c r="F621" s="9"/>
       <c r="G621" s="9"/>
     </row>
-    <row r="622">
+    <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="9"/>
       <c r="B622" s="18" t="s">
         <v>30</v>
@@ -10224,7 +10233,7 @@
       <c r="F622" s="9"/>
       <c r="G622" s="9"/>
     </row>
-    <row r="623">
+    <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="9"/>
       <c r="B623" s="9"/>
       <c r="C623" s="11"/>
@@ -10233,7 +10242,7 @@
       <c r="F623" s="9"/>
       <c r="G623" s="9"/>
     </row>
-    <row r="624">
+    <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="8" t="s">
         <v>134</v>
       </c>
@@ -10244,7 +10253,7 @@
       <c r="F624" s="9"/>
       <c r="G624" s="9"/>
     </row>
-    <row r="625">
+    <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="9"/>
       <c r="B625" s="9" t="s">
         <v>10</v>
@@ -10257,7 +10266,7 @@
       <c r="F625" s="9"/>
       <c r="G625" s="9"/>
     </row>
-    <row r="626">
+    <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="9"/>
       <c r="B626" s="9" t="s">
         <v>12</v>
@@ -10270,7 +10279,7 @@
       <c r="F626" s="9"/>
       <c r="G626" s="9"/>
     </row>
-    <row r="627">
+    <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="10"/>
       <c r="B627" s="10" t="s">
         <v>2</v>
@@ -10283,7 +10292,7 @@
       <c r="F627" s="11"/>
       <c r="G627" s="9"/>
     </row>
-    <row r="628">
+    <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="9"/>
       <c r="B628" s="9" t="s">
         <v>19</v>
@@ -10296,7 +10305,7 @@
       <c r="F628" s="9"/>
       <c r="G628" s="9"/>
     </row>
-    <row r="629">
+    <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="9"/>
       <c r="B629" s="9" t="s">
         <v>20</v>
@@ -10309,7 +10318,7 @@
       <c r="F629" s="9"/>
       <c r="G629" s="9"/>
     </row>
-    <row r="630">
+    <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="9"/>
       <c r="B630" s="9" t="s">
         <v>22</v>
@@ -10322,7 +10331,7 @@
       <c r="F630" s="9"/>
       <c r="G630" s="9"/>
     </row>
-    <row r="631">
+    <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="9"/>
       <c r="B631" s="9" t="s">
         <v>23</v>
@@ -10335,7 +10344,7 @@
       <c r="F631" s="9"/>
       <c r="G631" s="9"/>
     </row>
-    <row r="632">
+    <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="9"/>
       <c r="B632" s="9" t="s">
         <v>25</v>
@@ -10348,7 +10357,7 @@
       <c r="F632" s="9"/>
       <c r="G632" s="9"/>
     </row>
-    <row r="633">
+    <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="9"/>
       <c r="B633" s="10" t="s">
         <v>26</v>
@@ -10361,7 +10370,7 @@
       <c r="F633" s="9"/>
       <c r="G633" s="9"/>
     </row>
-    <row r="634">
+    <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="9"/>
       <c r="B634" s="9" t="s">
         <v>28</v>
@@ -10374,7 +10383,7 @@
       <c r="F634" s="9"/>
       <c r="G634" s="9"/>
     </row>
-    <row r="635">
+    <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="9"/>
       <c r="B635" s="18" t="s">
         <v>30</v>
@@ -10387,7 +10396,7 @@
       <c r="F635" s="9"/>
       <c r="G635" s="9"/>
     </row>
-    <row r="636">
+    <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="9"/>
       <c r="B636" s="9"/>
       <c r="C636" s="9"/>
@@ -10396,7 +10405,7 @@
       <c r="F636" s="9"/>
       <c r="G636" s="9"/>
     </row>
-    <row r="637">
+    <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="8" t="s">
         <v>136</v>
       </c>
@@ -10407,7 +10416,7 @@
       <c r="F637" s="9"/>
       <c r="G637" s="9"/>
     </row>
-    <row r="638">
+    <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="9"/>
       <c r="B638" s="9" t="s">
         <v>10</v>
@@ -10420,7 +10429,7 @@
       <c r="F638" s="9"/>
       <c r="G638" s="9"/>
     </row>
-    <row r="639">
+    <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="9"/>
       <c r="B639" s="9" t="s">
         <v>12</v>
@@ -10433,7 +10442,7 @@
       <c r="F639" s="9"/>
       <c r="G639" s="9"/>
     </row>
-    <row r="640">
+    <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="10"/>
       <c r="B640" s="10" t="s">
         <v>2</v>
@@ -10446,7 +10455,7 @@
       <c r="F640" s="9"/>
       <c r="G640" s="9"/>
     </row>
-    <row r="641">
+    <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="9"/>
       <c r="B641" s="9" t="s">
         <v>19</v>
@@ -10459,7 +10468,7 @@
       <c r="F641" s="9"/>
       <c r="G641" s="9"/>
     </row>
-    <row r="642">
+    <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="9"/>
       <c r="B642" s="9" t="s">
         <v>20</v>
@@ -10472,7 +10481,7 @@
       <c r="F642" s="9"/>
       <c r="G642" s="9"/>
     </row>
-    <row r="643">
+    <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="9"/>
       <c r="B643" s="9" t="s">
         <v>22</v>
@@ -10485,7 +10494,7 @@
       <c r="F643" s="9"/>
       <c r="G643" s="9"/>
     </row>
-    <row r="644">
+    <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="9"/>
       <c r="B644" s="9" t="s">
         <v>23</v>
@@ -10498,7 +10507,7 @@
       <c r="F644" s="9"/>
       <c r="G644" s="9"/>
     </row>
-    <row r="645">
+    <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="9"/>
       <c r="B645" s="9" t="s">
         <v>25</v>
@@ -10511,7 +10520,7 @@
       <c r="F645" s="9"/>
       <c r="G645" s="9"/>
     </row>
-    <row r="646">
+    <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="9"/>
       <c r="B646" s="10" t="s">
         <v>26</v>
@@ -10524,7 +10533,7 @@
       <c r="F646" s="9"/>
       <c r="G646" s="9"/>
     </row>
-    <row r="647">
+    <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="9"/>
       <c r="B647" s="9" t="s">
         <v>28</v>
@@ -10537,7 +10546,7 @@
       <c r="F647" s="9"/>
       <c r="G647" s="9"/>
     </row>
-    <row r="648">
+    <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="9"/>
       <c r="B648" s="18" t="s">
         <v>30</v>
@@ -10550,7 +10559,8 @@
       <c r="F648" s="9"/>
       <c r="G648" s="9"/>
     </row>
-    <row r="650">
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="8" t="s">
         <v>138</v>
       </c>
@@ -10561,7 +10571,7 @@
       <c r="F650" s="9"/>
       <c r="G650" s="9"/>
     </row>
-    <row r="651">
+    <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="9"/>
       <c r="B651" s="9" t="s">
         <v>10</v>
@@ -10574,7 +10584,7 @@
       <c r="F651" s="9"/>
       <c r="G651" s="9"/>
     </row>
-    <row r="652">
+    <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="9"/>
       <c r="B652" s="9" t="s">
         <v>12</v>
@@ -10587,7 +10597,7 @@
       <c r="F652" s="9"/>
       <c r="G652" s="9"/>
     </row>
-    <row r="653">
+    <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="11"/>
       <c r="B653" s="10" t="s">
         <v>2</v>
@@ -10602,7 +10612,7 @@
       </c>
       <c r="G653" s="9"/>
     </row>
-    <row r="654">
+    <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="9"/>
       <c r="B654" s="10" t="s">
         <v>16</v>
@@ -10617,7 +10627,7 @@
       </c>
       <c r="G654" s="9"/>
     </row>
-    <row r="655">
+    <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="9"/>
       <c r="B655" s="9" t="s">
         <v>19</v>
@@ -10630,7 +10640,7 @@
       <c r="F655" s="9"/>
       <c r="G655" s="9"/>
     </row>
-    <row r="656">
+    <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="9"/>
       <c r="B656" s="9" t="s">
         <v>20</v>
@@ -10643,7 +10653,7 @@
       <c r="F656" s="9"/>
       <c r="G656" s="9"/>
     </row>
-    <row r="657">
+    <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="9"/>
       <c r="B657" s="9" t="s">
         <v>22</v>
@@ -10656,7 +10666,7 @@
       <c r="F657" s="9"/>
       <c r="G657" s="9"/>
     </row>
-    <row r="658">
+    <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="9"/>
       <c r="B658" s="9" t="s">
         <v>23</v>
@@ -10669,7 +10679,7 @@
       <c r="F658" s="9"/>
       <c r="G658" s="9"/>
     </row>
-    <row r="659">
+    <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="9"/>
       <c r="B659" s="9" t="s">
         <v>25</v>
@@ -10682,7 +10692,7 @@
       <c r="F659" s="9"/>
       <c r="G659" s="9"/>
     </row>
-    <row r="660">
+    <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="9"/>
       <c r="B660" s="10" t="s">
         <v>26</v>
@@ -10695,7 +10705,7 @@
       <c r="F660" s="9"/>
       <c r="G660" s="9"/>
     </row>
-    <row r="661">
+    <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="9"/>
       <c r="B661" s="9" t="s">
         <v>28</v>
@@ -10708,7 +10718,7 @@
       <c r="F661" s="9"/>
       <c r="G661" s="9"/>
     </row>
-    <row r="662">
+    <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="9"/>
       <c r="B662" s="18" t="s">
         <v>30</v>
@@ -10721,7 +10731,7 @@
       <c r="F662" s="9"/>
       <c r="G662" s="9"/>
     </row>
-    <row r="663">
+    <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="9"/>
       <c r="B663" s="9"/>
       <c r="C663" s="9"/>
@@ -10730,7 +10740,7 @@
       <c r="F663" s="9"/>
       <c r="G663" s="9"/>
     </row>
-    <row r="664">
+    <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="8" t="s">
         <v>141</v>
       </c>
@@ -10741,7 +10751,7 @@
       <c r="F664" s="9"/>
       <c r="G664" s="9"/>
     </row>
-    <row r="665">
+    <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="9"/>
       <c r="B665" s="9" t="s">
         <v>10</v>
@@ -10754,7 +10764,7 @@
       <c r="F665" s="9"/>
       <c r="G665" s="9"/>
     </row>
-    <row r="666">
+    <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="9"/>
       <c r="B666" s="9" t="s">
         <v>12</v>
@@ -10767,7 +10777,7 @@
       <c r="F666" s="9"/>
       <c r="G666" s="9"/>
     </row>
-    <row r="667">
+    <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="11"/>
       <c r="B667" s="10" t="s">
         <v>2</v>
@@ -10782,7 +10792,7 @@
       </c>
       <c r="G667" s="9"/>
     </row>
-    <row r="668">
+    <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="9"/>
       <c r="B668" s="10" t="s">
         <v>16</v>
@@ -10797,7 +10807,7 @@
       </c>
       <c r="G668" s="9"/>
     </row>
-    <row r="669">
+    <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="9"/>
       <c r="B669" s="9" t="s">
         <v>19</v>
@@ -10810,7 +10820,7 @@
       <c r="F669" s="9"/>
       <c r="G669" s="9"/>
     </row>
-    <row r="670">
+    <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="9"/>
       <c r="B670" s="9" t="s">
         <v>20</v>
@@ -10823,7 +10833,7 @@
       <c r="F670" s="9"/>
       <c r="G670" s="9"/>
     </row>
-    <row r="671">
+    <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="9"/>
       <c r="B671" s="9" t="s">
         <v>22</v>
@@ -10836,7 +10846,7 @@
       <c r="F671" s="9"/>
       <c r="G671" s="9"/>
     </row>
-    <row r="672">
+    <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="9"/>
       <c r="B672" s="9" t="s">
         <v>23</v>
@@ -10849,7 +10859,7 @@
       <c r="F672" s="9"/>
       <c r="G672" s="9"/>
     </row>
-    <row r="673">
+    <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="9"/>
       <c r="B673" s="9" t="s">
         <v>25</v>
@@ -10862,7 +10872,7 @@
       <c r="F673" s="9"/>
       <c r="G673" s="9"/>
     </row>
-    <row r="674">
+    <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="9"/>
       <c r="B674" s="10" t="s">
         <v>26</v>
@@ -10875,7 +10885,7 @@
       <c r="F674" s="9"/>
       <c r="G674" s="9"/>
     </row>
-    <row r="675">
+    <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="9"/>
       <c r="B675" s="9" t="s">
         <v>28</v>
@@ -10888,7 +10898,7 @@
       <c r="F675" s="9"/>
       <c r="G675" s="9"/>
     </row>
-    <row r="676">
+    <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="9"/>
       <c r="B676" s="18" t="s">
         <v>30</v>
@@ -10901,7 +10911,7 @@
       <c r="F676" s="9"/>
       <c r="G676" s="9"/>
     </row>
-    <row r="677">
+    <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="9"/>
       <c r="B677" s="9"/>
       <c r="C677" s="11"/>
@@ -10910,7 +10920,7 @@
       <c r="F677" s="9"/>
       <c r="G677" s="9"/>
     </row>
-    <row r="678">
+    <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="8" t="s">
         <v>143</v>
       </c>
@@ -10921,7 +10931,7 @@
       <c r="F678" s="9"/>
       <c r="G678" s="9"/>
     </row>
-    <row r="679">
+    <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="9"/>
       <c r="B679" s="9" t="s">
         <v>10</v>
@@ -10934,7 +10944,7 @@
       <c r="F679" s="9"/>
       <c r="G679" s="9"/>
     </row>
-    <row r="680">
+    <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="9"/>
       <c r="B680" s="9" t="s">
         <v>12</v>
@@ -10947,7 +10957,7 @@
       <c r="F680" s="9"/>
       <c r="G680" s="9"/>
     </row>
-    <row r="681">
+    <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="10"/>
       <c r="B681" s="10" t="s">
         <v>2</v>
@@ -10960,7 +10970,7 @@
       <c r="F681" s="11"/>
       <c r="G681" s="9"/>
     </row>
-    <row r="682">
+    <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="9"/>
       <c r="B682" s="9" t="s">
         <v>19</v>
@@ -10973,7 +10983,7 @@
       <c r="F682" s="9"/>
       <c r="G682" s="9"/>
     </row>
-    <row r="683">
+    <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="9"/>
       <c r="B683" s="9" t="s">
         <v>20</v>
@@ -10986,7 +10996,7 @@
       <c r="F683" s="9"/>
       <c r="G683" s="9"/>
     </row>
-    <row r="684">
+    <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="9"/>
       <c r="B684" s="9" t="s">
         <v>22</v>
@@ -10999,7 +11009,7 @@
       <c r="F684" s="9"/>
       <c r="G684" s="9"/>
     </row>
-    <row r="685">
+    <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="9"/>
       <c r="B685" s="9" t="s">
         <v>23</v>
@@ -11012,7 +11022,7 @@
       <c r="F685" s="9"/>
       <c r="G685" s="9"/>
     </row>
-    <row r="686">
+    <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="9"/>
       <c r="B686" s="9" t="s">
         <v>25</v>
@@ -11025,7 +11035,7 @@
       <c r="F686" s="9"/>
       <c r="G686" s="9"/>
     </row>
-    <row r="687">
+    <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="9"/>
       <c r="B687" s="10" t="s">
         <v>26</v>
@@ -11038,7 +11048,7 @@
       <c r="F687" s="9"/>
       <c r="G687" s="9"/>
     </row>
-    <row r="688">
+    <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="9"/>
       <c r="B688" s="9" t="s">
         <v>28</v>
@@ -11051,7 +11061,7 @@
       <c r="F688" s="9"/>
       <c r="G688" s="9"/>
     </row>
-    <row r="689">
+    <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="9"/>
       <c r="B689" s="18" t="s">
         <v>30</v>
@@ -11064,7 +11074,7 @@
       <c r="F689" s="9"/>
       <c r="G689" s="9"/>
     </row>
-    <row r="690">
+    <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="9"/>
       <c r="B690" s="9"/>
       <c r="C690" s="9"/>
@@ -11073,7 +11083,7 @@
       <c r="F690" s="9"/>
       <c r="G690" s="9"/>
     </row>
-    <row r="691">
+    <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="8" t="s">
         <v>145</v>
       </c>
@@ -11084,7 +11094,7 @@
       <c r="F691" s="9"/>
       <c r="G691" s="9"/>
     </row>
-    <row r="692">
+    <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="9"/>
       <c r="B692" s="9" t="s">
         <v>10</v>
@@ -11097,7 +11107,7 @@
       <c r="F692" s="9"/>
       <c r="G692" s="9"/>
     </row>
-    <row r="693">
+    <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="9"/>
       <c r="B693" s="9" t="s">
         <v>12</v>
@@ -11110,7 +11120,7 @@
       <c r="F693" s="9"/>
       <c r="G693" s="9"/>
     </row>
-    <row r="694">
+    <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="10"/>
       <c r="B694" s="10" t="s">
         <v>2</v>
@@ -11123,7 +11133,7 @@
       <c r="F694" s="9"/>
       <c r="G694" s="9"/>
     </row>
-    <row r="695">
+    <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="9"/>
       <c r="B695" s="9" t="s">
         <v>19</v>
@@ -11136,7 +11146,7 @@
       <c r="F695" s="9"/>
       <c r="G695" s="9"/>
     </row>
-    <row r="696">
+    <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="9"/>
       <c r="B696" s="9" t="s">
         <v>20</v>
@@ -11149,7 +11159,7 @@
       <c r="F696" s="9"/>
       <c r="G696" s="9"/>
     </row>
-    <row r="697">
+    <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="9"/>
       <c r="B697" s="9" t="s">
         <v>22</v>
@@ -11162,7 +11172,7 @@
       <c r="F697" s="9"/>
       <c r="G697" s="9"/>
     </row>
-    <row r="698">
+    <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="9"/>
       <c r="B698" s="9" t="s">
         <v>23</v>
@@ -11175,7 +11185,7 @@
       <c r="F698" s="9"/>
       <c r="G698" s="9"/>
     </row>
-    <row r="699">
+    <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="9"/>
       <c r="B699" s="9" t="s">
         <v>25</v>
@@ -11188,7 +11198,7 @@
       <c r="F699" s="9"/>
       <c r="G699" s="9"/>
     </row>
-    <row r="700">
+    <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="9"/>
       <c r="B700" s="10" t="s">
         <v>26</v>
@@ -11201,7 +11211,7 @@
       <c r="F700" s="9"/>
       <c r="G700" s="9"/>
     </row>
-    <row r="701">
+    <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="9"/>
       <c r="B701" s="9" t="s">
         <v>28</v>
@@ -11214,7 +11224,7 @@
       <c r="F701" s="9"/>
       <c r="G701" s="9"/>
     </row>
-    <row r="702">
+    <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="9"/>
       <c r="B702" s="18" t="s">
         <v>30</v>
@@ -11227,7 +11237,8 @@
       <c r="F702" s="9"/>
       <c r="G702" s="9"/>
     </row>
-    <row r="704">
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="8" t="s">
         <v>147</v>
       </c>
@@ -11238,7 +11249,7 @@
       <c r="F704" s="9"/>
       <c r="G704" s="9"/>
     </row>
-    <row r="705">
+    <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="9"/>
       <c r="B705" s="9" t="s">
         <v>10</v>
@@ -11251,7 +11262,7 @@
       <c r="F705" s="9"/>
       <c r="G705" s="9"/>
     </row>
-    <row r="706">
+    <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="9"/>
       <c r="B706" s="9" t="s">
         <v>12</v>
@@ -11264,7 +11275,7 @@
       <c r="F706" s="9"/>
       <c r="G706" s="9"/>
     </row>
-    <row r="707">
+    <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="11"/>
       <c r="B707" s="10" t="s">
         <v>2</v>
@@ -11279,7 +11290,7 @@
       </c>
       <c r="G707" s="9"/>
     </row>
-    <row r="708">
+    <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="9"/>
       <c r="B708" s="10" t="s">
         <v>16</v>
@@ -11294,7 +11305,7 @@
       </c>
       <c r="G708" s="9"/>
     </row>
-    <row r="709">
+    <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="9"/>
       <c r="B709" s="9" t="s">
         <v>19</v>
@@ -11307,7 +11318,7 @@
       <c r="F709" s="9"/>
       <c r="G709" s="9"/>
     </row>
-    <row r="710">
+    <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="9"/>
       <c r="B710" s="9" t="s">
         <v>20</v>
@@ -11320,7 +11331,7 @@
       <c r="F710" s="9"/>
       <c r="G710" s="9"/>
     </row>
-    <row r="711">
+    <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="9"/>
       <c r="B711" s="9" t="s">
         <v>22</v>
@@ -11333,7 +11344,7 @@
       <c r="F711" s="9"/>
       <c r="G711" s="9"/>
     </row>
-    <row r="712">
+    <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="9"/>
       <c r="B712" s="9" t="s">
         <v>23</v>
@@ -11346,7 +11357,7 @@
       <c r="F712" s="9"/>
       <c r="G712" s="9"/>
     </row>
-    <row r="713">
+    <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="9"/>
       <c r="B713" s="9" t="s">
         <v>25</v>
@@ -11359,7 +11370,7 @@
       <c r="F713" s="9"/>
       <c r="G713" s="9"/>
     </row>
-    <row r="714">
+    <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="9"/>
       <c r="B714" s="10" t="s">
         <v>26</v>
@@ -11372,7 +11383,7 @@
       <c r="F714" s="9"/>
       <c r="G714" s="9"/>
     </row>
-    <row r="715">
+    <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="9"/>
       <c r="B715" s="9" t="s">
         <v>28</v>
@@ -11385,7 +11396,7 @@
       <c r="F715" s="9"/>
       <c r="G715" s="9"/>
     </row>
-    <row r="716">
+    <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="9"/>
       <c r="B716" s="18" t="s">
         <v>30</v>
@@ -11398,7 +11409,7 @@
       <c r="F716" s="9"/>
       <c r="G716" s="9"/>
     </row>
-    <row r="717">
+    <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="9"/>
       <c r="B717" s="9"/>
       <c r="C717" s="9"/>
@@ -11407,7 +11418,7 @@
       <c r="F717" s="9"/>
       <c r="G717" s="9"/>
     </row>
-    <row r="718">
+    <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="8" t="s">
         <v>150</v>
       </c>
@@ -11418,7 +11429,7 @@
       <c r="F718" s="9"/>
       <c r="G718" s="9"/>
     </row>
-    <row r="719">
+    <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="9"/>
       <c r="B719" s="9" t="s">
         <v>10</v>
@@ -11431,7 +11442,7 @@
       <c r="F719" s="9"/>
       <c r="G719" s="9"/>
     </row>
-    <row r="720">
+    <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="9"/>
       <c r="B720" s="9" t="s">
         <v>12</v>
@@ -11444,7 +11455,7 @@
       <c r="F720" s="9"/>
       <c r="G720" s="9"/>
     </row>
-    <row r="721">
+    <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="11"/>
       <c r="B721" s="10" t="s">
         <v>2</v>
@@ -11459,7 +11470,7 @@
       </c>
       <c r="G721" s="9"/>
     </row>
-    <row r="722">
+    <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="9"/>
       <c r="B722" s="10" t="s">
         <v>16</v>
@@ -11474,7 +11485,7 @@
       </c>
       <c r="G722" s="9"/>
     </row>
-    <row r="723">
+    <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="9"/>
       <c r="B723" s="9" t="s">
         <v>19</v>
@@ -11487,7 +11498,7 @@
       <c r="F723" s="9"/>
       <c r="G723" s="9"/>
     </row>
-    <row r="724">
+    <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="9"/>
       <c r="B724" s="9" t="s">
         <v>20</v>
@@ -11500,7 +11511,7 @@
       <c r="F724" s="9"/>
       <c r="G724" s="9"/>
     </row>
-    <row r="725">
+    <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="9"/>
       <c r="B725" s="9" t="s">
         <v>22</v>
@@ -11513,7 +11524,7 @@
       <c r="F725" s="9"/>
       <c r="G725" s="9"/>
     </row>
-    <row r="726">
+    <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="9"/>
       <c r="B726" s="9" t="s">
         <v>23</v>
@@ -11526,7 +11537,7 @@
       <c r="F726" s="9"/>
       <c r="G726" s="9"/>
     </row>
-    <row r="727">
+    <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="9"/>
       <c r="B727" s="9" t="s">
         <v>25</v>
@@ -11539,7 +11550,7 @@
       <c r="F727" s="9"/>
       <c r="G727" s="9"/>
     </row>
-    <row r="728">
+    <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="9"/>
       <c r="B728" s="10" t="s">
         <v>26</v>
@@ -11552,7 +11563,7 @@
       <c r="F728" s="9"/>
       <c r="G728" s="9"/>
     </row>
-    <row r="729">
+    <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="9"/>
       <c r="B729" s="9" t="s">
         <v>28</v>
@@ -11565,7 +11576,7 @@
       <c r="F729" s="9"/>
       <c r="G729" s="9"/>
     </row>
-    <row r="730">
+    <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="9"/>
       <c r="B730" s="18" t="s">
         <v>30</v>
@@ -11578,7 +11589,7 @@
       <c r="F730" s="9"/>
       <c r="G730" s="9"/>
     </row>
-    <row r="731">
+    <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="9"/>
       <c r="B731" s="9"/>
       <c r="C731" s="11"/>
@@ -11587,7 +11598,7 @@
       <c r="F731" s="9"/>
       <c r="G731" s="9"/>
     </row>
-    <row r="732">
+    <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="8" t="s">
         <v>152</v>
       </c>
@@ -11598,7 +11609,7 @@
       <c r="F732" s="9"/>
       <c r="G732" s="9"/>
     </row>
-    <row r="733">
+    <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="9"/>
       <c r="B733" s="9" t="s">
         <v>10</v>
@@ -11611,7 +11622,7 @@
       <c r="F733" s="9"/>
       <c r="G733" s="9"/>
     </row>
-    <row r="734">
+    <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="9"/>
       <c r="B734" s="9" t="s">
         <v>12</v>
@@ -11624,7 +11635,7 @@
       <c r="F734" s="9"/>
       <c r="G734" s="9"/>
     </row>
-    <row r="735">
+    <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="10"/>
       <c r="B735" s="10" t="s">
         <v>2</v>
@@ -11637,7 +11648,7 @@
       <c r="F735" s="11"/>
       <c r="G735" s="9"/>
     </row>
-    <row r="736">
+    <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="9"/>
       <c r="B736" s="9" t="s">
         <v>19</v>
@@ -11650,7 +11661,7 @@
       <c r="F736" s="9"/>
       <c r="G736" s="9"/>
     </row>
-    <row r="737">
+    <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="9"/>
       <c r="B737" s="9" t="s">
         <v>20</v>
@@ -11663,7 +11674,7 @@
       <c r="F737" s="9"/>
       <c r="G737" s="9"/>
     </row>
-    <row r="738">
+    <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="9"/>
       <c r="B738" s="9" t="s">
         <v>22</v>
@@ -11676,7 +11687,7 @@
       <c r="F738" s="9"/>
       <c r="G738" s="9"/>
     </row>
-    <row r="739">
+    <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="9"/>
       <c r="B739" s="9" t="s">
         <v>23</v>
@@ -11689,7 +11700,7 @@
       <c r="F739" s="9"/>
       <c r="G739" s="9"/>
     </row>
-    <row r="740">
+    <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="9"/>
       <c r="B740" s="9" t="s">
         <v>25</v>
@@ -11702,7 +11713,7 @@
       <c r="F740" s="9"/>
       <c r="G740" s="9"/>
     </row>
-    <row r="741">
+    <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="9"/>
       <c r="B741" s="10" t="s">
         <v>26</v>
@@ -11715,7 +11726,7 @@
       <c r="F741" s="9"/>
       <c r="G741" s="9"/>
     </row>
-    <row r="742">
+    <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="9"/>
       <c r="B742" s="9" t="s">
         <v>28</v>
@@ -11728,7 +11739,7 @@
       <c r="F742" s="9"/>
       <c r="G742" s="9"/>
     </row>
-    <row r="743">
+    <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="9"/>
       <c r="B743" s="18" t="s">
         <v>30</v>
@@ -11741,7 +11752,7 @@
       <c r="F743" s="9"/>
       <c r="G743" s="9"/>
     </row>
-    <row r="744">
+    <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="9"/>
       <c r="B744" s="9"/>
       <c r="C744" s="9"/>
@@ -11750,7 +11761,7 @@
       <c r="F744" s="9"/>
       <c r="G744" s="9"/>
     </row>
-    <row r="745">
+    <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="8" t="s">
         <v>154</v>
       </c>
@@ -11761,7 +11772,7 @@
       <c r="F745" s="9"/>
       <c r="G745" s="9"/>
     </row>
-    <row r="746">
+    <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="9"/>
       <c r="B746" s="9" t="s">
         <v>10</v>
@@ -11774,7 +11785,7 @@
       <c r="F746" s="9"/>
       <c r="G746" s="9"/>
     </row>
-    <row r="747">
+    <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="9"/>
       <c r="B747" s="9" t="s">
         <v>12</v>
@@ -11787,7 +11798,7 @@
       <c r="F747" s="9"/>
       <c r="G747" s="9"/>
     </row>
-    <row r="748">
+    <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="10"/>
       <c r="B748" s="10" t="s">
         <v>2</v>
@@ -11800,7 +11811,7 @@
       <c r="F748" s="9"/>
       <c r="G748" s="9"/>
     </row>
-    <row r="749">
+    <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="9"/>
       <c r="B749" s="9" t="s">
         <v>19</v>
@@ -11813,7 +11824,7 @@
       <c r="F749" s="9"/>
       <c r="G749" s="9"/>
     </row>
-    <row r="750">
+    <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="9"/>
       <c r="B750" s="9" t="s">
         <v>20</v>
@@ -11826,7 +11837,7 @@
       <c r="F750" s="9"/>
       <c r="G750" s="9"/>
     </row>
-    <row r="751">
+    <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="9"/>
       <c r="B751" s="9" t="s">
         <v>22</v>
@@ -11839,7 +11850,7 @@
       <c r="F751" s="9"/>
       <c r="G751" s="9"/>
     </row>
-    <row r="752">
+    <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="9"/>
       <c r="B752" s="9" t="s">
         <v>23</v>
@@ -11852,7 +11863,7 @@
       <c r="F752" s="9"/>
       <c r="G752" s="9"/>
     </row>
-    <row r="753">
+    <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="9"/>
       <c r="B753" s="9" t="s">
         <v>25</v>
@@ -11865,7 +11876,7 @@
       <c r="F753" s="9"/>
       <c r="G753" s="9"/>
     </row>
-    <row r="754">
+    <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="9"/>
       <c r="B754" s="10" t="s">
         <v>26</v>
@@ -11878,7 +11889,7 @@
       <c r="F754" s="9"/>
       <c r="G754" s="9"/>
     </row>
-    <row r="755">
+    <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="9"/>
       <c r="B755" s="9" t="s">
         <v>28</v>
@@ -11891,7 +11902,7 @@
       <c r="F755" s="9"/>
       <c r="G755" s="9"/>
     </row>
-    <row r="756">
+    <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="9"/>
       <c r="B756" s="18" t="s">
         <v>30</v>
@@ -11904,7 +11915,8 @@
       <c r="F756" s="9"/>
       <c r="G756" s="9"/>
     </row>
-    <row r="758">
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="8" t="s">
         <v>156</v>
       </c>
@@ -11915,7 +11927,7 @@
       <c r="F758" s="9"/>
       <c r="G758" s="9"/>
     </row>
-    <row r="759">
+    <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="9"/>
       <c r="B759" s="9" t="s">
         <v>10</v>
@@ -11928,7 +11940,7 @@
       <c r="F759" s="9"/>
       <c r="G759" s="9"/>
     </row>
-    <row r="760">
+    <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="9"/>
       <c r="B760" s="9" t="s">
         <v>12</v>
@@ -11941,7 +11953,7 @@
       <c r="F760" s="9"/>
       <c r="G760" s="9"/>
     </row>
-    <row r="761">
+    <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="11"/>
       <c r="B761" s="10" t="s">
         <v>2</v>
@@ -11956,7 +11968,7 @@
       </c>
       <c r="G761" s="9"/>
     </row>
-    <row r="762">
+    <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="9"/>
       <c r="B762" s="10" t="s">
         <v>16</v>
@@ -11971,7 +11983,7 @@
       </c>
       <c r="G762" s="9"/>
     </row>
-    <row r="763">
+    <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="9"/>
       <c r="B763" s="9" t="s">
         <v>19</v>
@@ -11984,7 +11996,7 @@
       <c r="F763" s="9"/>
       <c r="G763" s="9"/>
     </row>
-    <row r="764">
+    <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="9"/>
       <c r="B764" s="9" t="s">
         <v>20</v>
@@ -11997,7 +12009,7 @@
       <c r="F764" s="9"/>
       <c r="G764" s="9"/>
     </row>
-    <row r="765">
+    <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="9"/>
       <c r="B765" s="9" t="s">
         <v>22</v>
@@ -12010,7 +12022,7 @@
       <c r="F765" s="9"/>
       <c r="G765" s="9"/>
     </row>
-    <row r="766">
+    <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="9"/>
       <c r="B766" s="9" t="s">
         <v>23</v>
@@ -12023,7 +12035,7 @@
       <c r="F766" s="9"/>
       <c r="G766" s="9"/>
     </row>
-    <row r="767">
+    <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="9"/>
       <c r="B767" s="9" t="s">
         <v>25</v>
@@ -12036,7 +12048,7 @@
       <c r="F767" s="9"/>
       <c r="G767" s="9"/>
     </row>
-    <row r="768">
+    <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="9"/>
       <c r="B768" s="10" t="s">
         <v>26</v>
@@ -12049,7 +12061,7 @@
       <c r="F768" s="9"/>
       <c r="G768" s="9"/>
     </row>
-    <row r="769">
+    <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="9"/>
       <c r="B769" s="9" t="s">
         <v>28</v>
@@ -12062,7 +12074,7 @@
       <c r="F769" s="9"/>
       <c r="G769" s="9"/>
     </row>
-    <row r="770">
+    <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="9"/>
       <c r="B770" s="18" t="s">
         <v>30</v>
@@ -12075,7 +12087,7 @@
       <c r="F770" s="9"/>
       <c r="G770" s="9"/>
     </row>
-    <row r="771">
+    <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="9"/>
       <c r="B771" s="9"/>
       <c r="C771" s="9"/>
@@ -12084,7 +12096,7 @@
       <c r="F771" s="9"/>
       <c r="G771" s="9"/>
     </row>
-    <row r="772">
+    <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="8" t="s">
         <v>159</v>
       </c>
@@ -12095,7 +12107,7 @@
       <c r="F772" s="9"/>
       <c r="G772" s="9"/>
     </row>
-    <row r="773">
+    <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="9"/>
       <c r="B773" s="9" t="s">
         <v>10</v>
@@ -12108,7 +12120,7 @@
       <c r="F773" s="9"/>
       <c r="G773" s="9"/>
     </row>
-    <row r="774">
+    <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="9"/>
       <c r="B774" s="9" t="s">
         <v>12</v>
@@ -12121,7 +12133,7 @@
       <c r="F774" s="9"/>
       <c r="G774" s="9"/>
     </row>
-    <row r="775">
+    <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="11"/>
       <c r="B775" s="10" t="s">
         <v>2</v>
@@ -12136,7 +12148,7 @@
       </c>
       <c r="G775" s="9"/>
     </row>
-    <row r="776">
+    <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="9"/>
       <c r="B776" s="10" t="s">
         <v>16</v>
@@ -12151,7 +12163,7 @@
       </c>
       <c r="G776" s="9"/>
     </row>
-    <row r="777">
+    <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="9"/>
       <c r="B777" s="9" t="s">
         <v>19</v>
@@ -12164,7 +12176,7 @@
       <c r="F777" s="9"/>
       <c r="G777" s="9"/>
     </row>
-    <row r="778">
+    <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="9"/>
       <c r="B778" s="9" t="s">
         <v>20</v>
@@ -12177,7 +12189,7 @@
       <c r="F778" s="9"/>
       <c r="G778" s="9"/>
     </row>
-    <row r="779">
+    <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="9"/>
       <c r="B779" s="9" t="s">
         <v>22</v>
@@ -12190,7 +12202,7 @@
       <c r="F779" s="9"/>
       <c r="G779" s="9"/>
     </row>
-    <row r="780">
+    <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="9"/>
       <c r="B780" s="9" t="s">
         <v>23</v>
@@ -12203,7 +12215,7 @@
       <c r="F780" s="9"/>
       <c r="G780" s="9"/>
     </row>
-    <row r="781">
+    <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="9"/>
       <c r="B781" s="9" t="s">
         <v>25</v>
@@ -12216,7 +12228,7 @@
       <c r="F781" s="9"/>
       <c r="G781" s="9"/>
     </row>
-    <row r="782">
+    <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="9"/>
       <c r="B782" s="10" t="s">
         <v>26</v>
@@ -12229,7 +12241,7 @@
       <c r="F782" s="9"/>
       <c r="G782" s="9"/>
     </row>
-    <row r="783">
+    <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="9"/>
       <c r="B783" s="9" t="s">
         <v>28</v>
@@ -12242,7 +12254,7 @@
       <c r="F783" s="9"/>
       <c r="G783" s="9"/>
     </row>
-    <row r="784">
+    <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="9"/>
       <c r="B784" s="18" t="s">
         <v>30</v>
@@ -12255,7 +12267,7 @@
       <c r="F784" s="9"/>
       <c r="G784" s="9"/>
     </row>
-    <row r="785">
+    <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="9"/>
       <c r="B785" s="9"/>
       <c r="C785" s="11"/>
@@ -12264,7 +12276,7 @@
       <c r="F785" s="9"/>
       <c r="G785" s="9"/>
     </row>
-    <row r="786">
+    <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="8" t="s">
         <v>161</v>
       </c>
@@ -12275,7 +12287,7 @@
       <c r="F786" s="9"/>
       <c r="G786" s="9"/>
     </row>
-    <row r="787">
+    <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="9"/>
       <c r="B787" s="9" t="s">
         <v>10</v>
@@ -12288,7 +12300,7 @@
       <c r="F787" s="9"/>
       <c r="G787" s="9"/>
     </row>
-    <row r="788">
+    <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="9"/>
       <c r="B788" s="9" t="s">
         <v>12</v>
@@ -12301,7 +12313,7 @@
       <c r="F788" s="9"/>
       <c r="G788" s="9"/>
     </row>
-    <row r="789">
+    <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="10"/>
       <c r="B789" s="10" t="s">
         <v>2</v>
@@ -12314,7 +12326,7 @@
       <c r="F789" s="11"/>
       <c r="G789" s="9"/>
     </row>
-    <row r="790">
+    <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="9"/>
       <c r="B790" s="9" t="s">
         <v>19</v>
@@ -12327,7 +12339,7 @@
       <c r="F790" s="9"/>
       <c r="G790" s="9"/>
     </row>
-    <row r="791">
+    <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="9"/>
       <c r="B791" s="9" t="s">
         <v>20</v>
@@ -12340,7 +12352,7 @@
       <c r="F791" s="9"/>
       <c r="G791" s="9"/>
     </row>
-    <row r="792">
+    <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="9"/>
       <c r="B792" s="9" t="s">
         <v>22</v>
@@ -12353,7 +12365,7 @@
       <c r="F792" s="9"/>
       <c r="G792" s="9"/>
     </row>
-    <row r="793">
+    <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="9"/>
       <c r="B793" s="9" t="s">
         <v>23</v>
@@ -12366,7 +12378,7 @@
       <c r="F793" s="9"/>
       <c r="G793" s="9"/>
     </row>
-    <row r="794">
+    <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="9"/>
       <c r="B794" s="9" t="s">
         <v>25</v>
@@ -12379,7 +12391,7 @@
       <c r="F794" s="9"/>
       <c r="G794" s="9"/>
     </row>
-    <row r="795">
+    <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="9"/>
       <c r="B795" s="10" t="s">
         <v>26</v>
@@ -12392,7 +12404,7 @@
       <c r="F795" s="9"/>
       <c r="G795" s="9"/>
     </row>
-    <row r="796">
+    <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="9"/>
       <c r="B796" s="9" t="s">
         <v>28</v>
@@ -12405,7 +12417,7 @@
       <c r="F796" s="9"/>
       <c r="G796" s="9"/>
     </row>
-    <row r="797">
+    <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="9"/>
       <c r="B797" s="18" t="s">
         <v>30</v>
@@ -12418,7 +12430,7 @@
       <c r="F797" s="9"/>
       <c r="G797" s="9"/>
     </row>
-    <row r="798">
+    <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="9"/>
       <c r="B798" s="9"/>
       <c r="C798" s="9"/>
@@ -12427,7 +12439,7 @@
       <c r="F798" s="9"/>
       <c r="G798" s="9"/>
     </row>
-    <row r="799">
+    <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="8" t="s">
         <v>163</v>
       </c>
@@ -12438,7 +12450,7 @@
       <c r="F799" s="9"/>
       <c r="G799" s="9"/>
     </row>
-    <row r="800">
+    <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="9"/>
       <c r="B800" s="9" t="s">
         <v>10</v>
@@ -12451,7 +12463,7 @@
       <c r="F800" s="9"/>
       <c r="G800" s="9"/>
     </row>
-    <row r="801">
+    <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="9"/>
       <c r="B801" s="9" t="s">
         <v>12</v>
@@ -12464,7 +12476,7 @@
       <c r="F801" s="9"/>
       <c r="G801" s="9"/>
     </row>
-    <row r="802">
+    <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="10"/>
       <c r="B802" s="10" t="s">
         <v>2</v>
@@ -12477,7 +12489,7 @@
       <c r="F802" s="9"/>
       <c r="G802" s="9"/>
     </row>
-    <row r="803">
+    <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="9"/>
       <c r="B803" s="9" t="s">
         <v>19</v>
@@ -12490,7 +12502,7 @@
       <c r="F803" s="9"/>
       <c r="G803" s="9"/>
     </row>
-    <row r="804">
+    <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="9"/>
       <c r="B804" s="9" t="s">
         <v>20</v>
@@ -12503,7 +12515,7 @@
       <c r="F804" s="9"/>
       <c r="G804" s="9"/>
     </row>
-    <row r="805">
+    <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="9"/>
       <c r="B805" s="9" t="s">
         <v>22</v>
@@ -12516,7 +12528,7 @@
       <c r="F805" s="9"/>
       <c r="G805" s="9"/>
     </row>
-    <row r="806">
+    <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="9"/>
       <c r="B806" s="9" t="s">
         <v>23</v>
@@ -12529,7 +12541,7 @@
       <c r="F806" s="9"/>
       <c r="G806" s="9"/>
     </row>
-    <row r="807">
+    <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="9"/>
       <c r="B807" s="9" t="s">
         <v>25</v>
@@ -12542,7 +12554,7 @@
       <c r="F807" s="9"/>
       <c r="G807" s="9"/>
     </row>
-    <row r="808">
+    <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="9"/>
       <c r="B808" s="10" t="s">
         <v>26</v>
@@ -12555,7 +12567,7 @@
       <c r="F808" s="9"/>
       <c r="G808" s="9"/>
     </row>
-    <row r="809">
+    <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="9"/>
       <c r="B809" s="9" t="s">
         <v>28</v>
@@ -12568,7 +12580,7 @@
       <c r="F809" s="9"/>
       <c r="G809" s="9"/>
     </row>
-    <row r="810">
+    <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="9"/>
       <c r="B810" s="18" t="s">
         <v>30</v>
@@ -12581,7 +12593,8 @@
       <c r="F810" s="9"/>
       <c r="G810" s="9"/>
     </row>
-    <row r="812">
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="8" t="s">
         <v>165</v>
       </c>
@@ -12591,7 +12604,7 @@
       <c r="E812" s="9"/>
       <c r="F812" s="9"/>
     </row>
-    <row r="813">
+    <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="9"/>
       <c r="B813" s="9" t="s">
         <v>10</v>
@@ -12603,7 +12616,7 @@
       <c r="E813" s="9"/>
       <c r="F813" s="9"/>
     </row>
-    <row r="814">
+    <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="9"/>
       <c r="B814" s="9" t="s">
         <v>12</v>
@@ -12615,7 +12628,7 @@
       <c r="E814" s="9"/>
       <c r="F814" s="9"/>
     </row>
-    <row r="815">
+    <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="11"/>
       <c r="B815" s="10" t="s">
         <v>2</v>
@@ -12629,7 +12642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="816">
+    <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="9"/>
       <c r="B816" s="10" t="s">
         <v>16</v>
@@ -12643,7 +12656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="817">
+    <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="9"/>
       <c r="B817" s="9" t="s">
         <v>19</v>
@@ -12655,7 +12668,7 @@
       <c r="E817" s="9"/>
       <c r="F817" s="9"/>
     </row>
-    <row r="818">
+    <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="9"/>
       <c r="B818" s="9" t="s">
         <v>20</v>
@@ -12667,7 +12680,7 @@
       <c r="E818" s="9"/>
       <c r="F818" s="9"/>
     </row>
-    <row r="819">
+    <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="9"/>
       <c r="B819" s="9" t="s">
         <v>22</v>
@@ -12679,7 +12692,7 @@
       <c r="E819" s="9"/>
       <c r="F819" s="9"/>
     </row>
-    <row r="820">
+    <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="9"/>
       <c r="B820" s="9" t="s">
         <v>23</v>
@@ -12691,7 +12704,7 @@
       <c r="E820" s="9"/>
       <c r="F820" s="9"/>
     </row>
-    <row r="821">
+    <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="9"/>
       <c r="B821" s="9" t="s">
         <v>25</v>
@@ -12703,7 +12716,7 @@
       <c r="E821" s="9"/>
       <c r="F821" s="9"/>
     </row>
-    <row r="822">
+    <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="9"/>
       <c r="B822" s="10" t="s">
         <v>26</v>
@@ -12715,7 +12728,7 @@
       </c>
       <c r="F822" s="9"/>
     </row>
-    <row r="823">
+    <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="9"/>
       <c r="B823" s="9" t="s">
         <v>28</v>
@@ -12727,7 +12740,7 @@
       <c r="E823" s="9"/>
       <c r="F823" s="9"/>
     </row>
-    <row r="824">
+    <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="9"/>
       <c r="B824" s="18" t="s">
         <v>30</v>
@@ -12739,7 +12752,7 @@
       <c r="E824" s="9"/>
       <c r="F824" s="9"/>
     </row>
-    <row r="825">
+    <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="9"/>
       <c r="B825" s="9"/>
       <c r="C825" s="9"/>
@@ -12747,7 +12760,7 @@
       <c r="E825" s="9"/>
       <c r="F825" s="9"/>
     </row>
-    <row r="826">
+    <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="8" t="s">
         <v>168</v>
       </c>
@@ -12757,7 +12770,7 @@
       <c r="E826" s="9"/>
       <c r="F826" s="9"/>
     </row>
-    <row r="827">
+    <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="9"/>
       <c r="B827" s="9" t="s">
         <v>10</v>
@@ -12769,7 +12782,7 @@
       <c r="E827" s="9"/>
       <c r="F827" s="9"/>
     </row>
-    <row r="828">
+    <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="9"/>
       <c r="B828" s="9" t="s">
         <v>12</v>
@@ -12781,7 +12794,7 @@
       <c r="E828" s="9"/>
       <c r="F828" s="9"/>
     </row>
-    <row r="829">
+    <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="11"/>
       <c r="B829" s="10" t="s">
         <v>2</v>
@@ -12795,7 +12808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="830">
+    <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="9"/>
       <c r="B830" s="10" t="s">
         <v>16</v>
@@ -12809,7 +12822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="831">
+    <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="9"/>
       <c r="B831" s="9" t="s">
         <v>19</v>
@@ -12821,7 +12834,7 @@
       <c r="E831" s="9"/>
       <c r="F831" s="9"/>
     </row>
-    <row r="832">
+    <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="9"/>
       <c r="B832" s="9" t="s">
         <v>20</v>
@@ -12833,7 +12846,7 @@
       <c r="E832" s="9"/>
       <c r="F832" s="9"/>
     </row>
-    <row r="833">
+    <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="9"/>
       <c r="B833" s="9" t="s">
         <v>22</v>
@@ -12845,7 +12858,7 @@
       <c r="E833" s="9"/>
       <c r="F833" s="9"/>
     </row>
-    <row r="834">
+    <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="9"/>
       <c r="B834" s="9" t="s">
         <v>23</v>
@@ -12857,7 +12870,7 @@
       <c r="E834" s="9"/>
       <c r="F834" s="9"/>
     </row>
-    <row r="835">
+    <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="9"/>
       <c r="B835" s="9" t="s">
         <v>25</v>
@@ -12869,7 +12882,7 @@
       <c r="E835" s="9"/>
       <c r="F835" s="9"/>
     </row>
-    <row r="836">
+    <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="9"/>
       <c r="B836" s="10" t="s">
         <v>26</v>
@@ -12881,7 +12894,7 @@
       </c>
       <c r="F836" s="9"/>
     </row>
-    <row r="837">
+    <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="9"/>
       <c r="B837" s="9" t="s">
         <v>28</v>
@@ -12893,7 +12906,7 @@
       <c r="E837" s="9"/>
       <c r="F837" s="9"/>
     </row>
-    <row r="838">
+    <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="9"/>
       <c r="B838" s="18" t="s">
         <v>30</v>
@@ -12905,7 +12918,7 @@
       <c r="E838" s="9"/>
       <c r="F838" s="9"/>
     </row>
-    <row r="839">
+    <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="9"/>
       <c r="B839" s="9"/>
       <c r="C839" s="11"/>
@@ -12913,7 +12926,7 @@
       <c r="E839" s="9"/>
       <c r="F839" s="9"/>
     </row>
-    <row r="840">
+    <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="8" t="s">
         <v>170</v>
       </c>
@@ -12923,7 +12936,7 @@
       <c r="E840" s="9"/>
       <c r="F840" s="9"/>
     </row>
-    <row r="841">
+    <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="9"/>
       <c r="B841" s="9" t="s">
         <v>10</v>
@@ -12935,7 +12948,7 @@
       <c r="E841" s="9"/>
       <c r="F841" s="9"/>
     </row>
-    <row r="842">
+    <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="9"/>
       <c r="B842" s="9" t="s">
         <v>12</v>
@@ -12947,7 +12960,7 @@
       <c r="E842" s="9"/>
       <c r="F842" s="9"/>
     </row>
-    <row r="843">
+    <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="10"/>
       <c r="B843" s="10" t="s">
         <v>2</v>
@@ -12959,7 +12972,7 @@
       <c r="E843" s="11"/>
       <c r="F843" s="11"/>
     </row>
-    <row r="844">
+    <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="9"/>
       <c r="B844" s="9" t="s">
         <v>19</v>
@@ -12971,7 +12984,7 @@
       <c r="E844" s="9"/>
       <c r="F844" s="9"/>
     </row>
-    <row r="845">
+    <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="9"/>
       <c r="B845" s="9" t="s">
         <v>20</v>
@@ -12983,7 +12996,7 @@
       <c r="E845" s="9"/>
       <c r="F845" s="9"/>
     </row>
-    <row r="846">
+    <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="9"/>
       <c r="B846" s="9" t="s">
         <v>22</v>
@@ -12995,7 +13008,7 @@
       <c r="E846" s="9"/>
       <c r="F846" s="9"/>
     </row>
-    <row r="847">
+    <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="9"/>
       <c r="B847" s="9" t="s">
         <v>23</v>
@@ -13007,7 +13020,7 @@
       <c r="E847" s="9"/>
       <c r="F847" s="9"/>
     </row>
-    <row r="848">
+    <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="9"/>
       <c r="B848" s="9" t="s">
         <v>25</v>
@@ -13019,7 +13032,7 @@
       <c r="E848" s="9"/>
       <c r="F848" s="9"/>
     </row>
-    <row r="849">
+    <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="9"/>
       <c r="B849" s="10" t="s">
         <v>26</v>
@@ -13031,7 +13044,7 @@
       </c>
       <c r="F849" s="9"/>
     </row>
-    <row r="850">
+    <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="9"/>
       <c r="B850" s="9" t="s">
         <v>28</v>
@@ -13043,7 +13056,7 @@
       <c r="E850" s="9"/>
       <c r="F850" s="9"/>
     </row>
-    <row r="851">
+    <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="9"/>
       <c r="B851" s="18" t="s">
         <v>30</v>
@@ -13055,7 +13068,7 @@
       <c r="E851" s="9"/>
       <c r="F851" s="9"/>
     </row>
-    <row r="852">
+    <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="9"/>
       <c r="B852" s="9"/>
       <c r="C852" s="9"/>
@@ -13063,7 +13076,7 @@
       <c r="E852" s="9"/>
       <c r="F852" s="9"/>
     </row>
-    <row r="853">
+    <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="8" t="s">
         <v>172</v>
       </c>
@@ -13073,7 +13086,7 @@
       <c r="E853" s="9"/>
       <c r="F853" s="9"/>
     </row>
-    <row r="854">
+    <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="9"/>
       <c r="B854" s="9" t="s">
         <v>10</v>
@@ -13085,7 +13098,7 @@
       <c r="E854" s="9"/>
       <c r="F854" s="9"/>
     </row>
-    <row r="855">
+    <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="9"/>
       <c r="B855" s="9" t="s">
         <v>12</v>
@@ -13097,7 +13110,7 @@
       <c r="E855" s="9"/>
       <c r="F855" s="9"/>
     </row>
-    <row r="856">
+    <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="10"/>
       <c r="B856" s="10" t="s">
         <v>2</v>
@@ -13109,7 +13122,7 @@
       <c r="E856" s="11"/>
       <c r="F856" s="9"/>
     </row>
-    <row r="857">
+    <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="9"/>
       <c r="B857" s="9" t="s">
         <v>19</v>
@@ -13121,7 +13134,7 @@
       <c r="E857" s="9"/>
       <c r="F857" s="9"/>
     </row>
-    <row r="858">
+    <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="9"/>
       <c r="B858" s="9" t="s">
         <v>20</v>
@@ -13133,7 +13146,7 @@
       <c r="E858" s="9"/>
       <c r="F858" s="9"/>
     </row>
-    <row r="859">
+    <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="9"/>
       <c r="B859" s="9" t="s">
         <v>22</v>
@@ -13145,7 +13158,7 @@
       <c r="E859" s="9"/>
       <c r="F859" s="9"/>
     </row>
-    <row r="860">
+    <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="9"/>
       <c r="B860" s="9" t="s">
         <v>23</v>
@@ -13157,7 +13170,7 @@
       <c r="E860" s="9"/>
       <c r="F860" s="9"/>
     </row>
-    <row r="861">
+    <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="9"/>
       <c r="B861" s="9" t="s">
         <v>25</v>
@@ -13169,7 +13182,7 @@
       <c r="E861" s="9"/>
       <c r="F861" s="9"/>
     </row>
-    <row r="862">
+    <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="9"/>
       <c r="B862" s="10" t="s">
         <v>26</v>
@@ -13181,7 +13194,7 @@
       </c>
       <c r="F862" s="9"/>
     </row>
-    <row r="863">
+    <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="9"/>
       <c r="B863" s="9" t="s">
         <v>28</v>
@@ -13193,7 +13206,7 @@
       <c r="E863" s="9"/>
       <c r="F863" s="9"/>
     </row>
-    <row r="864">
+    <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="9"/>
       <c r="B864" s="18" t="s">
         <v>30</v>
@@ -13205,7 +13218,8 @@
       <c r="E864" s="9"/>
       <c r="F864" s="9"/>
     </row>
-    <row r="866">
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="8" t="s">
         <v>174</v>
       </c>
@@ -13216,7 +13230,7 @@
       <c r="F866" s="9"/>
       <c r="G866" s="9"/>
     </row>
-    <row r="867">
+    <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="9"/>
       <c r="B867" s="9" t="s">
         <v>10</v>
@@ -13229,7 +13243,7 @@
       <c r="F867" s="9"/>
       <c r="G867" s="9"/>
     </row>
-    <row r="868">
+    <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="9"/>
       <c r="B868" s="9" t="s">
         <v>12</v>
@@ -13242,7 +13256,7 @@
       <c r="F868" s="9"/>
       <c r="G868" s="9"/>
     </row>
-    <row r="869">
+    <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="11"/>
       <c r="B869" s="10" t="s">
         <v>2</v>
@@ -13257,7 +13271,7 @@
       </c>
       <c r="G869" s="9"/>
     </row>
-    <row r="870">
+    <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="9"/>
       <c r="B870" s="10" t="s">
         <v>16</v>
@@ -13272,7 +13286,7 @@
       </c>
       <c r="G870" s="9"/>
     </row>
-    <row r="871">
+    <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="9"/>
       <c r="B871" s="9" t="s">
         <v>19</v>
@@ -13285,7 +13299,7 @@
       <c r="F871" s="9"/>
       <c r="G871" s="9"/>
     </row>
-    <row r="872">
+    <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="9"/>
       <c r="B872" s="9" t="s">
         <v>20</v>
@@ -13298,7 +13312,7 @@
       <c r="F872" s="9"/>
       <c r="G872" s="9"/>
     </row>
-    <row r="873">
+    <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="9"/>
       <c r="B873" s="9" t="s">
         <v>22</v>
@@ -13311,7 +13325,7 @@
       <c r="F873" s="9"/>
       <c r="G873" s="9"/>
     </row>
-    <row r="874">
+    <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="9"/>
       <c r="B874" s="9" t="s">
         <v>23</v>
@@ -13324,7 +13338,7 @@
       <c r="F874" s="9"/>
       <c r="G874" s="9"/>
     </row>
-    <row r="875">
+    <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="9"/>
       <c r="B875" s="9" t="s">
         <v>25</v>
@@ -13337,7 +13351,7 @@
       <c r="F875" s="9"/>
       <c r="G875" s="9"/>
     </row>
-    <row r="876">
+    <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="9"/>
       <c r="B876" s="10" t="s">
         <v>26</v>
@@ -13350,7 +13364,7 @@
       <c r="F876" s="9"/>
       <c r="G876" s="9"/>
     </row>
-    <row r="877">
+    <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="9"/>
       <c r="B877" s="9" t="s">
         <v>28</v>
@@ -13363,7 +13377,7 @@
       <c r="F877" s="9"/>
       <c r="G877" s="9"/>
     </row>
-    <row r="878">
+    <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="9"/>
       <c r="B878" s="18" t="s">
         <v>30</v>
@@ -13376,7 +13390,7 @@
       <c r="F878" s="9"/>
       <c r="G878" s="9"/>
     </row>
-    <row r="879">
+    <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="9"/>
       <c r="B879" s="9"/>
       <c r="C879" s="9"/>
@@ -13385,7 +13399,7 @@
       <c r="F879" s="9"/>
       <c r="G879" s="9"/>
     </row>
-    <row r="880">
+    <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="8" t="s">
         <v>177</v>
       </c>
@@ -13396,7 +13410,7 @@
       <c r="F880" s="9"/>
       <c r="G880" s="9"/>
     </row>
-    <row r="881">
+    <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="9"/>
       <c r="B881" s="9" t="s">
         <v>10</v>
@@ -13409,7 +13423,7 @@
       <c r="F881" s="9"/>
       <c r="G881" s="9"/>
     </row>
-    <row r="882">
+    <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="9"/>
       <c r="B882" s="9" t="s">
         <v>12</v>
@@ -13422,7 +13436,7 @@
       <c r="F882" s="9"/>
       <c r="G882" s="9"/>
     </row>
-    <row r="883">
+    <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="11"/>
       <c r="B883" s="10" t="s">
         <v>2</v>
@@ -13437,7 +13451,7 @@
       </c>
       <c r="G883" s="9"/>
     </row>
-    <row r="884">
+    <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="9"/>
       <c r="B884" s="10" t="s">
         <v>16</v>
@@ -13452,7 +13466,7 @@
       </c>
       <c r="G884" s="9"/>
     </row>
-    <row r="885">
+    <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="9"/>
       <c r="B885" s="9" t="s">
         <v>19</v>
@@ -13465,7 +13479,7 @@
       <c r="F885" s="9"/>
       <c r="G885" s="9"/>
     </row>
-    <row r="886">
+    <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="9"/>
       <c r="B886" s="9" t="s">
         <v>20</v>
@@ -13478,7 +13492,7 @@
       <c r="F886" s="9"/>
       <c r="G886" s="9"/>
     </row>
-    <row r="887">
+    <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="9"/>
       <c r="B887" s="9" t="s">
         <v>22</v>
@@ -13491,7 +13505,7 @@
       <c r="F887" s="9"/>
       <c r="G887" s="9"/>
     </row>
-    <row r="888">
+    <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="9"/>
       <c r="B888" s="9" t="s">
         <v>23</v>
@@ -13504,7 +13518,7 @@
       <c r="F888" s="9"/>
       <c r="G888" s="9"/>
     </row>
-    <row r="889">
+    <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="9"/>
       <c r="B889" s="9" t="s">
         <v>25</v>
@@ -13517,7 +13531,7 @@
       <c r="F889" s="9"/>
       <c r="G889" s="9"/>
     </row>
-    <row r="890">
+    <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="9"/>
       <c r="B890" s="10" t="s">
         <v>26</v>
@@ -13530,7 +13544,7 @@
       <c r="F890" s="9"/>
       <c r="G890" s="9"/>
     </row>
-    <row r="891">
+    <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="9"/>
       <c r="B891" s="9" t="s">
         <v>28</v>
@@ -13543,7 +13557,7 @@
       <c r="F891" s="9"/>
       <c r="G891" s="9"/>
     </row>
-    <row r="892">
+    <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="9"/>
       <c r="B892" s="18" t="s">
         <v>30</v>
@@ -13556,7 +13570,7 @@
       <c r="F892" s="9"/>
       <c r="G892" s="9"/>
     </row>
-    <row r="893">
+    <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="9"/>
       <c r="B893" s="9"/>
       <c r="C893" s="11"/>
@@ -13565,7 +13579,7 @@
       <c r="F893" s="9"/>
       <c r="G893" s="9"/>
     </row>
-    <row r="894">
+    <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="8" t="s">
         <v>179</v>
       </c>
@@ -13576,7 +13590,7 @@
       <c r="F894" s="9"/>
       <c r="G894" s="9"/>
     </row>
-    <row r="895">
+    <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="9"/>
       <c r="B895" s="9" t="s">
         <v>10</v>
@@ -13589,7 +13603,7 @@
       <c r="F895" s="9"/>
       <c r="G895" s="9"/>
     </row>
-    <row r="896">
+    <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="9"/>
       <c r="B896" s="9" t="s">
         <v>12</v>
@@ -13602,7 +13616,7 @@
       <c r="F896" s="9"/>
       <c r="G896" s="9"/>
     </row>
-    <row r="897">
+    <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="10"/>
       <c r="B897" s="10" t="s">
         <v>2</v>
@@ -13615,7 +13629,7 @@
       <c r="F897" s="11"/>
       <c r="G897" s="9"/>
     </row>
-    <row r="898">
+    <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="9"/>
       <c r="B898" s="9" t="s">
         <v>19</v>
@@ -13628,7 +13642,7 @@
       <c r="F898" s="9"/>
       <c r="G898" s="9"/>
     </row>
-    <row r="899">
+    <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="9"/>
       <c r="B899" s="9" t="s">
         <v>20</v>
@@ -13641,7 +13655,7 @@
       <c r="F899" s="9"/>
       <c r="G899" s="9"/>
     </row>
-    <row r="900">
+    <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="9"/>
       <c r="B900" s="9" t="s">
         <v>22</v>
@@ -13654,7 +13668,7 @@
       <c r="F900" s="9"/>
       <c r="G900" s="9"/>
     </row>
-    <row r="901">
+    <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="9"/>
       <c r="B901" s="9" t="s">
         <v>23</v>
@@ -13667,7 +13681,7 @@
       <c r="F901" s="9"/>
       <c r="G901" s="9"/>
     </row>
-    <row r="902">
+    <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="9"/>
       <c r="B902" s="9" t="s">
         <v>25</v>
@@ -13680,7 +13694,7 @@
       <c r="F902" s="9"/>
       <c r="G902" s="9"/>
     </row>
-    <row r="903">
+    <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="9"/>
       <c r="B903" s="10" t="s">
         <v>26</v>
@@ -13693,7 +13707,7 @@
       <c r="F903" s="9"/>
       <c r="G903" s="9"/>
     </row>
-    <row r="904">
+    <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="9"/>
       <c r="B904" s="9" t="s">
         <v>28</v>
@@ -13706,7 +13720,7 @@
       <c r="F904" s="9"/>
       <c r="G904" s="9"/>
     </row>
-    <row r="905">
+    <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="9"/>
       <c r="B905" s="18" t="s">
         <v>30</v>
@@ -13719,7 +13733,7 @@
       <c r="F905" s="9"/>
       <c r="G905" s="9"/>
     </row>
-    <row r="906">
+    <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="9"/>
       <c r="B906" s="9"/>
       <c r="C906" s="9"/>
@@ -13728,7 +13742,7 @@
       <c r="F906" s="9"/>
       <c r="G906" s="9"/>
     </row>
-    <row r="907">
+    <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="8" t="s">
         <v>181</v>
       </c>
@@ -13739,7 +13753,7 @@
       <c r="F907" s="9"/>
       <c r="G907" s="9"/>
     </row>
-    <row r="908">
+    <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="9"/>
       <c r="B908" s="9" t="s">
         <v>10</v>
@@ -13752,7 +13766,7 @@
       <c r="F908" s="9"/>
       <c r="G908" s="9"/>
     </row>
-    <row r="909">
+    <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="9"/>
       <c r="B909" s="9" t="s">
         <v>12</v>
@@ -13765,7 +13779,7 @@
       <c r="F909" s="9"/>
       <c r="G909" s="9"/>
     </row>
-    <row r="910">
+    <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="10"/>
       <c r="B910" s="10" t="s">
         <v>2</v>
@@ -13778,7 +13792,7 @@
       <c r="F910" s="9"/>
       <c r="G910" s="9"/>
     </row>
-    <row r="911">
+    <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="9"/>
       <c r="B911" s="9" t="s">
         <v>19</v>
@@ -13791,7 +13805,7 @@
       <c r="F911" s="9"/>
       <c r="G911" s="9"/>
     </row>
-    <row r="912">
+    <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="9"/>
       <c r="B912" s="9" t="s">
         <v>20</v>
@@ -13804,7 +13818,7 @@
       <c r="F912" s="9"/>
       <c r="G912" s="9"/>
     </row>
-    <row r="913">
+    <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="9"/>
       <c r="B913" s="9" t="s">
         <v>22</v>
@@ -13817,7 +13831,7 @@
       <c r="F913" s="9"/>
       <c r="G913" s="9"/>
     </row>
-    <row r="914">
+    <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="9"/>
       <c r="B914" s="9" t="s">
         <v>23</v>
@@ -13830,7 +13844,7 @@
       <c r="F914" s="9"/>
       <c r="G914" s="9"/>
     </row>
-    <row r="915">
+    <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="9"/>
       <c r="B915" s="9" t="s">
         <v>25</v>
@@ -13843,7 +13857,7 @@
       <c r="F915" s="9"/>
       <c r="G915" s="9"/>
     </row>
-    <row r="916">
+    <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="9"/>
       <c r="B916" s="10" t="s">
         <v>26</v>
@@ -13856,7 +13870,7 @@
       <c r="F916" s="9"/>
       <c r="G916" s="9"/>
     </row>
-    <row r="917">
+    <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="9"/>
       <c r="B917" s="9" t="s">
         <v>28</v>
@@ -13869,7 +13883,7 @@
       <c r="F917" s="9"/>
       <c r="G917" s="9"/>
     </row>
-    <row r="918">
+    <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="9"/>
       <c r="B918" s="18" t="s">
         <v>30</v>
@@ -13882,7 +13896,8 @@
       <c r="F918" s="9"/>
       <c r="G918" s="9"/>
     </row>
-    <row r="920">
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="9" t="s">
         <v>183</v>
       </c>
@@ -13891,7 +13906,7 @@
       <c r="D920" s="9"/>
       <c r="E920" s="9"/>
     </row>
-    <row r="921">
+    <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="9"/>
       <c r="B921" s="9" t="s">
         <v>10</v>
@@ -13902,7 +13917,7 @@
       <c r="D921" s="9"/>
       <c r="E921" s="9"/>
     </row>
-    <row r="922">
+    <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="9"/>
       <c r="B922" s="9" t="s">
         <v>12</v>
@@ -13913,7 +13928,7 @@
       <c r="D922" s="9"/>
       <c r="E922" s="9"/>
     </row>
-    <row r="923">
+    <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="9"/>
       <c r="B923" s="9" t="s">
         <v>2</v>
@@ -13924,7 +13939,7 @@
       <c r="D923" s="9"/>
       <c r="E923" s="9"/>
     </row>
-    <row r="924">
+    <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="9"/>
       <c r="B924" s="9" t="s">
         <v>19</v>
@@ -13933,7 +13948,7 @@
       <c r="D924" s="9"/>
       <c r="E924" s="9"/>
     </row>
-    <row r="925">
+    <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="9"/>
       <c r="B925" s="9" t="s">
         <v>20</v>
@@ -13944,7 +13959,7 @@
       <c r="D925" s="9"/>
       <c r="E925" s="9"/>
     </row>
-    <row r="926">
+    <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="9"/>
       <c r="B926" s="9" t="s">
         <v>186</v>
@@ -13955,7 +13970,7 @@
       <c r="D926" s="9"/>
       <c r="E926" s="9"/>
     </row>
-    <row r="927">
+    <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="9"/>
       <c r="B927" s="11" t="s">
         <v>188</v>
@@ -13966,7 +13981,8 @@
       <c r="D927" s="9"/>
       <c r="E927" s="9"/>
     </row>
-    <row r="929">
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="9" t="s">
         <v>190</v>
       </c>
@@ -13975,7 +13991,7 @@
       <c r="D929" s="9"/>
       <c r="E929" s="9"/>
     </row>
-    <row r="930">
+    <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="9"/>
       <c r="B930" s="9" t="s">
         <v>10</v>
@@ -13986,7 +14002,7 @@
       <c r="D930" s="9"/>
       <c r="E930" s="9"/>
     </row>
-    <row r="931">
+    <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="9"/>
       <c r="B931" s="9" t="s">
         <v>12</v>
@@ -13997,7 +14013,7 @@
       <c r="D931" s="9"/>
       <c r="E931" s="9"/>
     </row>
-    <row r="932">
+    <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="9"/>
       <c r="B932" s="9" t="s">
         <v>2</v>
@@ -14008,7 +14024,7 @@
       <c r="D932" s="9"/>
       <c r="E932" s="9"/>
     </row>
-    <row r="933">
+    <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="9"/>
       <c r="B933" s="9" t="s">
         <v>19</v>
@@ -14017,7 +14033,7 @@
       <c r="D933" s="9"/>
       <c r="E933" s="9"/>
     </row>
-    <row r="934">
+    <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="9"/>
       <c r="B934" s="9" t="s">
         <v>20</v>
@@ -14028,7 +14044,7 @@
       <c r="D934" s="9"/>
       <c r="E934" s="9"/>
     </row>
-    <row r="935">
+    <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="9"/>
       <c r="B935" s="9" t="s">
         <v>186</v>
@@ -14039,7 +14055,7 @@
       <c r="D935" s="9"/>
       <c r="E935" s="9"/>
     </row>
-    <row r="936">
+    <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="9"/>
       <c r="B936" s="11" t="s">
         <v>188</v>
@@ -14050,7 +14066,8 @@
       <c r="D936" s="9"/>
       <c r="E936" s="9"/>
     </row>
-    <row r="938">
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="9" t="s">
         <v>192</v>
       </c>
@@ -14059,7 +14076,7 @@
       <c r="D938" s="9"/>
       <c r="E938" s="9"/>
     </row>
-    <row r="939">
+    <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="9"/>
       <c r="B939" s="9" t="s">
         <v>10</v>
@@ -14070,7 +14087,7 @@
       <c r="D939" s="9"/>
       <c r="E939" s="9"/>
     </row>
-    <row r="940">
+    <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="9"/>
       <c r="B940" s="9" t="s">
         <v>12</v>
@@ -14081,7 +14098,7 @@
       <c r="D940" s="9"/>
       <c r="E940" s="9"/>
     </row>
-    <row r="941">
+    <row r="941" ht="15.75" customHeight="1">
       <c r="A941" s="9"/>
       <c r="B941" s="9" t="s">
         <v>2</v>
@@ -14092,7 +14109,7 @@
       <c r="D941" s="9"/>
       <c r="E941" s="9"/>
     </row>
-    <row r="942">
+    <row r="942" ht="15.75" customHeight="1">
       <c r="A942" s="9"/>
       <c r="B942" s="9" t="s">
         <v>19</v>
@@ -14101,7 +14118,7 @@
       <c r="D942" s="9"/>
       <c r="E942" s="9"/>
     </row>
-    <row r="943">
+    <row r="943" ht="15.75" customHeight="1">
       <c r="A943" s="9"/>
       <c r="B943" s="9" t="s">
         <v>20</v>
@@ -14112,7 +14129,7 @@
       <c r="D943" s="9"/>
       <c r="E943" s="9"/>
     </row>
-    <row r="944">
+    <row r="944" ht="15.75" customHeight="1">
       <c r="A944" s="9"/>
       <c r="B944" s="9" t="s">
         <v>186</v>
@@ -14123,7 +14140,7 @@
       <c r="D944" s="9"/>
       <c r="E944" s="9"/>
     </row>
-    <row r="945">
+    <row r="945" ht="15.75" customHeight="1">
       <c r="A945" s="9"/>
       <c r="B945" s="11" t="s">
         <v>188</v>
@@ -14134,7 +14151,8 @@
       <c r="D945" s="9"/>
       <c r="E945" s="9"/>
     </row>
-    <row r="947">
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1">
       <c r="A947" s="9" t="s">
         <v>194</v>
       </c>
@@ -14143,7 +14161,7 @@
       <c r="D947" s="9"/>
       <c r="E947" s="9"/>
     </row>
-    <row r="948">
+    <row r="948" ht="15.75" customHeight="1">
       <c r="A948" s="9"/>
       <c r="B948" s="9" t="s">
         <v>10</v>
@@ -14154,7 +14172,7 @@
       <c r="D948" s="9"/>
       <c r="E948" s="9"/>
     </row>
-    <row r="949">
+    <row r="949" ht="15.75" customHeight="1">
       <c r="A949" s="9"/>
       <c r="B949" s="9" t="s">
         <v>12</v>
@@ -14165,7 +14183,7 @@
       <c r="D949" s="9"/>
       <c r="E949" s="9"/>
     </row>
-    <row r="950">
+    <row r="950" ht="15.75" customHeight="1">
       <c r="A950" s="9"/>
       <c r="B950" s="9" t="s">
         <v>2</v>
@@ -14176,7 +14194,7 @@
       <c r="D950" s="9"/>
       <c r="E950" s="9"/>
     </row>
-    <row r="951">
+    <row r="951" ht="15.75" customHeight="1">
       <c r="A951" s="9"/>
       <c r="B951" s="9" t="s">
         <v>19</v>
@@ -14185,7 +14203,7 @@
       <c r="D951" s="9"/>
       <c r="E951" s="9"/>
     </row>
-    <row r="952">
+    <row r="952" ht="15.75" customHeight="1">
       <c r="A952" s="9"/>
       <c r="B952" s="9" t="s">
         <v>20</v>
@@ -14196,7 +14214,7 @@
       <c r="D952" s="9"/>
       <c r="E952" s="9"/>
     </row>
-    <row r="953">
+    <row r="953" ht="15.75" customHeight="1">
       <c r="A953" s="9"/>
       <c r="B953" s="9" t="s">
         <v>186</v>
@@ -14207,7 +14225,7 @@
       <c r="D953" s="9"/>
       <c r="E953" s="9"/>
     </row>
-    <row r="954">
+    <row r="954" ht="15.75" customHeight="1">
       <c r="A954" s="9"/>
       <c r="B954" s="11" t="s">
         <v>188</v>
@@ -14218,7 +14236,8 @@
       <c r="D954" s="9"/>
       <c r="E954" s="9"/>
     </row>
-    <row r="956">
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1">
       <c r="A956" s="9" t="s">
         <v>196</v>
       </c>
@@ -14227,7 +14246,7 @@
       <c r="D956" s="9"/>
       <c r="E956" s="9"/>
     </row>
-    <row r="957">
+    <row r="957" ht="15.75" customHeight="1">
       <c r="A957" s="9"/>
       <c r="B957" s="9" t="s">
         <v>10</v>
@@ -14238,7 +14257,7 @@
       <c r="D957" s="9"/>
       <c r="E957" s="9"/>
     </row>
-    <row r="958">
+    <row r="958" ht="15.75" customHeight="1">
       <c r="A958" s="9"/>
       <c r="B958" s="9" t="s">
         <v>12</v>
@@ -14249,7 +14268,7 @@
       <c r="D958" s="9"/>
       <c r="E958" s="9"/>
     </row>
-    <row r="959">
+    <row r="959" ht="15.75" customHeight="1">
       <c r="A959" s="9"/>
       <c r="B959" s="9" t="s">
         <v>2</v>
@@ -14260,7 +14279,7 @@
       <c r="D959" s="9"/>
       <c r="E959" s="9"/>
     </row>
-    <row r="960">
+    <row r="960" ht="15.75" customHeight="1">
       <c r="A960" s="9"/>
       <c r="B960" s="9" t="s">
         <v>19</v>
@@ -14269,7 +14288,7 @@
       <c r="D960" s="9"/>
       <c r="E960" s="9"/>
     </row>
-    <row r="961">
+    <row r="961" ht="15.75" customHeight="1">
       <c r="A961" s="9"/>
       <c r="B961" s="9" t="s">
         <v>20</v>
@@ -14280,7 +14299,7 @@
       <c r="D961" s="9"/>
       <c r="E961" s="9"/>
     </row>
-    <row r="962">
+    <row r="962" ht="15.75" customHeight="1">
       <c r="A962" s="9"/>
       <c r="B962" s="9" t="s">
         <v>186</v>
@@ -14291,7 +14310,7 @@
       <c r="D962" s="9"/>
       <c r="E962" s="9"/>
     </row>
-    <row r="963">
+    <row r="963" ht="15.75" customHeight="1">
       <c r="A963" s="9"/>
       <c r="B963" s="11" t="s">
         <v>188</v>
@@ -14302,7 +14321,8 @@
       <c r="D963" s="9"/>
       <c r="E963" s="9"/>
     </row>
-    <row r="965">
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1">
       <c r="A965" s="9" t="s">
         <v>198</v>
       </c>
@@ -14311,7 +14331,7 @@
       <c r="D965" s="9"/>
       <c r="E965" s="9"/>
     </row>
-    <row r="966">
+    <row r="966" ht="15.75" customHeight="1">
       <c r="A966" s="9"/>
       <c r="B966" s="9" t="s">
         <v>10</v>
@@ -14322,7 +14342,7 @@
       <c r="D966" s="9"/>
       <c r="E966" s="9"/>
     </row>
-    <row r="967">
+    <row r="967" ht="15.75" customHeight="1">
       <c r="A967" s="9"/>
       <c r="B967" s="9" t="s">
         <v>12</v>
@@ -14333,7 +14353,7 @@
       <c r="D967" s="9"/>
       <c r="E967" s="9"/>
     </row>
-    <row r="968">
+    <row r="968" ht="15.75" customHeight="1">
       <c r="A968" s="9"/>
       <c r="B968" s="9" t="s">
         <v>2</v>
@@ -14344,7 +14364,7 @@
       <c r="D968" s="9"/>
       <c r="E968" s="9"/>
     </row>
-    <row r="969">
+    <row r="969" ht="15.75" customHeight="1">
       <c r="A969" s="9"/>
       <c r="B969" s="9" t="s">
         <v>19</v>
@@ -14353,7 +14373,7 @@
       <c r="D969" s="9"/>
       <c r="E969" s="9"/>
     </row>
-    <row r="970">
+    <row r="970" ht="15.75" customHeight="1">
       <c r="A970" s="9"/>
       <c r="B970" s="9" t="s">
         <v>20</v>
@@ -14364,7 +14384,7 @@
       <c r="D970" s="9"/>
       <c r="E970" s="9"/>
     </row>
-    <row r="971">
+    <row r="971" ht="15.75" customHeight="1">
       <c r="A971" s="9"/>
       <c r="B971" s="9" t="s">
         <v>186</v>
@@ -14375,7 +14395,7 @@
       <c r="D971" s="9"/>
       <c r="E971" s="9"/>
     </row>
-    <row r="972">
+    <row r="972" ht="15.75" customHeight="1">
       <c r="A972" s="9"/>
       <c r="B972" s="11" t="s">
         <v>188</v>
@@ -14386,7 +14406,8 @@
       <c r="D972" s="9"/>
       <c r="E972" s="9"/>
     </row>
-    <row r="974">
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1">
       <c r="A974" s="9" t="s">
         <v>200</v>
       </c>
@@ -14395,7 +14416,7 @@
       <c r="D974" s="9"/>
       <c r="E974" s="9"/>
     </row>
-    <row r="975">
+    <row r="975" ht="15.75" customHeight="1">
       <c r="A975" s="9"/>
       <c r="B975" s="9" t="s">
         <v>10</v>
@@ -14406,7 +14427,7 @@
       <c r="D975" s="9"/>
       <c r="E975" s="9"/>
     </row>
-    <row r="976">
+    <row r="976" ht="15.75" customHeight="1">
       <c r="A976" s="9"/>
       <c r="B976" s="9" t="s">
         <v>12</v>
@@ -14417,7 +14438,7 @@
       <c r="D976" s="9"/>
       <c r="E976" s="9"/>
     </row>
-    <row r="977">
+    <row r="977" ht="15.75" customHeight="1">
       <c r="A977" s="9"/>
       <c r="B977" s="9" t="s">
         <v>2</v>
@@ -14428,7 +14449,7 @@
       <c r="D977" s="9"/>
       <c r="E977" s="9"/>
     </row>
-    <row r="978">
+    <row r="978" ht="15.75" customHeight="1">
       <c r="A978" s="9"/>
       <c r="B978" s="9" t="s">
         <v>19</v>
@@ -14437,7 +14458,7 @@
       <c r="D978" s="9"/>
       <c r="E978" s="9"/>
     </row>
-    <row r="979">
+    <row r="979" ht="15.75" customHeight="1">
       <c r="A979" s="9"/>
       <c r="B979" s="9" t="s">
         <v>20</v>
@@ -14448,7 +14469,7 @@
       <c r="D979" s="9"/>
       <c r="E979" s="9"/>
     </row>
-    <row r="980">
+    <row r="980" ht="15.75" customHeight="1">
       <c r="A980" s="9"/>
       <c r="B980" s="9" t="s">
         <v>186</v>
@@ -14459,7 +14480,7 @@
       <c r="D980" s="9"/>
       <c r="E980" s="9"/>
     </row>
-    <row r="981">
+    <row r="981" ht="15.75" customHeight="1">
       <c r="A981" s="9"/>
       <c r="B981" s="11" t="s">
         <v>188</v>
@@ -14470,7 +14491,8 @@
       <c r="D981" s="9"/>
       <c r="E981" s="9"/>
     </row>
-    <row r="983">
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1">
       <c r="A983" s="9" t="s">
         <v>202</v>
       </c>
@@ -14479,7 +14501,7 @@
       <c r="D983" s="9"/>
       <c r="E983" s="9"/>
     </row>
-    <row r="984">
+    <row r="984" ht="15.75" customHeight="1">
       <c r="A984" s="9"/>
       <c r="B984" s="9" t="s">
         <v>10</v>
@@ -14490,7 +14512,7 @@
       <c r="D984" s="9"/>
       <c r="E984" s="9"/>
     </row>
-    <row r="985">
+    <row r="985" ht="15.75" customHeight="1">
       <c r="A985" s="9"/>
       <c r="B985" s="9" t="s">
         <v>12</v>
@@ -14501,7 +14523,7 @@
       <c r="D985" s="9"/>
       <c r="E985" s="9"/>
     </row>
-    <row r="986">
+    <row r="986" ht="15.75" customHeight="1">
       <c r="A986" s="9"/>
       <c r="B986" s="9" t="s">
         <v>2</v>
@@ -14512,7 +14534,7 @@
       <c r="D986" s="9"/>
       <c r="E986" s="9"/>
     </row>
-    <row r="987">
+    <row r="987" ht="15.75" customHeight="1">
       <c r="A987" s="9"/>
       <c r="B987" s="9" t="s">
         <v>19</v>
@@ -14521,7 +14543,7 @@
       <c r="D987" s="9"/>
       <c r="E987" s="9"/>
     </row>
-    <row r="988">
+    <row r="988" ht="15.75" customHeight="1">
       <c r="A988" s="9"/>
       <c r="B988" s="9" t="s">
         <v>20</v>
@@ -14532,7 +14554,7 @@
       <c r="D988" s="9"/>
       <c r="E988" s="9"/>
     </row>
-    <row r="989">
+    <row r="989" ht="15.75" customHeight="1">
       <c r="A989" s="9"/>
       <c r="B989" s="9" t="s">
         <v>186</v>
@@ -14543,7 +14565,7 @@
       <c r="D989" s="9"/>
       <c r="E989" s="9"/>
     </row>
-    <row r="990">
+    <row r="990" ht="15.75" customHeight="1">
       <c r="A990" s="9"/>
       <c r="B990" s="11" t="s">
         <v>188</v>
@@ -14554,7 +14576,8 @@
       <c r="D990" s="9"/>
       <c r="E990" s="9"/>
     </row>
-    <row r="992">
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1">
       <c r="A992" s="9" t="s">
         <v>204</v>
       </c>
@@ -14563,7 +14586,7 @@
       <c r="D992" s="9"/>
       <c r="E992" s="9"/>
     </row>
-    <row r="993">
+    <row r="993" ht="15.75" customHeight="1">
       <c r="A993" s="9"/>
       <c r="B993" s="9" t="s">
         <v>10</v>
@@ -14574,7 +14597,7 @@
       <c r="D993" s="9"/>
       <c r="E993" s="9"/>
     </row>
-    <row r="994">
+    <row r="994" ht="15.75" customHeight="1">
       <c r="A994" s="9"/>
       <c r="B994" s="9" t="s">
         <v>12</v>
@@ -14585,7 +14608,7 @@
       <c r="D994" s="9"/>
       <c r="E994" s="9"/>
     </row>
-    <row r="995">
+    <row r="995" ht="15.75" customHeight="1">
       <c r="A995" s="9"/>
       <c r="B995" s="9" t="s">
         <v>2</v>
@@ -14596,7 +14619,7 @@
       <c r="D995" s="9"/>
       <c r="E995" s="9"/>
     </row>
-    <row r="996">
+    <row r="996" ht="15.75" customHeight="1">
       <c r="A996" s="9"/>
       <c r="B996" s="9" t="s">
         <v>19</v>
@@ -14605,7 +14628,7 @@
       <c r="D996" s="9"/>
       <c r="E996" s="9"/>
     </row>
-    <row r="997">
+    <row r="997" ht="15.75" customHeight="1">
       <c r="A997" s="9"/>
       <c r="B997" s="9" t="s">
         <v>20</v>
@@ -14616,7 +14639,7 @@
       <c r="D997" s="9"/>
       <c r="E997" s="9"/>
     </row>
-    <row r="998">
+    <row r="998" ht="15.75" customHeight="1">
       <c r="A998" s="9"/>
       <c r="B998" s="9" t="s">
         <v>186</v>
@@ -14627,7 +14650,7 @@
       <c r="D998" s="9"/>
       <c r="E998" s="9"/>
     </row>
-    <row r="999">
+    <row r="999" ht="15.75" customHeight="1">
       <c r="A999" s="9"/>
       <c r="B999" s="11" t="s">
         <v>188</v>
@@ -14638,7 +14661,8 @@
       <c r="D999" s="9"/>
       <c r="E999" s="9"/>
     </row>
-    <row r="1001">
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1">
       <c r="A1001" s="9" t="s">
         <v>206</v>
       </c>
@@ -14647,7 +14671,7 @@
       <c r="D1001" s="9"/>
       <c r="E1001" s="9"/>
     </row>
-    <row r="1002">
+    <row r="1002" ht="15.75" customHeight="1">
       <c r="A1002" s="9"/>
       <c r="B1002" s="9" t="s">
         <v>10</v>
@@ -14658,7 +14682,7 @@
       <c r="D1002" s="9"/>
       <c r="E1002" s="9"/>
     </row>
-    <row r="1003">
+    <row r="1003" ht="15.75" customHeight="1">
       <c r="A1003" s="9"/>
       <c r="B1003" s="9" t="s">
         <v>12</v>
@@ -14669,7 +14693,7 @@
       <c r="D1003" s="9"/>
       <c r="E1003" s="9"/>
     </row>
-    <row r="1004">
+    <row r="1004" ht="15.75" customHeight="1">
       <c r="A1004" s="9"/>
       <c r="B1004" s="9" t="s">
         <v>2</v>
@@ -14680,7 +14704,7 @@
       <c r="D1004" s="9"/>
       <c r="E1004" s="9"/>
     </row>
-    <row r="1005">
+    <row r="1005" ht="15.75" customHeight="1">
       <c r="A1005" s="9"/>
       <c r="B1005" s="9" t="s">
         <v>19</v>
@@ -14689,7 +14713,7 @@
       <c r="D1005" s="9"/>
       <c r="E1005" s="9"/>
     </row>
-    <row r="1006">
+    <row r="1006" ht="15.75" customHeight="1">
       <c r="A1006" s="9"/>
       <c r="B1006" s="9" t="s">
         <v>20</v>
@@ -14700,7 +14724,7 @@
       <c r="D1006" s="9"/>
       <c r="E1006" s="9"/>
     </row>
-    <row r="1007">
+    <row r="1007" ht="15.75" customHeight="1">
       <c r="A1007" s="9"/>
       <c r="B1007" s="9" t="s">
         <v>186</v>
@@ -14711,7 +14735,7 @@
       <c r="D1007" s="9"/>
       <c r="E1007" s="9"/>
     </row>
-    <row r="1008">
+    <row r="1008" ht="15.75" customHeight="1">
       <c r="A1008" s="9"/>
       <c r="B1008" s="11" t="s">
         <v>188</v>
@@ -14722,7 +14746,8 @@
       <c r="D1008" s="9"/>
       <c r="E1008" s="9"/>
     </row>
-    <row r="1010">
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1">
       <c r="A1010" s="9" t="s">
         <v>208</v>
       </c>
@@ -14731,7 +14756,7 @@
       <c r="D1010" s="9"/>
       <c r="E1010" s="9"/>
     </row>
-    <row r="1011">
+    <row r="1011" ht="15.75" customHeight="1">
       <c r="A1011" s="9"/>
       <c r="B1011" s="9" t="s">
         <v>10</v>
@@ -14742,7 +14767,7 @@
       <c r="D1011" s="9"/>
       <c r="E1011" s="9"/>
     </row>
-    <row r="1012">
+    <row r="1012" ht="15.75" customHeight="1">
       <c r="A1012" s="9"/>
       <c r="B1012" s="9" t="s">
         <v>12</v>
@@ -14753,7 +14778,7 @@
       <c r="D1012" s="9"/>
       <c r="E1012" s="9"/>
     </row>
-    <row r="1013">
+    <row r="1013" ht="15.75" customHeight="1">
       <c r="A1013" s="9"/>
       <c r="B1013" s="9" t="s">
         <v>2</v>
@@ -14764,7 +14789,7 @@
       <c r="D1013" s="9"/>
       <c r="E1013" s="9"/>
     </row>
-    <row r="1014">
+    <row r="1014" ht="15.75" customHeight="1">
       <c r="A1014" s="9"/>
       <c r="B1014" s="9" t="s">
         <v>19</v>
@@ -14773,7 +14798,7 @@
       <c r="D1014" s="9"/>
       <c r="E1014" s="9"/>
     </row>
-    <row r="1015">
+    <row r="1015" ht="15.75" customHeight="1">
       <c r="A1015" s="9"/>
       <c r="B1015" s="9" t="s">
         <v>20</v>
@@ -14784,7 +14809,7 @@
       <c r="D1015" s="9"/>
       <c r="E1015" s="9"/>
     </row>
-    <row r="1016">
+    <row r="1016" ht="15.75" customHeight="1">
       <c r="A1016" s="9"/>
       <c r="B1016" s="9" t="s">
         <v>186</v>
@@ -14795,7 +14820,7 @@
       <c r="D1016" s="9"/>
       <c r="E1016" s="9"/>
     </row>
-    <row r="1017">
+    <row r="1017" ht="15.75" customHeight="1">
       <c r="A1017" s="9"/>
       <c r="B1017" s="11" t="s">
         <v>188</v>
@@ -14806,7 +14831,8 @@
       <c r="D1017" s="9"/>
       <c r="E1017" s="9"/>
     </row>
-    <row r="1019">
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1">
       <c r="A1019" s="9" t="s">
         <v>210</v>
       </c>
@@ -14815,7 +14841,7 @@
       <c r="D1019" s="9"/>
       <c r="E1019" s="9"/>
     </row>
-    <row r="1020">
+    <row r="1020" ht="15.75" customHeight="1">
       <c r="A1020" s="9"/>
       <c r="B1020" s="9" t="s">
         <v>10</v>
@@ -14826,7 +14852,7 @@
       <c r="D1020" s="9"/>
       <c r="E1020" s="9"/>
     </row>
-    <row r="1021">
+    <row r="1021" ht="15.75" customHeight="1">
       <c r="A1021" s="9"/>
       <c r="B1021" s="9" t="s">
         <v>12</v>
@@ -14837,7 +14863,7 @@
       <c r="D1021" s="9"/>
       <c r="E1021" s="9"/>
     </row>
-    <row r="1022">
+    <row r="1022" ht="15.75" customHeight="1">
       <c r="A1022" s="9"/>
       <c r="B1022" s="9" t="s">
         <v>2</v>
@@ -14848,7 +14874,7 @@
       <c r="D1022" s="9"/>
       <c r="E1022" s="9"/>
     </row>
-    <row r="1023">
+    <row r="1023" ht="15.75" customHeight="1">
       <c r="A1023" s="9"/>
       <c r="B1023" s="9" t="s">
         <v>19</v>
@@ -14857,7 +14883,7 @@
       <c r="D1023" s="9"/>
       <c r="E1023" s="9"/>
     </row>
-    <row r="1024">
+    <row r="1024" ht="15.75" customHeight="1">
       <c r="A1024" s="9"/>
       <c r="B1024" s="9" t="s">
         <v>20</v>
@@ -14868,7 +14894,7 @@
       <c r="D1024" s="9"/>
       <c r="E1024" s="9"/>
     </row>
-    <row r="1025">
+    <row r="1025" ht="15.75" customHeight="1">
       <c r="A1025" s="9"/>
       <c r="B1025" s="9" t="s">
         <v>186</v>
@@ -14879,7 +14905,7 @@
       <c r="D1025" s="9"/>
       <c r="E1025" s="9"/>
     </row>
-    <row r="1026">
+    <row r="1026" ht="15.75" customHeight="1">
       <c r="A1026" s="9"/>
       <c r="B1026" s="11" t="s">
         <v>188</v>
@@ -14890,7 +14916,8 @@
       <c r="D1026" s="9"/>
       <c r="E1026" s="9"/>
     </row>
-    <row r="1028">
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1">
       <c r="A1028" s="9" t="s">
         <v>212</v>
       </c>
@@ -14899,7 +14926,7 @@
       <c r="D1028" s="9"/>
       <c r="E1028" s="9"/>
     </row>
-    <row r="1029">
+    <row r="1029" ht="15.75" customHeight="1">
       <c r="A1029" s="9"/>
       <c r="B1029" s="9" t="s">
         <v>10</v>
@@ -14910,7 +14937,7 @@
       <c r="D1029" s="9"/>
       <c r="E1029" s="9"/>
     </row>
-    <row r="1030">
+    <row r="1030" ht="15.75" customHeight="1">
       <c r="A1030" s="9"/>
       <c r="B1030" s="9" t="s">
         <v>12</v>
@@ -14921,7 +14948,7 @@
       <c r="D1030" s="9"/>
       <c r="E1030" s="9"/>
     </row>
-    <row r="1031">
+    <row r="1031" ht="15.75" customHeight="1">
       <c r="A1031" s="9"/>
       <c r="B1031" s="9" t="s">
         <v>2</v>
@@ -14932,7 +14959,7 @@
       <c r="D1031" s="9"/>
       <c r="E1031" s="9"/>
     </row>
-    <row r="1032">
+    <row r="1032" ht="15.75" customHeight="1">
       <c r="A1032" s="9"/>
       <c r="B1032" s="9" t="s">
         <v>19</v>
@@ -14941,7 +14968,7 @@
       <c r="D1032" s="9"/>
       <c r="E1032" s="9"/>
     </row>
-    <row r="1033">
+    <row r="1033" ht="15.75" customHeight="1">
       <c r="A1033" s="9"/>
       <c r="B1033" s="9" t="s">
         <v>20</v>
@@ -14952,7 +14979,7 @@
       <c r="D1033" s="9"/>
       <c r="E1033" s="9"/>
     </row>
-    <row r="1034">
+    <row r="1034" ht="15.75" customHeight="1">
       <c r="A1034" s="9"/>
       <c r="B1034" s="9" t="s">
         <v>186</v>
@@ -14963,7 +14990,7 @@
       <c r="D1034" s="9"/>
       <c r="E1034" s="9"/>
     </row>
-    <row r="1035">
+    <row r="1035" ht="15.75" customHeight="1">
       <c r="A1035" s="9"/>
       <c r="B1035" s="11" t="s">
         <v>188</v>
@@ -14974,7 +15001,8 @@
       <c r="D1035" s="9"/>
       <c r="E1035" s="9"/>
     </row>
-    <row r="1037">
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1">
       <c r="A1037" s="9" t="s">
         <v>214</v>
       </c>
@@ -14983,7 +15011,7 @@
       <c r="D1037" s="9"/>
       <c r="E1037" s="9"/>
     </row>
-    <row r="1038">
+    <row r="1038" ht="15.75" customHeight="1">
       <c r="A1038" s="9"/>
       <c r="B1038" s="9" t="s">
         <v>10</v>
@@ -14994,7 +15022,7 @@
       <c r="D1038" s="9"/>
       <c r="E1038" s="9"/>
     </row>
-    <row r="1039">
+    <row r="1039" ht="15.75" customHeight="1">
       <c r="A1039" s="9"/>
       <c r="B1039" s="9" t="s">
         <v>12</v>
@@ -15005,7 +15033,7 @@
       <c r="D1039" s="9"/>
       <c r="E1039" s="9"/>
     </row>
-    <row r="1040">
+    <row r="1040" ht="15.75" customHeight="1">
       <c r="A1040" s="9"/>
       <c r="B1040" s="9" t="s">
         <v>2</v>
@@ -15016,7 +15044,7 @@
       <c r="D1040" s="9"/>
       <c r="E1040" s="9"/>
     </row>
-    <row r="1041">
+    <row r="1041" ht="15.75" customHeight="1">
       <c r="A1041" s="9"/>
       <c r="B1041" s="9" t="s">
         <v>19</v>
@@ -15025,7 +15053,7 @@
       <c r="D1041" s="9"/>
       <c r="E1041" s="9"/>
     </row>
-    <row r="1042">
+    <row r="1042" ht="15.75" customHeight="1">
       <c r="A1042" s="9"/>
       <c r="B1042" s="9" t="s">
         <v>20</v>
@@ -15036,7 +15064,7 @@
       <c r="D1042" s="9"/>
       <c r="E1042" s="9"/>
     </row>
-    <row r="1043">
+    <row r="1043" ht="15.75" customHeight="1">
       <c r="A1043" s="9"/>
       <c r="B1043" s="9" t="s">
         <v>186</v>
@@ -15047,7 +15075,7 @@
       <c r="D1043" s="9"/>
       <c r="E1043" s="9"/>
     </row>
-    <row r="1044">
+    <row r="1044" ht="15.75" customHeight="1">
       <c r="A1044" s="9"/>
       <c r="B1044" s="11" t="s">
         <v>188</v>
@@ -15058,7 +15086,8 @@
       <c r="D1044" s="9"/>
       <c r="E1044" s="9"/>
     </row>
-    <row r="1046">
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1">
       <c r="A1046" s="9" t="s">
         <v>216</v>
       </c>
@@ -15067,7 +15096,7 @@
       <c r="D1046" s="9"/>
       <c r="E1046" s="9"/>
     </row>
-    <row r="1047">
+    <row r="1047" ht="15.75" customHeight="1">
       <c r="A1047" s="9"/>
       <c r="B1047" s="9" t="s">
         <v>10</v>
@@ -15078,7 +15107,7 @@
       <c r="D1047" s="9"/>
       <c r="E1047" s="9"/>
     </row>
-    <row r="1048">
+    <row r="1048" ht="15.75" customHeight="1">
       <c r="A1048" s="9"/>
       <c r="B1048" s="9" t="s">
         <v>12</v>
@@ -15089,7 +15118,7 @@
       <c r="D1048" s="9"/>
       <c r="E1048" s="9"/>
     </row>
-    <row r="1049">
+    <row r="1049" ht="15.75" customHeight="1">
       <c r="A1049" s="9"/>
       <c r="B1049" s="9" t="s">
         <v>2</v>
@@ -15100,7 +15129,7 @@
       <c r="D1049" s="9"/>
       <c r="E1049" s="9"/>
     </row>
-    <row r="1050">
+    <row r="1050" ht="15.75" customHeight="1">
       <c r="A1050" s="9"/>
       <c r="B1050" s="9" t="s">
         <v>19</v>
@@ -15109,7 +15138,7 @@
       <c r="D1050" s="9"/>
       <c r="E1050" s="9"/>
     </row>
-    <row r="1051">
+    <row r="1051" ht="15.75" customHeight="1">
       <c r="A1051" s="9"/>
       <c r="B1051" s="9" t="s">
         <v>20</v>
@@ -15120,7 +15149,7 @@
       <c r="D1051" s="9"/>
       <c r="E1051" s="9"/>
     </row>
-    <row r="1052">
+    <row r="1052" ht="15.75" customHeight="1">
       <c r="A1052" s="9"/>
       <c r="B1052" s="9" t="s">
         <v>186</v>
@@ -15131,7 +15160,7 @@
       <c r="D1052" s="9"/>
       <c r="E1052" s="9"/>
     </row>
-    <row r="1053">
+    <row r="1053" ht="15.75" customHeight="1">
       <c r="A1053" s="9"/>
       <c r="B1053" s="11" t="s">
         <v>188</v>
